--- a/research/traditional_assets/database/data/chile/chile_steel.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_steel.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -590,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0805</v>
+        <v>0.040665</v>
       </c>
       <c r="G2">
-        <v>0.319154078549849</v>
+        <v>0.2863729871603887</v>
       </c>
       <c r="H2">
-        <v>0.319154078549849</v>
+        <v>0.2863729871603887</v>
       </c>
       <c r="I2">
-        <v>0.1437260825780463</v>
+        <v>0.1246080726395687</v>
       </c>
       <c r="J2">
-        <v>0.1437260825780463</v>
+        <v>0.1246080726395687</v>
       </c>
       <c r="K2">
-        <v>-203</v>
+        <v>-252.3</v>
       </c>
       <c r="L2">
-        <v>-0.08177240684793555</v>
+        <v>-0.08948712492019578</v>
       </c>
       <c r="M2">
-        <v>127.8</v>
+        <v>128.94</v>
       </c>
       <c r="N2">
-        <v>0.161608497723824</v>
+        <v>0.1512492668621701</v>
       </c>
       <c r="O2">
-        <v>-0.6295566502463054</v>
+        <v>-0.5110582639714625</v>
       </c>
       <c r="P2">
-        <v>127.8</v>
+        <v>128.94</v>
       </c>
       <c r="Q2">
-        <v>0.161608497723824</v>
+        <v>0.1512492668621701</v>
       </c>
       <c r="R2">
-        <v>-0.6295566502463054</v>
+        <v>-0.5110582639714625</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -635,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>459.9</v>
+        <v>477.8</v>
       </c>
       <c r="V2">
-        <v>0.5815629742033384</v>
+        <v>0.5604692082111437</v>
       </c>
       <c r="W2">
-        <v>-0.09586324140536456</v>
+        <v>-0.2521569728153583</v>
       </c>
       <c r="X2">
-        <v>0.1886208396490575</v>
+        <v>0.2219064327649955</v>
       </c>
       <c r="Y2">
-        <v>-0.2844840810544221</v>
+        <v>-0.4740634055803539</v>
       </c>
       <c r="Z2">
-        <v>0.739103251161129</v>
+        <v>0.772544184134813</v>
       </c>
       <c r="AA2">
-        <v>0.1062284149100869</v>
+        <v>0.04368868285924023</v>
       </c>
       <c r="AB2">
-        <v>0.09287537190101647</v>
+        <v>0.08959542339165047</v>
       </c>
       <c r="AC2">
-        <v>0.01335304300907046</v>
+        <v>-0.04590674053241024</v>
       </c>
       <c r="AD2">
-        <v>1802.4</v>
+        <v>2048.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1802.4</v>
+        <v>2048.2</v>
       </c>
       <c r="AG2">
-        <v>1342.5</v>
+        <v>1570.4</v>
       </c>
       <c r="AH2">
-        <v>0.6950485886163814</v>
+        <v>0.7061054228289724</v>
       </c>
       <c r="AI2">
-        <v>0.3548590329185698</v>
+        <v>0.3772285251215559</v>
       </c>
       <c r="AJ2">
-        <v>0.6293067079173111</v>
+        <v>0.6481489124602748</v>
       </c>
       <c r="AK2">
-        <v>0.2906284501980819</v>
+        <v>0.3171372026333859</v>
       </c>
       <c r="AL2">
-        <v>118.3</v>
+        <v>146.8</v>
       </c>
       <c r="AM2">
-        <v>92.59999999999999</v>
+        <v>119.83</v>
       </c>
       <c r="AN2">
-        <v>2.478547854785479</v>
+        <v>2.777596962299973</v>
       </c>
       <c r="AO2">
-        <v>3.016060862214708</v>
+        <v>2.393188010899182</v>
       </c>
       <c r="AP2">
-        <v>1.846122112211221</v>
+        <v>2.129644697586114</v>
       </c>
       <c r="AQ2">
-        <v>3.853131749460044</v>
+        <v>2.931820078444463</v>
       </c>
     </row>
     <row r="3">
@@ -775,10 +775,10 @@
         <v>-0.09586324140536456</v>
       </c>
       <c r="X3">
-        <v>0.1886208396490575</v>
+        <v>0.1885623465803147</v>
       </c>
       <c r="Y3">
-        <v>-0.2844840810544221</v>
+        <v>-0.2844255879856792</v>
       </c>
       <c r="Z3">
         <v>0.739103251161129</v>
@@ -787,10 +787,10 @@
         <v>0.1062284149100869</v>
       </c>
       <c r="AB3">
-        <v>0.09287537190101647</v>
+        <v>0.09285753435714718</v>
       </c>
       <c r="AC3">
-        <v>0.01335304300907046</v>
+        <v>0.01337088055293975</v>
       </c>
       <c r="AD3">
         <v>1802.4</v>
@@ -833,6 +833,137 @@
       </c>
       <c r="AQ3">
         <v>3.853131749460044</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cintac S.A. (SNSE:CINTAC)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.00083</v>
+      </c>
+      <c r="G4">
+        <v>0.0448204214900564</v>
+      </c>
+      <c r="H4">
+        <v>0.0448204214900564</v>
+      </c>
+      <c r="I4">
+        <v>-0.01626595428910656</v>
+      </c>
+      <c r="J4">
+        <v>-0.01626595428910656</v>
+      </c>
+      <c r="K4">
+        <v>-49.3</v>
+      </c>
+      <c r="L4">
+        <v>-0.1463342238052835</v>
+      </c>
+      <c r="M4">
+        <v>1.14</v>
+      </c>
+      <c r="N4">
+        <v>0.01847649918962723</v>
+      </c>
+      <c r="O4">
+        <v>-0.0231237322515213</v>
+      </c>
+      <c r="P4">
+        <v>1.14</v>
+      </c>
+      <c r="Q4">
+        <v>0.01847649918962723</v>
+      </c>
+      <c r="R4">
+        <v>-0.0231237322515213</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>17.9</v>
+      </c>
+      <c r="V4">
+        <v>0.2901134521880064</v>
+      </c>
+      <c r="W4">
+        <v>-0.4084507042253521</v>
+      </c>
+      <c r="X4">
+        <v>0.2552505189496764</v>
+      </c>
+      <c r="Y4">
+        <v>-0.6637012231750284</v>
+      </c>
+      <c r="Z4">
+        <v>1.158926728586171</v>
+      </c>
+      <c r="AA4">
+        <v>-0.01885104919160646</v>
+      </c>
+      <c r="AB4">
+        <v>0.08633331242615377</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1051843616177602</v>
+      </c>
+      <c r="AD4">
+        <v>245.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>245.8</v>
+      </c>
+      <c r="AG4">
+        <v>227.9</v>
+      </c>
+      <c r="AH4">
+        <v>0.799349593495935</v>
+      </c>
+      <c r="AI4">
+        <v>0.7014840182648403</v>
+      </c>
+      <c r="AJ4">
+        <v>0.7869475138121547</v>
+      </c>
+      <c r="AK4">
+        <v>0.6854135338345865</v>
+      </c>
+      <c r="AL4">
+        <v>28.5</v>
+      </c>
+      <c r="AM4">
+        <v>27.23</v>
+      </c>
+      <c r="AN4">
+        <v>24.09803921568628</v>
+      </c>
+      <c r="AO4">
+        <v>-0.192280701754386</v>
+      </c>
+      <c r="AP4">
+        <v>22.34313725490196</v>
+      </c>
+      <c r="AQ4">
+        <v>-0.2012486228424532</v>
       </c>
     </row>
   </sheetData>
@@ -1127,49 +1258,49 @@
         <v>3.01606086221471</v>
       </c>
       <c r="F2">
-        <v>4.54141823625129</v>
+        <v>4.52988569141856</v>
       </c>
       <c r="G2">
         <v>2.47854785478548</v>
       </c>
       <c r="H2">
-        <v>2.46054455445545</v>
+        <v>2.56752475247525</v>
       </c>
       <c r="I2">
         <v>0.695048588616381</v>
       </c>
       <c r="J2">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="K2">
         <v>790.8</v>
       </c>
       <c r="L2">
-        <v>882.11462455301</v>
+        <v>891.614513337938</v>
       </c>
       <c r="M2">
         <v>2133.3</v>
       </c>
       <c r="N2">
-        <v>2211.52262455301</v>
+        <v>2298.81851333794</v>
       </c>
       <c r="O2">
         <v>1802.4</v>
       </c>
       <c r="P2">
-        <v>1789.308</v>
+        <v>1867.104</v>
       </c>
       <c r="Q2">
-        <v>0.0928753719010165</v>
+        <v>0.09285753435714721</v>
       </c>
       <c r="R2">
-        <v>0.09121029323484151</v>
+        <v>0.0894693185919825</v>
       </c>
       <c r="S2">
         <v>0.0508672072898587</v>
       </c>
       <c r="T2">
-        <v>0.0483852072898587</v>
+        <v>0.0464872072898587</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1182,16 +1313,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.188620839649058</v>
+        <v>0.188562346580315</v>
       </c>
       <c r="X2">
-        <v>0.186530645822061</v>
+        <v>0.199994747654587</v>
       </c>
       <c r="Y2">
         <v>2.61474251368371</v>
       </c>
       <c r="Z2">
-        <v>2.57647555856206</v>
+        <v>2.82413095425242</v>
       </c>
       <c r="AA2">
         <v>1802.4</v>
@@ -1224,7 +1355,7 @@
         <v>790.8</v>
       </c>
       <c r="AK2">
-        <v>0.05462137816692637</v>
+        <v>0.05459900767788712</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1412,13 +1543,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09941496891340668</v>
+        <v>0.0993930106048713</v>
       </c>
       <c r="C2">
-        <v>2332.994266614905</v>
+        <v>2333.051683607365</v>
       </c>
       <c r="D2">
-        <v>1873.094266614905</v>
+        <v>1873.151683607365</v>
       </c>
       <c r="E2">
         <v>-1802.4</v>
@@ -1463,19 +1594,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09941496891340668</v>
+        <v>0.0993930106048713</v>
       </c>
       <c r="T2">
         <v>0.9815748103161358</v>
       </c>
       <c r="U2">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V2">
         <v>0.27</v>
       </c>
       <c r="W2">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1494,13 +1625,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09925080057023906</v>
+        <v>0.09921868154913673</v>
       </c>
       <c r="C3">
-        <v>2312.815272726438</v>
+        <v>2313.232615540187</v>
       </c>
       <c r="D3">
-        <v>1878.847272726438</v>
+        <v>1879.264615540186</v>
       </c>
       <c r="E3">
         <v>-1776.468</v>
@@ -1527,37 +1658,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M3">
-        <v>1.558023237589883</v>
+        <v>1.521718437589883</v>
       </c>
       <c r="N3">
-        <v>537.0419767624101</v>
+        <v>537.07828156241</v>
       </c>
       <c r="O3">
-        <v>145.0013337258507</v>
+        <v>145.0111360218507</v>
       </c>
       <c r="P3">
-        <v>392.0406430365593</v>
+        <v>392.0671455405593</v>
       </c>
       <c r="Q3">
-        <v>762.4406430365593</v>
+        <v>762.4671455405594</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09981031161347523</v>
+        <v>0.09978819139013953</v>
       </c>
       <c r="T3">
         <v>0.9888126851800831</v>
       </c>
       <c r="U3">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V3">
         <v>0.27</v>
       </c>
       <c r="W3">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1565,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>345.6944588536201</v>
+        <v>353.9419558147966</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1576,13 +1707,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09908663222707145</v>
+        <v>0.09904435249340217</v>
       </c>
       <c r="C4">
-        <v>2292.671727183723</v>
+        <v>2293.453576569115</v>
       </c>
       <c r="D4">
-        <v>1884.635727183723</v>
+        <v>1885.417576569115</v>
       </c>
       <c r="E4">
         <v>-1750.536</v>
@@ -1609,37 +1740,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M4">
-        <v>3.116046475179767</v>
+        <v>3.043436875179767</v>
       </c>
       <c r="N4">
-        <v>535.4839535248201</v>
+        <v>535.5565631248202</v>
       </c>
       <c r="O4">
-        <v>144.5806674517014</v>
+        <v>144.6002720437015</v>
       </c>
       <c r="P4">
-        <v>390.9032860731187</v>
+        <v>390.9562910811187</v>
       </c>
       <c r="Q4">
-        <v>761.3032860731187</v>
+        <v>761.3562910811188</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1002137225319125</v>
+        <v>0.1001914370893928</v>
       </c>
       <c r="T4">
         <v>0.9961982717759477</v>
       </c>
       <c r="U4">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V4">
         <v>0.27</v>
       </c>
       <c r="W4">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1647,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>172.8472294268101</v>
+        <v>176.9709779073983</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1658,13 +1789,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09892246388390384</v>
+        <v>0.0988700234376676</v>
       </c>
       <c r="C5">
-        <v>2272.563958632822</v>
+        <v>2273.714961167385</v>
       </c>
       <c r="D5">
-        <v>1890.459958632822</v>
+        <v>1891.610961167385</v>
       </c>
       <c r="E5">
         <v>-1724.604</v>
@@ -1691,37 +1822,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M5">
-        <v>4.67406971276965</v>
+        <v>4.565155312769649</v>
       </c>
       <c r="N5">
-        <v>533.9259302872302</v>
+        <v>534.0348446872302</v>
       </c>
       <c r="O5">
-        <v>144.1600011775522</v>
+        <v>144.1894080655522</v>
       </c>
       <c r="P5">
-        <v>389.765929109678</v>
+        <v>389.8454366216781</v>
       </c>
       <c r="Q5">
-        <v>760.165929109678</v>
+        <v>760.2454366216781</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1006254512012454</v>
+        <v>0.1006029971329607</v>
       </c>
       <c r="T5">
         <v>1.003736138507809</v>
       </c>
       <c r="U5">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V5">
         <v>0.27</v>
       </c>
       <c r="W5">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1729,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>115.23148628454</v>
+        <v>117.9806519382656</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1740,13 +1871,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09875829554073624</v>
+        <v>0.09869569438193301</v>
       </c>
       <c r="C6">
-        <v>2252.492299794948</v>
+        <v>2254.017169008508</v>
       </c>
       <c r="D6">
-        <v>1896.320299794948</v>
+        <v>1897.845169008508</v>
       </c>
       <c r="E6">
         <v>-1698.672</v>
@@ -1773,37 +1904,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M6">
-        <v>6.232092950359533</v>
+        <v>6.086873750359533</v>
       </c>
       <c r="N6">
-        <v>532.3679070496404</v>
+        <v>532.5131262496403</v>
       </c>
       <c r="O6">
-        <v>143.7393349034029</v>
+        <v>143.7785440874029</v>
       </c>
       <c r="P6">
-        <v>388.6285721462375</v>
+        <v>388.7345821622374</v>
       </c>
       <c r="Q6">
-        <v>759.0285721462376</v>
+        <v>759.1345821622374</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1010457575511895</v>
+        <v>0.1010231313441028</v>
       </c>
       <c r="T6">
         <v>1.011431044129918</v>
       </c>
       <c r="U6">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V6">
         <v>0.27</v>
       </c>
       <c r="W6">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1811,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>86.42361471340503</v>
+        <v>88.48548895369916</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1822,13 +1953,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09859412719756862</v>
+        <v>0.09852136532619847</v>
       </c>
       <c r="C7">
-        <v>2232.457087529831</v>
+        <v>2234.360605052256</v>
       </c>
       <c r="D7">
-        <v>1902.217087529831</v>
+        <v>1904.120605052256</v>
       </c>
       <c r="E7">
         <v>-1672.74</v>
@@ -1855,37 +1986,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M7">
-        <v>7.790116187949416</v>
+        <v>7.608592187949417</v>
       </c>
       <c r="N7">
-        <v>530.8098838120505</v>
+        <v>530.9914078120505</v>
       </c>
       <c r="O7">
-        <v>143.3186686292537</v>
+        <v>143.3676801092537</v>
       </c>
       <c r="P7">
-        <v>387.4912151827969</v>
+        <v>387.6237277027968</v>
       </c>
       <c r="Q7">
-        <v>757.8912151827969</v>
+        <v>758.0237277027968</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1014749124558691</v>
+        <v>0.1014521104860058</v>
       </c>
       <c r="T7">
         <v>1.019287947765124</v>
       </c>
       <c r="U7">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V7">
         <v>0.27</v>
       </c>
       <c r="W7">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1893,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>69.13889177072403</v>
+        <v>70.78839116295934</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1904,13 +2035,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09842995885440101</v>
+        <v>0.0983470362704639</v>
       </c>
       <c r="C8">
-        <v>2212.458662900255</v>
+        <v>2214.745679632351</v>
       </c>
       <c r="D8">
-        <v>1908.150662900255</v>
+        <v>1910.437679632352</v>
       </c>
       <c r="E8">
         <v>-1646.808</v>
@@ -1937,37 +2068,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M8">
-        <v>9.3481394255393</v>
+        <v>9.130310625539298</v>
       </c>
       <c r="N8">
-        <v>529.2518605744606</v>
+        <v>529.4696893744606</v>
       </c>
       <c r="O8">
-        <v>142.8980023551044</v>
+        <v>142.9568161311044</v>
       </c>
       <c r="P8">
-        <v>386.3538582193562</v>
+        <v>386.5128732433562</v>
       </c>
       <c r="Q8">
-        <v>756.7538582193563</v>
+        <v>756.9128732433562</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1019131983159675</v>
+        <v>0.101890216843694</v>
       </c>
       <c r="T8">
         <v>1.027312019562781</v>
       </c>
       <c r="U8">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V8">
         <v>0.27</v>
       </c>
       <c r="W8">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1975,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>57.61574314227002</v>
+        <v>58.99032596913278</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1986,13 +2117,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09826579051123339</v>
+        <v>0.09817270721472933</v>
       </c>
       <c r="C9">
-        <v>2192.497371237823</v>
+        <v>2195.172808545901</v>
       </c>
       <c r="D9">
-        <v>1914.121371237823</v>
+        <v>1916.796808545901</v>
       </c>
       <c r="E9">
         <v>-1620.876</v>
@@ -2019,37 +2150,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M9">
-        <v>10.90616266312918</v>
+        <v>10.65202906312918</v>
       </c>
       <c r="N9">
-        <v>527.6938373368707</v>
+        <v>527.9479709368708</v>
       </c>
       <c r="O9">
-        <v>142.4773360809551</v>
+        <v>142.5459521529551</v>
       </c>
       <c r="P9">
-        <v>385.2165012559157</v>
+        <v>385.4020187839157</v>
       </c>
       <c r="Q9">
-        <v>755.6165012559156</v>
+        <v>755.8020187839156</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1023609096784336</v>
+        <v>0.102337744843483</v>
       </c>
       <c r="T9">
         <v>1.035508652044259</v>
       </c>
       <c r="U9">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V9">
         <v>0.27</v>
       </c>
       <c r="W9">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2057,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>49.3849226933743</v>
+        <v>50.56313654497095</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2068,13 +2199,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.0981016221680658</v>
+        <v>0.09799837815899476</v>
       </c>
       <c r="C10">
-        <v>2172.57356220995</v>
+        <v>2175.64241314463</v>
       </c>
       <c r="D10">
-        <v>1920.12956220995</v>
+        <v>1923.19841314463</v>
       </c>
       <c r="E10">
         <v>-1594.944</v>
@@ -2101,37 +2232,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M10">
-        <v>12.46418590071907</v>
+        <v>12.17374750071907</v>
       </c>
       <c r="N10">
-        <v>526.1358140992809</v>
+        <v>526.4262524992808</v>
       </c>
       <c r="O10">
-        <v>142.0566698068058</v>
+        <v>142.1350881748058</v>
       </c>
       <c r="P10">
-        <v>384.079144292475</v>
+        <v>384.291164324475</v>
       </c>
       <c r="Q10">
-        <v>754.479144292475</v>
+        <v>754.691164324475</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1028183538966055</v>
+        <v>0.1027950017128327</v>
       </c>
       <c r="T10">
         <v>1.043883472188377</v>
       </c>
       <c r="U10">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V10">
         <v>0.27</v>
       </c>
       <c r="W10">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2139,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>43.21180735670251</v>
+        <v>44.24274447684958</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2150,13 +2281,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09793745382489819</v>
+        <v>0.0978240491032602</v>
       </c>
       <c r="C11">
-        <v>2152.68758988813</v>
+        <v>2156.154920427949</v>
       </c>
       <c r="D11">
-        <v>1926.17558988813</v>
+        <v>1929.642920427949</v>
       </c>
       <c r="E11">
         <v>-1569.012</v>
@@ -2183,37 +2314,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M11">
-        <v>14.02220913830895</v>
+        <v>13.69546593830895</v>
       </c>
       <c r="N11">
-        <v>524.5777908616909</v>
+        <v>524.9045340616909</v>
       </c>
       <c r="O11">
-        <v>141.6360035326566</v>
+        <v>141.7242241966566</v>
       </c>
       <c r="P11">
-        <v>382.9417873290344</v>
+        <v>383.1803098650344</v>
       </c>
       <c r="Q11">
-        <v>753.3417873290343</v>
+        <v>753.5803098650345</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1032858518338581</v>
+        <v>0.1032623081837065</v>
       </c>
       <c r="T11">
         <v>1.052442354313685</v>
       </c>
       <c r="U11">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V11">
         <v>0.27</v>
       </c>
       <c r="W11">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2221,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>38.41049542818001</v>
+        <v>39.32688397942185</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2232,13 +2363,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09777328548173056</v>
+        <v>0.09764972004752563</v>
       </c>
       <c r="C12">
-        <v>2132.839812817485</v>
+        <v>2136.710763137896</v>
       </c>
       <c r="D12">
-        <v>1932.259812817485</v>
+        <v>1936.130763137896</v>
       </c>
       <c r="E12">
         <v>-1543.08</v>
@@ -2265,37 +2396,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M12">
-        <v>15.58023237589883</v>
+        <v>15.21718437589883</v>
       </c>
       <c r="N12">
-        <v>523.0197676241011</v>
+        <v>523.3828156241011</v>
       </c>
       <c r="O12">
-        <v>141.2153372585073</v>
+        <v>141.3133602185073</v>
       </c>
       <c r="P12">
-        <v>381.8044303655938</v>
+        <v>382.0694554055938</v>
       </c>
       <c r="Q12">
-        <v>752.2044303655938</v>
+        <v>752.4694554055939</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1037637386141608</v>
+        <v>0.103739999242822</v>
       </c>
       <c r="T12">
         <v>1.061191433819556</v>
       </c>
       <c r="U12">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V12">
         <v>0.27</v>
       </c>
       <c r="W12">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2303,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.56944588536201</v>
+        <v>35.39419558147967</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2314,13 +2445,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09760911713856295</v>
+        <v>0.09747539099179107</v>
       </c>
       <c r="C13">
-        <v>2113.030594087647</v>
+        <v>2117.310379855998</v>
       </c>
       <c r="D13">
-        <v>1938.382594087647</v>
+        <v>1942.662379855998</v>
       </c>
       <c r="E13">
         <v>-1517.148</v>
@@ -2347,37 +2478,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M13">
-        <v>17.13825561348872</v>
+        <v>16.73890281348872</v>
       </c>
       <c r="N13">
-        <v>521.4617443865112</v>
+        <v>521.8610971865112</v>
       </c>
       <c r="O13">
-        <v>140.794670984358</v>
+        <v>140.902496240358</v>
       </c>
       <c r="P13">
-        <v>380.6670734021532</v>
+        <v>380.9586009461532</v>
       </c>
       <c r="Q13">
-        <v>751.0670734021533</v>
+        <v>751.3586009461533</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1042523644232343</v>
+        <v>0.1042284249324794</v>
       </c>
       <c r="T13">
         <v>1.070137121853648</v>
       </c>
       <c r="U13">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V13">
         <v>0.27</v>
       </c>
       <c r="W13">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2385,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>31.42676898669274</v>
+        <v>32.17654143770879</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2396,13 +2527,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09744494879539535</v>
+        <v>0.09730106193605649</v>
       </c>
       <c r="C14">
-        <v>2093.260301404987</v>
+        <v>2097.954215102111</v>
       </c>
       <c r="D14">
-        <v>1944.544301404988</v>
+        <v>1949.238215102112</v>
       </c>
       <c r="E14">
         <v>-1491.216</v>
@@ -2429,37 +2560,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M14">
-        <v>18.6962788510786</v>
+        <v>18.2606212510786</v>
       </c>
       <c r="N14">
-        <v>519.9037211489214</v>
+        <v>520.3393787489213</v>
       </c>
       <c r="O14">
-        <v>140.3740047102088</v>
+        <v>140.4916322622088</v>
       </c>
       <c r="P14">
-        <v>379.5297164387126</v>
+        <v>379.8477464867125</v>
       </c>
       <c r="Q14">
-        <v>749.9297164387126</v>
+        <v>750.2477464867125</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1047520953643322</v>
+        <v>0.1047279512059926</v>
       </c>
       <c r="T14">
         <v>1.079286120979424</v>
       </c>
       <c r="U14">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V14">
         <v>0.27</v>
       </c>
       <c r="W14">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2467,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.80787157113501</v>
+        <v>29.49516298456639</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2478,13 +2609,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.09728078045222774</v>
+        <v>0.09712673288032193</v>
       </c>
       <c r="C15">
-        <v>2073.529307166233</v>
+        <v>2078.642719435259</v>
       </c>
       <c r="D15">
-        <v>1950.745307166233</v>
+        <v>1955.858719435259</v>
       </c>
       <c r="E15">
         <v>-1465.284</v>
@@ -2511,37 +2642,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M15">
-        <v>20.25430208866848</v>
+        <v>19.78233968866848</v>
       </c>
       <c r="N15">
-        <v>518.3456979113314</v>
+        <v>518.8176603113315</v>
       </c>
       <c r="O15">
-        <v>139.9533384360595</v>
+        <v>140.0807682840595</v>
       </c>
       <c r="P15">
-        <v>378.3923594752719</v>
+        <v>378.7368920272719</v>
       </c>
       <c r="Q15">
-        <v>748.792359475272</v>
+        <v>749.136892027272</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1052633143730415</v>
+        <v>0.1052389608421153</v>
       </c>
       <c r="T15">
         <v>1.088645441924183</v>
       </c>
       <c r="U15">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V15">
         <v>0.27</v>
       </c>
       <c r="W15">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.59188145027847</v>
+        <v>27.2263042934459</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2560,13 +2691,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09711661210906011</v>
+        <v>0.09695240382458736</v>
       </c>
       <c r="C16">
-        <v>2053.837988533485</v>
+        <v>2059.376349556545</v>
       </c>
       <c r="D16">
-        <v>1956.985988533485</v>
+        <v>1962.524349556545</v>
       </c>
       <c r="E16">
         <v>-1439.352</v>
@@ -2593,37 +2724,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M16">
-        <v>21.81232532625837</v>
+        <v>21.30405812625837</v>
       </c>
       <c r="N16">
-        <v>516.7876746737415</v>
+        <v>517.2959418737415</v>
       </c>
       <c r="O16">
-        <v>139.5326721619102</v>
+        <v>139.6699043059102</v>
       </c>
       <c r="P16">
-        <v>377.2550025118313</v>
+        <v>377.6260375678313</v>
       </c>
       <c r="Q16">
-        <v>747.6550025118313</v>
+        <v>748.0260375678313</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1057864221959069</v>
+        <v>0.1057618544232641</v>
       </c>
       <c r="T16">
         <v>1.098222421495565</v>
       </c>
       <c r="U16">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2631,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.69246134668715</v>
+        <v>25.28156827248547</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2642,13 +2773,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09695244376589252</v>
+        <v>0.09677807476885281</v>
       </c>
       <c r="C17">
-        <v>2034.18672751069</v>
+        <v>2040.155568414173</v>
       </c>
       <c r="D17">
-        <v>1963.26672751069</v>
+        <v>1969.235568414173</v>
       </c>
       <c r="E17">
         <v>-1413.42</v>
@@ -2675,37 +2806,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M17">
-        <v>23.37034856384825</v>
+        <v>22.82577656384825</v>
       </c>
       <c r="N17">
-        <v>515.2296514361517</v>
+        <v>515.7742234361517</v>
       </c>
       <c r="O17">
-        <v>139.112005887761</v>
+        <v>139.259040327761</v>
       </c>
       <c r="P17">
-        <v>376.1176455483907</v>
+        <v>376.5151831083907</v>
       </c>
       <c r="Q17">
-        <v>746.5176455483908</v>
+        <v>746.9151831083907</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1063218384381338</v>
+        <v>0.106297051382793</v>
       </c>
       <c r="T17">
         <v>1.108024741762744</v>
       </c>
       <c r="U17">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.04629725690801</v>
+        <v>23.59613038765312</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2724,13 +2855,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09678827542272488</v>
+        <v>0.09660374571311822</v>
       </c>
       <c r="C18">
-        <v>2014.575911021595</v>
+        <v>2020.980845310627</v>
       </c>
       <c r="D18">
-        <v>1969.587911021595</v>
+        <v>1975.992845310627</v>
       </c>
       <c r="E18">
         <v>-1387.488</v>
@@ -2757,37 +2888,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M18">
-        <v>24.92837180143813</v>
+        <v>24.34749500143813</v>
       </c>
       <c r="N18">
-        <v>513.6716281985617</v>
+        <v>514.2525049985618</v>
       </c>
       <c r="O18">
-        <v>138.6913396136117</v>
+        <v>138.8481763496117</v>
       </c>
       <c r="P18">
-        <v>374.98028858495</v>
+        <v>375.4043286489501</v>
       </c>
       <c r="Q18">
-        <v>745.38028858495</v>
+        <v>745.8043286489501</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.106870002686128</v>
+        <v>0.1068449911270724</v>
       </c>
       <c r="T18">
         <v>1.118060450607713</v>
       </c>
       <c r="U18">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V18">
         <v>0.27</v>
       </c>
       <c r="W18">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.60590367835126</v>
+        <v>22.12137223842479</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2806,13 +2937,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09662410707955728</v>
+        <v>0.09642941665738367</v>
       </c>
       <c r="C19">
-        <v>1995.00593098919</v>
+        <v>2001.852656012069</v>
       </c>
       <c r="D19">
-        <v>1975.94993098919</v>
+        <v>1982.796656012069</v>
       </c>
       <c r="E19">
         <v>-1361.556</v>
@@ -2839,37 +2970,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M19">
-        <v>26.48639503902801</v>
+        <v>25.86921343902802</v>
       </c>
       <c r="N19">
-        <v>512.1136049609719</v>
+        <v>512.7307865609719</v>
       </c>
       <c r="O19">
-        <v>138.2706733394624</v>
+        <v>138.4373123714624</v>
       </c>
       <c r="P19">
-        <v>373.8429316215095</v>
+        <v>374.2934741895094</v>
       </c>
       <c r="Q19">
-        <v>744.2429316215096</v>
+        <v>744.6934741895095</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1074313757111823</v>
+        <v>0.107406134238684</v>
       </c>
       <c r="T19">
         <v>1.128337983762199</v>
       </c>
       <c r="U19">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2877,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.33496816786001</v>
+        <v>20.82011504792921</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2888,13 +3019,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09645993873638967</v>
+        <v>0.09625508760164909</v>
       </c>
       <c r="C20">
-        <v>1975.477184416729</v>
+        <v>1982.771482860003</v>
       </c>
       <c r="D20">
-        <v>1982.353184416728</v>
+        <v>1989.647482860003</v>
       </c>
       <c r="E20">
         <v>-1335.624</v>
@@ -2921,37 +3052,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M20">
-        <v>28.0444182766179</v>
+        <v>27.3909318766179</v>
       </c>
       <c r="N20">
-        <v>510.555581723382</v>
+        <v>511.209068123382</v>
       </c>
       <c r="O20">
-        <v>137.8500070653132</v>
+        <v>138.0264483933132</v>
       </c>
       <c r="P20">
-        <v>372.7055746580689</v>
+        <v>373.1826197300688</v>
       </c>
       <c r="Q20">
-        <v>743.1055746580689</v>
+        <v>743.5826197300689</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1080064407612379</v>
+        <v>0.1079809637676519</v>
       </c>
       <c r="T20">
         <v>1.138866188457038</v>
       </c>
       <c r="U20">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.20524771409001</v>
+        <v>19.66344198971093</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2970,13 +3101,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09629577039322208</v>
+        <v>0.09608075854591455</v>
       </c>
       <c r="C21">
-        <v>1955.990073470295</v>
+        <v>1963.737814885262</v>
       </c>
       <c r="D21">
-        <v>1988.798073470295</v>
+        <v>1996.545814885262</v>
       </c>
       <c r="E21">
         <v>-1309.692</v>
@@ -3003,37 +3134,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M21">
-        <v>29.60244151420778</v>
+        <v>28.91265031420778</v>
       </c>
       <c r="N21">
-        <v>508.9975584857921</v>
+        <v>509.6873496857921</v>
       </c>
       <c r="O21">
-        <v>137.4293407911639</v>
+        <v>137.6155844151639</v>
       </c>
       <c r="P21">
-        <v>371.5682176946282</v>
+        <v>372.0717652706282</v>
       </c>
       <c r="Q21">
-        <v>741.9682176946283</v>
+        <v>742.4717652706283</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.108595704948332</v>
+        <v>0.1085699866183227</v>
       </c>
       <c r="T21">
         <v>1.149654348823356</v>
       </c>
       <c r="U21">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V21">
         <v>0.27</v>
       </c>
       <c r="W21">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.19444520282211</v>
+        <v>18.62852399025246</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3052,13 +3183,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09613160205005446</v>
+        <v>0.09590642949018</v>
       </c>
       <c r="C22">
-        <v>1936.545005563016</v>
+        <v>1944.752147924377</v>
       </c>
       <c r="D22">
-        <v>1995.285005563016</v>
+        <v>2003.492147924377</v>
       </c>
       <c r="E22">
         <v>-1283.76</v>
@@ -3085,37 +3216,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M22">
-        <v>31.16046475179767</v>
+        <v>30.43436875179767</v>
       </c>
       <c r="N22">
-        <v>507.4395352482022</v>
+        <v>508.1656312482023</v>
       </c>
       <c r="O22">
-        <v>137.0086745170146</v>
+        <v>137.2047204370146</v>
       </c>
       <c r="P22">
-        <v>370.4308607311876</v>
+        <v>370.9609108111877</v>
       </c>
       <c r="Q22">
-        <v>740.8308607311876</v>
+        <v>741.3609108111878</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1091997007401034</v>
+        <v>0.1091737350402603</v>
       </c>
       <c r="T22">
         <v>1.160712213198831</v>
       </c>
       <c r="U22">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.284722942681</v>
+        <v>17.69709779073983</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3134,13 +3265,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09596743370688685</v>
+        <v>0.09573210043444541</v>
       </c>
       <c r="C23">
-        <v>1917.142393440903</v>
+        <v>1925.814984738379</v>
       </c>
       <c r="D23">
-        <v>2001.814393440903</v>
+        <v>2010.486984738379</v>
       </c>
       <c r="E23">
         <v>-1257.828</v>
@@ -3167,37 +3298,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M23">
-        <v>32.71848798938754</v>
+        <v>31.95608718938754</v>
       </c>
       <c r="N23">
-        <v>505.8815120106124</v>
+        <v>506.6439128106124</v>
       </c>
       <c r="O23">
-        <v>136.5880082428654</v>
+        <v>136.7938564588653</v>
       </c>
       <c r="P23">
-        <v>369.293503767747</v>
+        <v>369.8500563517471</v>
       </c>
       <c r="Q23">
-        <v>739.693503767747</v>
+        <v>740.2500563517472</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1098189875645779</v>
+        <v>0.1097927682323735</v>
       </c>
       <c r="T23">
         <v>1.172050023507862</v>
       </c>
       <c r="U23">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.46164089779144</v>
+        <v>16.85437884832366</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3216,13 +3347,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09580326536371923</v>
+        <v>0.09555777137871085</v>
       </c>
       <c r="C24">
-        <v>1897.782655270402</v>
+        <v>1906.926835134099</v>
       </c>
       <c r="D24">
-        <v>2008.386655270402</v>
+        <v>2017.530835134099</v>
       </c>
       <c r="E24">
         <v>-1231.896</v>
@@ -3249,37 +3380,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M24">
-        <v>34.27651122697743</v>
+        <v>33.47780562697744</v>
       </c>
       <c r="N24">
-        <v>504.3234887730225</v>
+        <v>505.1221943730225</v>
       </c>
       <c r="O24">
-        <v>136.1673419687161</v>
+        <v>136.3829924807161</v>
       </c>
       <c r="P24">
-        <v>368.1561468043064</v>
+        <v>368.7392018923064</v>
       </c>
       <c r="Q24">
-        <v>738.5561468043064</v>
+        <v>739.1392018923063</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1104541535383979</v>
+        <v>0.1104276740704384</v>
       </c>
       <c r="T24">
         <v>1.18367854690174</v>
       </c>
       <c r="U24">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V24">
         <v>0.27</v>
       </c>
       <c r="W24">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.71338449334637</v>
+        <v>16.08827071885439</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3298,13 +3429,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09563909702055161</v>
+        <v>0.0953834423229763</v>
       </c>
       <c r="C25">
-        <v>1878.466214727664</v>
+        <v>1888.088216088032</v>
       </c>
       <c r="D25">
-        <v>2015.002214727664</v>
+        <v>2024.624216088032</v>
       </c>
       <c r="E25">
         <v>-1205.964</v>
@@ -3331,37 +3462,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M25">
-        <v>35.83453446456732</v>
+        <v>34.99952406456732</v>
       </c>
       <c r="N25">
-        <v>502.7654655354326</v>
+        <v>503.6004759354326</v>
       </c>
       <c r="O25">
-        <v>135.7466756945668</v>
+        <v>135.9721285025668</v>
       </c>
       <c r="P25">
-        <v>367.0187898408658</v>
+        <v>367.6283474328658</v>
       </c>
       <c r="Q25">
-        <v>737.4187898408659</v>
+        <v>738.0283474328658</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1111058173297196</v>
+        <v>0.1110790709692322</v>
       </c>
       <c r="T25">
         <v>1.195609109864291</v>
       </c>
       <c r="U25">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V25">
         <v>0.27</v>
       </c>
       <c r="W25">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.03019386320087</v>
+        <v>15.38878068759985</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3380,13 +3511,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09547492867738401</v>
+        <v>0.09520911326724173</v>
       </c>
       <c r="C26">
-        <v>1859.193501089589</v>
+        <v>1869.299651872823</v>
       </c>
       <c r="D26">
-        <v>2021.661501089589</v>
+        <v>2031.767651872823</v>
       </c>
       <c r="E26">
         <v>-1180.032</v>
@@ -3413,37 +3544,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M26">
-        <v>37.3925577021572</v>
+        <v>36.52124250215719</v>
       </c>
       <c r="N26">
-        <v>501.2074422978427</v>
+        <v>502.0787574978427</v>
       </c>
       <c r="O26">
-        <v>135.3260094204175</v>
+        <v>135.5612645244175</v>
       </c>
       <c r="P26">
-        <v>365.8814328774251</v>
+        <v>366.5174929734252</v>
       </c>
       <c r="Q26">
-        <v>736.2814328774252</v>
+        <v>736.9174929734252</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1117746301681815</v>
+        <v>0.1117476098916785</v>
       </c>
       <c r="T26">
         <v>1.207853635010066</v>
       </c>
       <c r="U26">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V26">
         <v>0.27</v>
       </c>
       <c r="W26">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.4039357855675</v>
+        <v>14.7475814922832</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3462,13 +3593,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09531076033421639</v>
+        <v>0.09503478421150714</v>
       </c>
       <c r="C27">
-        <v>1839.964949326684</v>
+        <v>1850.561674186427</v>
       </c>
       <c r="D27">
-        <v>2028.364949326684</v>
+        <v>2038.961674186427</v>
       </c>
       <c r="E27">
         <v>-1154.1</v>
@@ -3495,37 +3626,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M27">
-        <v>38.95058093974708</v>
+        <v>38.04296093974708</v>
       </c>
       <c r="N27">
-        <v>499.6494190602529</v>
+        <v>500.5570390602528</v>
       </c>
       <c r="O27">
-        <v>134.9053431462683</v>
+        <v>135.1504005462683</v>
       </c>
       <c r="P27">
-        <v>364.7440759139846</v>
+        <v>365.4066385139845</v>
       </c>
       <c r="Q27">
-        <v>735.1440759139846</v>
+        <v>735.8066385139846</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.112461278015669</v>
+        <v>0.1124339765187233</v>
       </c>
       <c r="T27">
         <v>1.220424680826396</v>
       </c>
       <c r="U27">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V27">
         <v>0.27</v>
       </c>
       <c r="W27">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.82777835414481</v>
+        <v>14.15767823259187</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3544,13 +3675,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09514659199104879</v>
+        <v>0.09486045515577257</v>
       </c>
       <c r="C28">
-        <v>1820.781000197767</v>
+        <v>1831.87482228404</v>
       </c>
       <c r="D28">
-        <v>2035.113000197767</v>
+        <v>2046.206822284041</v>
       </c>
       <c r="E28">
         <v>-1128.168</v>
@@ -3577,37 +3708,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M28">
-        <v>40.50860417733696</v>
+        <v>39.56467937733697</v>
       </c>
       <c r="N28">
-        <v>498.0913958226629</v>
+        <v>499.0353206226629</v>
       </c>
       <c r="O28">
-        <v>134.484676872119</v>
+        <v>134.739536568119</v>
       </c>
       <c r="P28">
-        <v>363.606718950544</v>
+        <v>364.2957840545439</v>
       </c>
       <c r="Q28">
-        <v>734.0067189505439</v>
+        <v>734.695784054544</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1131664839130886</v>
+        <v>0.1131388935951477</v>
       </c>
       <c r="T28">
         <v>1.233335484637761</v>
       </c>
       <c r="U28">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V28">
         <v>0.27</v>
       </c>
       <c r="W28">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.29594072513924</v>
+        <v>13.61315214672295</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3626,13 +3757,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09498242364788118</v>
+        <v>0.094686126100038</v>
       </c>
       <c r="C29">
-        <v>1801.642100346579</v>
+        <v>1813.239643112847</v>
       </c>
       <c r="D29">
-        <v>2041.906100346579</v>
+        <v>2053.503643112847</v>
       </c>
       <c r="E29">
         <v>-1102.236</v>
@@ -3659,37 +3790,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M29">
-        <v>42.06662741492685</v>
+        <v>41.08639781492685</v>
       </c>
       <c r="N29">
-        <v>496.533372585073</v>
+        <v>497.5136021850731</v>
       </c>
       <c r="O29">
-        <v>134.0640105979697</v>
+        <v>134.3286725899697</v>
       </c>
       <c r="P29">
-        <v>362.4693619871033</v>
+        <v>363.1849295951033</v>
       </c>
       <c r="Q29">
-        <v>732.8693619871033</v>
+        <v>733.5849295951034</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1138910105200265</v>
+        <v>0.1138631234681865</v>
       </c>
       <c r="T29">
         <v>1.246600009101492</v>
       </c>
       <c r="U29">
-        <v>0.06008110587651871</v>
+        <v>0.05868110587651872</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.04385920728985866</v>
+        <v>0.04283720728985866</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.80349847606</v>
+        <v>13.10896132647395</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3708,13 +3839,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09504309530471355</v>
+        <v>0.09481839704430345</v>
       </c>
       <c r="C30">
-        <v>1773.194299391388</v>
+        <v>1781.766481379598</v>
       </c>
       <c r="D30">
-        <v>2039.390299391388</v>
+        <v>2047.962481379598</v>
       </c>
       <c r="E30">
         <v>-1076.304</v>
@@ -3741,37 +3872,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M30">
-        <v>44.42335625251673</v>
+        <v>43.69726025251673</v>
       </c>
       <c r="N30">
-        <v>494.1766437474832</v>
+        <v>494.9027397474832</v>
       </c>
       <c r="O30">
-        <v>133.4276938118205</v>
+        <v>133.6237397318205</v>
       </c>
       <c r="P30">
-        <v>360.7489499356627</v>
+        <v>361.2790000156627</v>
       </c>
       <c r="Q30">
-        <v>731.1489499356628</v>
+        <v>731.6790000156627</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.114635662866046</v>
+        <v>0.1146074708376986</v>
       </c>
       <c r="T30">
         <v>1.260232992578106</v>
       </c>
       <c r="U30">
-        <v>0.06118110587651871</v>
+        <v>0.06018110587651871</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.04466220728985866</v>
+        <v>0.04393220728985866</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.12425276781032</v>
+        <v>12.32571554572416</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3790,13 +3921,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09488695696154592</v>
+        <v>0.09465501798856887</v>
       </c>
       <c r="C31">
-        <v>1753.749298018509</v>
+        <v>1762.683198055252</v>
       </c>
       <c r="D31">
-        <v>2045.877298018509</v>
+        <v>2054.811198055251</v>
       </c>
       <c r="E31">
         <v>-1050.372</v>
@@ -3823,37 +3954,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M31">
-        <v>46.00990469010661</v>
+        <v>45.25787669010661</v>
       </c>
       <c r="N31">
-        <v>492.5900953098933</v>
+        <v>493.3421233098933</v>
       </c>
       <c r="O31">
-        <v>132.9993257336712</v>
+        <v>133.2023732936712</v>
       </c>
       <c r="P31">
-        <v>359.5907695762221</v>
+        <v>360.1397500162221</v>
       </c>
       <c r="Q31">
-        <v>729.9907695762222</v>
+        <v>730.5397500162221</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1154012913344886</v>
+        <v>0.1153727857387463</v>
       </c>
       <c r="T31">
         <v>1.274250003758285</v>
       </c>
       <c r="U31">
-        <v>0.06118110587651871</v>
+        <v>0.06018110587651871</v>
       </c>
       <c r="V31">
         <v>0.27</v>
       </c>
       <c r="W31">
-        <v>0.04466220728985866</v>
+        <v>0.04393220728985866</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.70617508616169</v>
+        <v>11.90069087173367</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3872,13 +4003,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09473081861837833</v>
+        <v>0.09449163893283433</v>
       </c>
       <c r="C32">
-        <v>1734.345696697636</v>
+        <v>1743.64587485416</v>
       </c>
       <c r="D32">
-        <v>2052.405696697635</v>
+        <v>2061.70587485416</v>
       </c>
       <c r="E32">
         <v>-1024.44</v>
@@ -3905,37 +4036,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M32">
-        <v>47.59645312769649</v>
+        <v>46.81849312769649</v>
       </c>
       <c r="N32">
-        <v>491.0035468723034</v>
+        <v>491.7815068723034</v>
       </c>
       <c r="O32">
-        <v>132.5709576555219</v>
+        <v>132.7810068555219</v>
       </c>
       <c r="P32">
-        <v>358.4325892167815</v>
+        <v>359.0005000167815</v>
       </c>
       <c r="Q32">
-        <v>728.8325892167816</v>
+        <v>729.4005000167815</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1161887949020296</v>
+        <v>0.1161599667798239</v>
       </c>
       <c r="T32">
         <v>1.288667500972184</v>
       </c>
       <c r="U32">
-        <v>0.06118110587651871</v>
+        <v>0.06018110587651871</v>
       </c>
       <c r="V32">
         <v>0.27</v>
       </c>
       <c r="W32">
-        <v>0.04466220728985866</v>
+        <v>0.04393220728985866</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.3159692499563</v>
+        <v>11.50400117600922</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3954,13 +4085,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09457468027521071</v>
+        <v>0.09432825987709975</v>
       </c>
       <c r="C33">
-        <v>1714.983893020441</v>
+        <v>1724.654975975222</v>
       </c>
       <c r="D33">
-        <v>2058.97589302044</v>
+        <v>2068.646975975221</v>
       </c>
       <c r="E33">
         <v>-998.5080000000002</v>
@@ -3987,37 +4118,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M33">
-        <v>49.18300156528638</v>
+        <v>48.37910956528638</v>
       </c>
       <c r="N33">
-        <v>489.4169984347135</v>
+        <v>490.2208904347135</v>
       </c>
       <c r="O33">
-        <v>132.1425895773727</v>
+        <v>132.3596404173726</v>
       </c>
       <c r="P33">
-        <v>357.2744088573409</v>
+        <v>357.8612500173409</v>
       </c>
       <c r="Q33">
-        <v>727.6744088573409</v>
+        <v>728.2612500173409</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1169991246599341</v>
+        <v>0.1169699646626718</v>
       </c>
       <c r="T33">
         <v>1.303502896656051</v>
       </c>
       <c r="U33">
-        <v>0.06118110587651871</v>
+        <v>0.06018110587651871</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.04466220728985866</v>
+        <v>0.04393220728985866</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.95093798382868</v>
+        <v>11.13290436387989</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4036,13 +4167,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.0944185419320431</v>
+        <v>0.09416488082136518</v>
       </c>
       <c r="C34">
-        <v>1695.66428968605</v>
+        <v>1705.71097188968</v>
       </c>
       <c r="D34">
-        <v>2065.58828968605</v>
+        <v>2075.63497188968</v>
       </c>
       <c r="E34">
         <v>-972.5760000000001</v>
@@ -4069,37 +4200,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M34">
-        <v>50.76955000287626</v>
+        <v>49.93972600287626</v>
       </c>
       <c r="N34">
-        <v>487.8304499971237</v>
+        <v>488.6602739971236</v>
       </c>
       <c r="O34">
-        <v>131.7142214992234</v>
+        <v>131.9382739792234</v>
       </c>
       <c r="P34">
-        <v>356.1162284979002</v>
+        <v>356.7220000179002</v>
       </c>
       <c r="Q34">
-        <v>726.5162284979003</v>
+        <v>727.1220000179003</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1178332876460123</v>
+        <v>0.1178037860126624</v>
       </c>
       <c r="T34">
         <v>1.318774627507091</v>
       </c>
       <c r="U34">
-        <v>0.06118110587651871</v>
+        <v>0.06018110587651871</v>
       </c>
       <c r="V34">
         <v>0.27</v>
       </c>
       <c r="W34">
-        <v>0.04466220728985866</v>
+        <v>0.04393220728985866</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.60872117183403</v>
+        <v>10.78500110250864</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4118,13 +4249,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0942624035888755</v>
+        <v>0.09400150176563062</v>
       </c>
       <c r="C35">
-        <v>1676.387294583331</v>
+        <v>1686.814339447435</v>
       </c>
       <c r="D35">
-        <v>2072.243294583331</v>
+        <v>2082.670339447435</v>
       </c>
       <c r="E35">
         <v>-946.6440000000001</v>
@@ -4151,37 +4282,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M35">
-        <v>52.35609844046614</v>
+        <v>51.50034244046614</v>
       </c>
       <c r="N35">
-        <v>486.2439015595338</v>
+        <v>487.0996575595337</v>
       </c>
       <c r="O35">
-        <v>131.2858534210741</v>
+        <v>131.5169075410741</v>
       </c>
       <c r="P35">
-        <v>354.9580481384596</v>
+        <v>355.5827500184596</v>
       </c>
       <c r="Q35">
-        <v>725.3580481384597</v>
+        <v>725.9827500184597</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1186923510197345</v>
+        <v>0.1186624975522049</v>
       </c>
       <c r="T35">
         <v>1.334502230920848</v>
       </c>
       <c r="U35">
-        <v>0.06118110587651871</v>
+        <v>0.06018110587651871</v>
       </c>
       <c r="V35">
         <v>0.27</v>
       </c>
       <c r="W35">
-        <v>0.04466220728985866</v>
+        <v>0.04393220728985866</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.28724477268755</v>
+        <v>10.45818288728111</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4200,13 +4331,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09410626524570788</v>
+        <v>0.09383812270989603</v>
       </c>
       <c r="C36">
-        <v>1657.153320874759</v>
+        <v>1667.965561985506</v>
       </c>
       <c r="D36">
-        <v>2078.941320874759</v>
+        <v>2089.753561985506</v>
       </c>
       <c r="E36">
         <v>-920.7120000000001</v>
@@ -4233,37 +4364,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M36">
-        <v>53.94264687805603</v>
+        <v>53.06095887805603</v>
       </c>
       <c r="N36">
-        <v>484.6573531219439</v>
+        <v>485.5390411219439</v>
       </c>
       <c r="O36">
-        <v>130.8574853429249</v>
+        <v>131.0955411029249</v>
       </c>
       <c r="P36">
-        <v>353.799867779019</v>
+        <v>354.443500019019</v>
       </c>
       <c r="Q36">
-        <v>724.1998677790191</v>
+        <v>724.8435000190191</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1195774466169029</v>
+        <v>0.1195472306535517</v>
       </c>
       <c r="T36">
         <v>1.350706428377446</v>
       </c>
       <c r="U36">
-        <v>0.06118110587651871</v>
+        <v>0.06018110587651871</v>
       </c>
       <c r="V36">
         <v>0.27</v>
       </c>
       <c r="W36">
-        <v>0.04466220728985866</v>
+        <v>0.04393220728985866</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.984678749961441</v>
+        <v>10.15058927294931</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4282,13 +4413,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09451222690254027</v>
+        <v>0.09367474365416148</v>
       </c>
       <c r="C37">
-        <v>1613.895681774577</v>
+        <v>1649.165129438723</v>
       </c>
       <c r="D37">
-        <v>2061.615681774576</v>
+        <v>2096.885129438723</v>
       </c>
       <c r="E37">
         <v>-894.7800000000001</v>
@@ -4315,45 +4446,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M37">
-        <v>57.52595931564591</v>
+        <v>54.62157531564591</v>
       </c>
       <c r="N37">
-        <v>481.074040684354</v>
+        <v>483.978424684354</v>
       </c>
       <c r="O37">
-        <v>129.8899909847756</v>
+        <v>130.6741746647756</v>
       </c>
       <c r="P37">
-        <v>351.1840496995784</v>
+        <v>353.3042500195784</v>
       </c>
       <c r="Q37">
-        <v>721.5840496995784</v>
+        <v>723.7042500195785</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1204897759247535</v>
+        <v>0.120459186311863</v>
       </c>
       <c r="T37">
         <v>1.367409216525017</v>
       </c>
       <c r="U37">
-        <v>0.06338110587651871</v>
+        <v>0.06018110587651871</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.04626820728985866</v>
+        <v>0.04393220728985866</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y37">
-        <v>9.362729564311872</v>
+        <v>9.860572436579329</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4364,13 +4495,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09437214855937268</v>
+        <v>0.09395812459842692</v>
       </c>
       <c r="C38">
-        <v>1593.909222944087</v>
+        <v>1610.894250112514</v>
       </c>
       <c r="D38">
-        <v>2067.561222944087</v>
+        <v>2084.546250112514</v>
       </c>
       <c r="E38">
         <v>-868.8480000000002</v>
@@ -4397,37 +4528,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M38">
-        <v>59.16955815323579</v>
+        <v>57.76923015323579</v>
       </c>
       <c r="N38">
-        <v>479.4304418467641</v>
+        <v>480.8307698467641</v>
       </c>
       <c r="O38">
-        <v>129.4462192986263</v>
+        <v>129.8243078586263</v>
       </c>
       <c r="P38">
-        <v>349.9842225481378</v>
+        <v>351.0064619881377</v>
       </c>
       <c r="Q38">
-        <v>720.3842225481378</v>
+        <v>721.4064619881378</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1214306155234743</v>
+        <v>0.1213996405844966</v>
       </c>
       <c r="T38">
         <v>1.384633966802199</v>
       </c>
       <c r="U38">
-        <v>0.06338110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V38">
         <v>0.27</v>
       </c>
       <c r="W38">
-        <v>0.04626820728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.102653743080987</v>
+        <v>9.32330236306311</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4446,13 +4577,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09423207021620505</v>
+        <v>0.09380715554269235</v>
       </c>
       <c r="C39">
-        <v>1573.957156265432</v>
+        <v>1591.517564116375</v>
       </c>
       <c r="D39">
-        <v>2073.541156265432</v>
+        <v>2091.101564116375</v>
       </c>
       <c r="E39">
         <v>-842.9160000000002</v>
@@ -4479,37 +4610,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M39">
-        <v>60.81315699082568</v>
+        <v>59.37393099082568</v>
       </c>
       <c r="N39">
-        <v>477.7868430091742</v>
+        <v>479.2260690091742</v>
       </c>
       <c r="O39">
-        <v>129.0024476124771</v>
+        <v>129.3910386324771</v>
       </c>
       <c r="P39">
-        <v>348.7843953966972</v>
+        <v>349.8350303766972</v>
       </c>
       <c r="Q39">
-        <v>719.1843953966973</v>
+        <v>720.2350303766973</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.122401323045964</v>
+        <v>0.1223699505483248</v>
       </c>
       <c r="T39">
         <v>1.402405534548498</v>
       </c>
       <c r="U39">
-        <v>0.06338110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V39">
         <v>0.27</v>
       </c>
       <c r="W39">
-        <v>0.04626820728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.856636074349069</v>
+        <v>9.071321218115457</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4528,13 +4659,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09409199187303743</v>
+        <v>0.09365618648695778</v>
       </c>
       <c r="C40">
-        <v>1554.039781017775</v>
+        <v>1572.182237436046</v>
       </c>
       <c r="D40">
-        <v>2079.555781017775</v>
+        <v>2097.698237436046</v>
       </c>
       <c r="E40">
         <v>-816.9840000000002</v>
@@ -4561,37 +4692,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M40">
-        <v>62.45675582841556</v>
+        <v>60.97863182841556</v>
       </c>
       <c r="N40">
-        <v>476.1432441715843</v>
+        <v>477.6213681715843</v>
       </c>
       <c r="O40">
-        <v>128.5586759263278</v>
+        <v>128.9577694063278</v>
       </c>
       <c r="P40">
-        <v>347.5845682452565</v>
+        <v>348.6635987652566</v>
       </c>
       <c r="Q40">
-        <v>717.9845682452566</v>
+        <v>719.0635987652565</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1234033437143406</v>
+        <v>0.1233715608335669</v>
       </c>
       <c r="T40">
         <v>1.42075037867371</v>
       </c>
       <c r="U40">
-        <v>0.06338110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V40">
         <v>0.27</v>
       </c>
       <c r="W40">
-        <v>0.04626820728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.623566703971461</v>
+        <v>8.832602238691367</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4610,13 +4741,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09395191352986983</v>
+        <v>0.09350521743122323</v>
       </c>
       <c r="C41">
-        <v>1534.157399962802</v>
+        <v>1552.888662731526</v>
       </c>
       <c r="D41">
-        <v>2085.605399962802</v>
+        <v>2104.336662731525</v>
       </c>
       <c r="E41">
         <v>-791.0520000000001</v>
@@ -4643,37 +4774,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M41">
-        <v>64.10035466600544</v>
+        <v>62.58333266600544</v>
       </c>
       <c r="N41">
-        <v>474.4996453339945</v>
+        <v>476.0166673339945</v>
       </c>
       <c r="O41">
-        <v>128.1149042401785</v>
+        <v>128.5245001801785</v>
       </c>
       <c r="P41">
-        <v>346.3847410938159</v>
+        <v>347.492167153816</v>
       </c>
       <c r="Q41">
-        <v>716.7847410938159</v>
+        <v>717.892167153816</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1244382175193852</v>
+        <v>0.1244060108002924</v>
       </c>
       <c r="T41">
         <v>1.439696693098109</v>
       </c>
       <c r="U41">
-        <v>0.06338110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.04626820728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.402449608997834</v>
+        <v>8.606125258212101</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4692,13 +4823,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09381183518670222</v>
+        <v>0.09335424837548867</v>
       </c>
       <c r="C42">
-        <v>1514.310319395524</v>
+        <v>1533.637237649074</v>
       </c>
       <c r="D42">
-        <v>2091.690319395524</v>
+        <v>2111.017237649074</v>
       </c>
       <c r="E42">
         <v>-765.1200000000001</v>
@@ -4725,37 +4856,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M42">
-        <v>65.74395350359532</v>
+        <v>64.18803350359532</v>
       </c>
       <c r="N42">
-        <v>472.8560464964046</v>
+        <v>474.4119664964046</v>
       </c>
       <c r="O42">
-        <v>127.6711325540292</v>
+        <v>128.0912309540292</v>
       </c>
       <c r="P42">
-        <v>345.1849139423754</v>
+        <v>346.3207355423754</v>
       </c>
       <c r="Q42">
-        <v>715.5849139423754</v>
+        <v>716.7207355423755</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1255075871179313</v>
+        <v>0.1254749424325753</v>
       </c>
       <c r="T42">
         <v>1.459274551336655</v>
       </c>
       <c r="U42">
-        <v>0.06338110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.04626820728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.192388368772889</v>
+        <v>8.3909721267568</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4774,13 +4905,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09367175684353461</v>
+        <v>0.0932032793197541</v>
       </c>
       <c r="C43">
-        <v>1494.498849195972</v>
+        <v>1514.42836490062</v>
       </c>
       <c r="D43">
-        <v>2097.810849195972</v>
+        <v>2117.74036490062</v>
       </c>
       <c r="E43">
         <v>-739.1880000000001</v>
@@ -4807,37 +4938,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M43">
-        <v>67.38755234118521</v>
+        <v>65.79273434118521</v>
       </c>
       <c r="N43">
-        <v>471.2124476588147</v>
+        <v>472.8072656588147</v>
       </c>
       <c r="O43">
-        <v>127.22736086788</v>
+        <v>127.65796172788</v>
       </c>
       <c r="P43">
-        <v>343.9850867909347</v>
+        <v>345.1493039309347</v>
       </c>
       <c r="Q43">
-        <v>714.3850867909348</v>
+        <v>715.5493039309347</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1266132065333772</v>
+        <v>0.1265801090354441</v>
       </c>
       <c r="T43">
         <v>1.479516065786677</v>
       </c>
       <c r="U43">
-        <v>0.06338110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V43">
         <v>0.27</v>
       </c>
       <c r="W43">
-        <v>0.04626820728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.992574018315013</v>
+        <v>8.186314270006633</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4856,13 +4987,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09353167850036699</v>
+        <v>0.09305231026401954</v>
       </c>
       <c r="C44">
-        <v>1474.723302881802</v>
+        <v>1495.262452344676</v>
       </c>
       <c r="D44">
-        <v>2103.967302881802</v>
+        <v>2124.506452344676</v>
       </c>
       <c r="E44">
         <v>-713.2560000000003</v>
@@ -4889,37 +5020,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M44">
-        <v>69.03115117877508</v>
+        <v>67.39743517877508</v>
       </c>
       <c r="N44">
-        <v>469.5688488212248</v>
+        <v>471.2025648212248</v>
       </c>
       <c r="O44">
-        <v>126.7835891817307</v>
+        <v>127.2246925017307</v>
       </c>
       <c r="P44">
-        <v>342.7852596394941</v>
+        <v>343.9778723194941</v>
       </c>
       <c r="Q44">
-        <v>713.1852596394942</v>
+        <v>714.3778723194941</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1277569507562523</v>
+        <v>0.1277233848315153</v>
       </c>
       <c r="T44">
         <v>1.500455563493596</v>
       </c>
       <c r="U44">
-        <v>0.06338110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V44">
         <v>0.27</v>
       </c>
       <c r="W44">
-        <v>0.04626820728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.802274636926562</v>
+        <v>7.991402025482667</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4938,13 +5069,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09386245015719941</v>
+        <v>0.09290134120828497</v>
       </c>
       <c r="C45">
-        <v>1434.311542727685</v>
+        <v>1476.139913068823</v>
       </c>
       <c r="D45">
-        <v>2089.487542727685</v>
+        <v>2131.315913068823</v>
       </c>
       <c r="E45">
         <v>-687.3240000000003</v>
@@ -4971,45 +5102,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M45">
-        <v>72.34736401636496</v>
+        <v>69.00213601636497</v>
       </c>
       <c r="N45">
-        <v>466.2526359836349</v>
+        <v>469.597863983635</v>
       </c>
       <c r="O45">
-        <v>125.8882117155814</v>
+        <v>126.7914232755815</v>
       </c>
       <c r="P45">
-        <v>340.3644242680535</v>
+        <v>342.8064407080535</v>
       </c>
       <c r="Q45">
-        <v>710.7644242680535</v>
+        <v>713.2064407080536</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1289408263553687</v>
+        <v>0.1289067755677995</v>
       </c>
       <c r="T45">
         <v>1.522129780418302</v>
       </c>
       <c r="U45">
-        <v>0.06488110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V45">
         <v>0.27</v>
       </c>
       <c r="W45">
-        <v>0.04736320728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>7.444638893521659</v>
+        <v>7.805555466750511</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5020,13 +5151,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09373332181403179</v>
+        <v>0.09275037215255039</v>
       </c>
       <c r="C46">
-        <v>1414.008446676979</v>
+        <v>1457.06116547378</v>
       </c>
       <c r="D46">
-        <v>2095.116446676979</v>
+        <v>2138.16916547378</v>
       </c>
       <c r="E46">
         <v>-661.3920000000001</v>
@@ -5053,45 +5184,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M46">
-        <v>74.02986085395487</v>
+        <v>70.60683685395486</v>
       </c>
       <c r="N46">
-        <v>464.5701391460451</v>
+        <v>467.993163146045</v>
       </c>
       <c r="O46">
-        <v>125.4339375694322</v>
+        <v>126.3581540494322</v>
       </c>
       <c r="P46">
-        <v>339.1362015766128</v>
+        <v>341.6350090966129</v>
       </c>
       <c r="Q46">
-        <v>709.5362015766129</v>
+        <v>712.0350090966128</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1301669832258821</v>
+        <v>0.130132430258951</v>
       </c>
       <c r="T46">
         <v>1.544578076518891</v>
       </c>
       <c r="U46">
-        <v>0.06488110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.04736320728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.275442555032527</v>
+        <v>7.628156478869816</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5102,13 +5233,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09360419347086416</v>
+        <v>0.09286220309681581</v>
       </c>
       <c r="C47">
-        <v>1393.735760135903</v>
+        <v>1426.048368973832</v>
       </c>
       <c r="D47">
-        <v>2100.775760135903</v>
+        <v>2133.088368973832</v>
       </c>
       <c r="E47">
         <v>-635.46</v>
@@ -5135,37 +5266,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M47">
-        <v>75.71235769154475</v>
+        <v>73.14508969154474</v>
       </c>
       <c r="N47">
-        <v>462.8876423084552</v>
+        <v>465.4549103084552</v>
       </c>
       <c r="O47">
-        <v>124.9796634232829</v>
+        <v>125.6728257832829</v>
       </c>
       <c r="P47">
-        <v>337.9079788851723</v>
+        <v>339.7820845251723</v>
       </c>
       <c r="Q47">
-        <v>708.3079788851724</v>
+        <v>710.1820845251723</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1314377276189596</v>
+        <v>0.1314026542115989</v>
       </c>
       <c r="T47">
         <v>1.567842674295864</v>
       </c>
       <c r="U47">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V47">
         <v>0.27</v>
       </c>
       <c r="W47">
-        <v>0.04736320728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.113766053809583</v>
+        <v>7.363447119571442</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5184,13 +5315,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09347506512769657</v>
+        <v>0.09271707404108127</v>
       </c>
       <c r="C48">
-        <v>1373.493730197745</v>
+        <v>1406.714672621592</v>
       </c>
       <c r="D48">
-        <v>2106.465730197745</v>
+        <v>2139.686672621592</v>
       </c>
       <c r="E48">
         <v>-609.528</v>
@@ -5217,37 +5348,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M48">
-        <v>77.39485452913463</v>
+        <v>74.77053612913463</v>
       </c>
       <c r="N48">
-        <v>461.2051454708653</v>
+        <v>463.8294638708653</v>
       </c>
       <c r="O48">
-        <v>124.5253892771336</v>
+        <v>125.2339552451336</v>
       </c>
       <c r="P48">
-        <v>336.6797561937316</v>
+        <v>338.5955086257317</v>
       </c>
       <c r="Q48">
-        <v>707.0797561937317</v>
+        <v>708.9955086257316</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1327555366191881</v>
+        <v>0.1327199234958265</v>
       </c>
       <c r="T48">
         <v>1.591968923842355</v>
       </c>
       <c r="U48">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V48">
         <v>0.27</v>
       </c>
       <c r="W48">
-        <v>0.04736320728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.959118965683287</v>
+        <v>7.203372182189455</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5266,13 +5397,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09334593678452893</v>
+        <v>0.0925719449853467</v>
       </c>
       <c r="C49">
-        <v>1353.28260664009</v>
+        <v>1387.421924131503</v>
       </c>
       <c r="D49">
-        <v>2112.18660664009</v>
+        <v>2146.325924131503</v>
       </c>
       <c r="E49">
         <v>-583.596</v>
@@ -5299,37 +5430,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M49">
-        <v>79.07735136672451</v>
+        <v>76.39598256672451</v>
       </c>
       <c r="N49">
-        <v>459.5226486332754</v>
+        <v>462.2040174332754</v>
       </c>
       <c r="O49">
-        <v>124.0711151309844</v>
+        <v>124.7950847069844</v>
       </c>
       <c r="P49">
-        <v>335.451533502291</v>
+        <v>337.408932726291</v>
       </c>
       <c r="Q49">
-        <v>705.851533502291</v>
+        <v>707.808932726291</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1341230742609346</v>
+        <v>0.1340869010549304</v>
       </c>
       <c r="T49">
         <v>1.617005597900034</v>
       </c>
       <c r="U49">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V49">
         <v>0.27</v>
       </c>
       <c r="W49">
-        <v>0.04736320728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.811052604711302</v>
+        <v>7.050108944270529</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5348,13 +5479,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09321680844136133</v>
+        <v>0.09242681592961213</v>
       </c>
       <c r="C50">
-        <v>1333.102641961353</v>
+        <v>1368.170505862369</v>
       </c>
       <c r="D50">
-        <v>2117.938641961352</v>
+        <v>2153.006505862369</v>
       </c>
       <c r="E50">
         <v>-557.6640000000002</v>
@@ -5381,37 +5512,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M50">
-        <v>80.75984820431439</v>
+        <v>78.02142900431438</v>
       </c>
       <c r="N50">
-        <v>457.8401517956855</v>
+        <v>460.5785709956855</v>
       </c>
       <c r="O50">
-        <v>123.6168409848351</v>
+        <v>124.3562141688351</v>
       </c>
       <c r="P50">
-        <v>334.2233108108504</v>
+        <v>336.2223568268504</v>
       </c>
       <c r="Q50">
-        <v>704.6233108108504</v>
+        <v>706.6223568268505</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1355432095042869</v>
+        <v>0.1355064546739999</v>
       </c>
       <c r="T50">
         <v>1.643005220959932</v>
       </c>
       <c r="U50">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V50">
         <v>0.27</v>
       </c>
       <c r="W50">
-        <v>0.04736320728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.669155675446484</v>
+        <v>6.903231674598228</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5430,13 +5561,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09308768009819371</v>
+        <v>0.09228168687387756</v>
       </c>
       <c r="C51">
-        <v>1312.95409141794</v>
+        <v>1348.960804948331</v>
       </c>
       <c r="D51">
-        <v>2123.72209141794</v>
+        <v>2159.72880494833</v>
       </c>
       <c r="E51">
         <v>-531.7320000000002</v>
@@ -5463,37 +5594,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M51">
-        <v>82.44234504190428</v>
+        <v>79.64687544190427</v>
       </c>
       <c r="N51">
-        <v>456.1576549580956</v>
+        <v>458.9531245580956</v>
       </c>
       <c r="O51">
-        <v>123.1625668386858</v>
+        <v>123.9173436306858</v>
       </c>
       <c r="P51">
-        <v>332.9950881194098</v>
+        <v>335.0357809274098</v>
       </c>
       <c r="Q51">
-        <v>703.3950881194098</v>
+        <v>705.4357809274098</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1370190363258098</v>
+        <v>0.1369816770624447</v>
       </c>
       <c r="T51">
         <v>1.670024437081002</v>
       </c>
       <c r="U51">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V51">
         <v>0.27</v>
       </c>
       <c r="W51">
-        <v>0.04736320728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.53305045758023</v>
+        <v>6.762349395524794</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5512,13 +5643,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.0929585517550261</v>
+        <v>0.09213655781814299</v>
       </c>
       <c r="C52">
-        <v>1292.837213062001</v>
+        <v>1329.79321337364</v>
       </c>
       <c r="D52">
-        <v>2129.537213062001</v>
+        <v>2166.49321337364</v>
       </c>
       <c r="E52">
         <v>-505.8000000000002</v>
@@ -5545,37 +5676,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M52">
-        <v>84.12484187949416</v>
+        <v>81.27232187949414</v>
       </c>
       <c r="N52">
-        <v>454.4751581205057</v>
+        <v>457.3276781205058</v>
       </c>
       <c r="O52">
-        <v>122.7082926925366</v>
+        <v>123.4784730925366</v>
       </c>
       <c r="P52">
-        <v>331.7668654279692</v>
+        <v>333.8492050279692</v>
       </c>
       <c r="Q52">
-        <v>702.1668654279692</v>
+        <v>704.2492050279693</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1385538962201935</v>
+        <v>0.1385159083464273</v>
       </c>
       <c r="T52">
         <v>1.698124421846915</v>
       </c>
       <c r="U52">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V52">
         <v>0.27</v>
       </c>
       <c r="W52">
-        <v>0.04736320728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.402389448428625</v>
+        <v>6.627102407614299</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5594,13 +5725,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09282942341185849</v>
+        <v>0.09199142876240841</v>
       </c>
       <c r="C53">
-        <v>1272.752267779817</v>
+        <v>1310.668128048862</v>
       </c>
       <c r="D53">
-        <v>2135.384267779817</v>
+        <v>2173.300128048862</v>
       </c>
       <c r="E53">
         <v>-479.8680000000002</v>
@@ -5627,37 +5758,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M53">
-        <v>85.80733871708404</v>
+        <v>82.89776831708403</v>
       </c>
       <c r="N53">
-        <v>452.7926612829159</v>
+        <v>455.7022316829159</v>
       </c>
       <c r="O53">
-        <v>122.2540185463873</v>
+        <v>123.0396025543873</v>
       </c>
       <c r="P53">
-        <v>330.5386427365286</v>
+        <v>332.6626291285286</v>
       </c>
       <c r="Q53">
-        <v>700.9386427365287</v>
+        <v>703.0626291285287</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1401514034572053</v>
+        <v>0.1401127613154704</v>
       </c>
       <c r="T53">
         <v>1.727371344766539</v>
       </c>
       <c r="U53">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V53">
         <v>0.27</v>
       </c>
       <c r="W53">
-        <v>0.04736320728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.276852400420221</v>
+        <v>6.497159223151273</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5676,13 +5807,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09270029506869087</v>
+        <v>0.09184629970667386</v>
       </c>
       <c r="C54">
-        <v>1252.699519330809</v>
+        <v>1291.585950888497</v>
       </c>
       <c r="D54">
-        <v>2141.263519330809</v>
+        <v>2180.149950888497</v>
       </c>
       <c r="E54">
         <v>-453.9360000000001</v>
@@ -5709,37 +5840,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M54">
-        <v>87.48983555467393</v>
+        <v>84.52321475467392</v>
       </c>
       <c r="N54">
-        <v>451.1101644453259</v>
+        <v>454.076785245326</v>
       </c>
       <c r="O54">
-        <v>121.799744400238</v>
+        <v>122.600732016238</v>
       </c>
       <c r="P54">
-        <v>329.3104200450879</v>
+        <v>331.4760532290879</v>
       </c>
       <c r="Q54">
-        <v>699.710420045088</v>
+        <v>701.876053229088</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1418154734957591</v>
+        <v>0.1417761498248903</v>
       </c>
       <c r="T54">
         <v>1.75783688947448</v>
       </c>
       <c r="U54">
-        <v>0.06488110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V54">
         <v>0.27</v>
       </c>
       <c r="W54">
-        <v>0.04736320728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.156143700412139</v>
+        <v>6.372213853475287</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5758,13 +5889,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09311282672552328</v>
+        <v>0.0917011706509393</v>
       </c>
       <c r="C55">
-        <v>1208.097339413874</v>
+        <v>1272.547088890104</v>
       </c>
       <c r="D55">
-        <v>2122.593339413874</v>
+        <v>2187.043088890104</v>
       </c>
       <c r="E55">
         <v>-428.0040000000001</v>
@@ -5791,45 +5922,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M55">
-        <v>91.0964867922638</v>
+        <v>86.1486611922638</v>
       </c>
       <c r="N55">
-        <v>447.5035132077361</v>
+        <v>452.4513388077361</v>
       </c>
       <c r="O55">
-        <v>120.8259485660888</v>
+        <v>122.1618614780888</v>
       </c>
       <c r="P55">
-        <v>326.6775646416473</v>
+        <v>330.2894773296473</v>
       </c>
       <c r="Q55">
-        <v>697.0775646416473</v>
+        <v>700.6894773296474</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1435503550253153</v>
+        <v>0.1435103208240728</v>
       </c>
       <c r="T55">
         <v>1.789598840340206</v>
       </c>
       <c r="U55">
-        <v>0.06628110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V55">
         <v>0.27</v>
       </c>
       <c r="W55">
-        <v>0.04838520728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y55">
-        <v>5.91241242077998</v>
+        <v>6.251983403409715</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5840,13 +5971,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09299391838235566</v>
+        <v>0.09155604159520472</v>
       </c>
       <c r="C56">
-        <v>1187.513360215272</v>
+        <v>1253.551954214895</v>
       </c>
       <c r="D56">
-        <v>2127.941360215272</v>
+        <v>2193.979954214894</v>
       </c>
       <c r="E56">
         <v>-402.0720000000001</v>
@@ -5873,45 +6004,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M56">
-        <v>92.81528842985369</v>
+        <v>87.77410762985369</v>
       </c>
       <c r="N56">
-        <v>445.7847115701462</v>
+        <v>450.8258923701462</v>
       </c>
       <c r="O56">
-        <v>120.3618721239395</v>
+        <v>121.7229909399395</v>
       </c>
       <c r="P56">
-        <v>325.4228394462067</v>
+        <v>329.1029014302067</v>
       </c>
       <c r="Q56">
-        <v>695.8228394462067</v>
+        <v>699.5029014302067</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1453606661865913</v>
+        <v>0.1453198905623501</v>
       </c>
       <c r="T56">
         <v>1.822741745591398</v>
       </c>
       <c r="U56">
-        <v>0.06628110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V56">
         <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.04838520728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y56">
-        <v>5.802923301876646</v>
+        <v>6.136205932976202</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5922,13 +6053,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09287501003918805</v>
+        <v>0.09181241253947017</v>
       </c>
       <c r="C57">
-        <v>1166.956398506085</v>
+        <v>1215.395585147547</v>
       </c>
       <c r="D57">
-        <v>2133.316398506085</v>
+        <v>2181.755585147547</v>
       </c>
       <c r="E57">
         <v>-376.1400000000001</v>
@@ -5955,37 +6086,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M57">
-        <v>94.53409006744357</v>
+        <v>90.82581406744357</v>
       </c>
       <c r="N57">
-        <v>444.0659099325563</v>
+        <v>447.7741859325563</v>
       </c>
       <c r="O57">
-        <v>119.8977956817902</v>
+        <v>120.8990302017902</v>
       </c>
       <c r="P57">
-        <v>324.1681142507661</v>
+        <v>326.8751557307661</v>
       </c>
       <c r="Q57">
-        <v>694.5681142507661</v>
+        <v>697.2751557307661</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1472514356217018</v>
+        <v>0.1472098856223287</v>
       </c>
       <c r="T57">
         <v>1.857357668853755</v>
       </c>
       <c r="U57">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V57">
         <v>0.27</v>
       </c>
       <c r="W57">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.69741560547889</v>
+        <v>5.930032177857028</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6004,13 +6135,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09275610169602043</v>
+        <v>0.0916745834837356</v>
       </c>
       <c r="C58">
-        <v>1146.426659537906</v>
+        <v>1196.018616045018</v>
       </c>
       <c r="D58">
-        <v>2138.718659537906</v>
+        <v>2188.310616045018</v>
       </c>
       <c r="E58">
         <v>-350.2080000000001</v>
@@ -6037,37 +6168,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M58">
-        <v>96.25289170503346</v>
+        <v>92.47719250503346</v>
       </c>
       <c r="N58">
-        <v>442.3471082949665</v>
+        <v>446.1228074949664</v>
       </c>
       <c r="O58">
-        <v>119.433719239641</v>
+        <v>120.4531580236409</v>
       </c>
       <c r="P58">
-        <v>322.9133890553255</v>
+        <v>325.6696494713255</v>
       </c>
       <c r="Q58">
-        <v>693.3133890553256</v>
+        <v>696.0696494713255</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1492281491220445</v>
+        <v>0.1491857895486699</v>
       </c>
       <c r="T58">
         <v>1.893547043173491</v>
       </c>
       <c r="U58">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V58">
         <v>0.27</v>
       </c>
       <c r="W58">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.595676041095338</v>
+        <v>5.824138746109581</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6086,13 +6217,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09263719335285282</v>
+        <v>0.09153675442800102</v>
       </c>
       <c r="C59">
-        <v>1125.924350646668</v>
+        <v>1176.681154499605</v>
       </c>
       <c r="D59">
-        <v>2144.148350646667</v>
+        <v>2194.905154499605</v>
       </c>
       <c r="E59">
         <v>-324.2760000000001</v>
@@ -6119,37 +6250,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M59">
-        <v>97.97169334262334</v>
+        <v>94.12857094262334</v>
       </c>
       <c r="N59">
-        <v>440.6283066573766</v>
+        <v>444.4714290573766</v>
       </c>
       <c r="O59">
-        <v>118.9696427974917</v>
+        <v>120.0072858454917</v>
       </c>
       <c r="P59">
-        <v>321.6586638598849</v>
+        <v>324.4641432118849</v>
       </c>
       <c r="Q59">
-        <v>692.058663859885</v>
+        <v>694.864143211885</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1512968027851939</v>
+        <v>0.151253595983213</v>
       </c>
       <c r="T59">
         <v>1.931419644205774</v>
       </c>
       <c r="U59">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V59">
         <v>0.27</v>
       </c>
       <c r="W59">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.497506285988402</v>
+        <v>5.721960873370817</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6168,13 +6299,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.0925182850096852</v>
+        <v>0.09139892537226646</v>
       </c>
       <c r="C60">
-        <v>1105.449681279162</v>
+        <v>1157.383558762465</v>
       </c>
       <c r="D60">
-        <v>2149.605681279162</v>
+        <v>2201.539558762465</v>
       </c>
       <c r="E60">
         <v>-298.3440000000003</v>
@@ -6201,37 +6332,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M60">
-        <v>99.69049498021322</v>
+        <v>95.77994938021321</v>
       </c>
       <c r="N60">
-        <v>438.9095050197867</v>
+        <v>442.8200506197867</v>
       </c>
       <c r="O60">
-        <v>118.5055663553424</v>
+        <v>119.5614136673424</v>
       </c>
       <c r="P60">
-        <v>320.4039386644443</v>
+        <v>323.2586369524442</v>
       </c>
       <c r="Q60">
-        <v>690.8039386644443</v>
+        <v>693.6586369524443</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1534639637656361</v>
+        <v>0.1534198693908296</v>
       </c>
       <c r="T60">
         <v>1.971095702430069</v>
       </c>
       <c r="U60">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V60">
         <v>0.27</v>
       </c>
       <c r="W60">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.402721694850672</v>
+        <v>5.623306375554079</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6250,13 +6381,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0923993766665176</v>
+        <v>0.0912610963165319</v>
       </c>
       <c r="C61">
-        <v>1085.002863019978</v>
+        <v>1138.126191429345</v>
       </c>
       <c r="D61">
-        <v>2155.090863019978</v>
+        <v>2208.214191429345</v>
       </c>
       <c r="E61">
         <v>-272.4120000000003</v>
@@ -6283,37 +6414,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M61">
-        <v>101.4092966178031</v>
+        <v>97.43132781780309</v>
       </c>
       <c r="N61">
-        <v>437.1907033821968</v>
+        <v>441.1686721821968</v>
       </c>
       <c r="O61">
-        <v>118.0414899131931</v>
+        <v>119.1155414891931</v>
       </c>
       <c r="P61">
-        <v>319.1492134690037</v>
+        <v>322.0531306930037</v>
       </c>
       <c r="Q61">
-        <v>689.5492134690037</v>
+        <v>692.4531306930037</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1557368399158561</v>
+        <v>0.1556918146719885</v>
       </c>
       <c r="T61">
         <v>2.01270717812872</v>
       </c>
       <c r="U61">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V61">
         <v>0.27</v>
       </c>
       <c r="W61">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.31115014070066</v>
+        <v>5.527996098002315</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6332,13 +6463,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09228046832334999</v>
+        <v>0.09112326726079732</v>
       </c>
       <c r="C62">
-        <v>1064.584109618843</v>
+        <v>1118.909419506639</v>
       </c>
       <c r="D62">
-        <v>2160.604109618842</v>
+        <v>2214.929419506639</v>
       </c>
       <c r="E62">
         <v>-246.4800000000002</v>
@@ -6365,37 +6496,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M62">
-        <v>103.128098255393</v>
+        <v>99.08270625539298</v>
       </c>
       <c r="N62">
-        <v>435.471901744607</v>
+        <v>439.5172937446069</v>
       </c>
       <c r="O62">
-        <v>117.5774134710439</v>
+        <v>118.6696693110439</v>
       </c>
       <c r="P62">
-        <v>317.8944882735631</v>
+        <v>320.8476244335631</v>
       </c>
       <c r="Q62">
-        <v>688.294488273563</v>
+        <v>691.247624433563</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.158123359873587</v>
+        <v>0.1580773572172053</v>
       </c>
       <c r="T62">
         <v>2.056399227612304</v>
       </c>
       <c r="U62">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V62">
         <v>0.27</v>
       </c>
       <c r="W62">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.222630971688982</v>
+        <v>5.435862829702277</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6414,13 +6545,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.09216155998018238</v>
+        <v>0.09098543820506276</v>
       </c>
       <c r="C63">
-        <v>1044.193637018389</v>
+        <v>1099.733614478653</v>
       </c>
       <c r="D63">
-        <v>2166.145637018389</v>
+        <v>2221.685614478653</v>
       </c>
       <c r="E63">
         <v>-220.5480000000002</v>
@@ -6447,37 +6578,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M63">
-        <v>104.8468998929829</v>
+        <v>100.7340846929829</v>
       </c>
       <c r="N63">
-        <v>433.7531001070171</v>
+        <v>437.8659153070171</v>
       </c>
       <c r="O63">
-        <v>117.1133370288946</v>
+        <v>118.2237971328946</v>
       </c>
       <c r="P63">
-        <v>316.6397630781224</v>
+        <v>319.6421181741225</v>
       </c>
       <c r="Q63">
-        <v>687.0397630781224</v>
+        <v>690.0421181741225</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1606322654701759</v>
+        <v>0.1605852352775615</v>
       </c>
       <c r="T63">
         <v>2.102331895018124</v>
       </c>
       <c r="U63">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V63">
         <v>0.27</v>
       </c>
       <c r="W63">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.137014070513754</v>
+        <v>5.346750324297322</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6496,13 +6627,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09204265163701478</v>
+        <v>0.09084760914932821</v>
       </c>
       <c r="C64">
-        <v>1023.831663382349</v>
+        <v>1080.599152376115</v>
       </c>
       <c r="D64">
-        <v>2171.715663382349</v>
+        <v>2228.483152376115</v>
       </c>
       <c r="E64">
         <v>-194.6160000000002</v>
@@ -6529,37 +6660,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M64">
-        <v>106.5657015305728</v>
+        <v>102.3854631305727</v>
       </c>
       <c r="N64">
-        <v>432.0342984694271</v>
+        <v>436.2145368694271</v>
       </c>
       <c r="O64">
-        <v>116.6492605867453</v>
+        <v>117.7779249547453</v>
       </c>
       <c r="P64">
-        <v>315.3850378826818</v>
+        <v>318.4366119146818</v>
       </c>
       <c r="Q64">
-        <v>685.7850378826818</v>
+        <v>688.8366119146818</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1632732187297432</v>
+        <v>0.1632251069200417</v>
       </c>
       <c r="T64">
         <v>2.150682071234776</v>
       </c>
       <c r="U64">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V64">
         <v>0.27</v>
       </c>
       <c r="W64">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.054159004860305</v>
+        <v>5.260512415840912</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6578,13 +6709,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.09192374329384716</v>
+        <v>0.09070978009359362</v>
       </c>
       <c r="C65">
-        <v>1003.498409124185</v>
+        <v>1061.506413845941</v>
       </c>
       <c r="D65">
-        <v>2177.314409124185</v>
+        <v>2235.32241384594</v>
       </c>
       <c r="E65">
         <v>-168.6840000000002</v>
@@ -6611,37 +6742,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M65">
-        <v>108.2845031681626</v>
+        <v>104.0368415681626</v>
       </c>
       <c r="N65">
-        <v>430.3154968318373</v>
+        <v>434.5631584318373</v>
       </c>
       <c r="O65">
-        <v>116.1851841445961</v>
+        <v>117.3320527765961</v>
       </c>
       <c r="P65">
-        <v>314.1303126872412</v>
+        <v>317.2311056552412</v>
       </c>
       <c r="Q65">
-        <v>684.5303126872412</v>
+        <v>687.6311056552413</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1660569262195573</v>
+        <v>0.1660076743269802</v>
       </c>
       <c r="T65">
         <v>2.201645770490165</v>
       </c>
       <c r="U65">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V65">
         <v>0.27</v>
       </c>
       <c r="W65">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.973934258751411</v>
+        <v>5.177012218764073</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6660,13 +6791,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09180483495067956</v>
+        <v>0.09057195103785907</v>
       </c>
       <c r="C66">
-        <v>983.1940969361606</v>
+        <v>1042.455784222276</v>
       </c>
       <c r="D66">
-        <v>2182.94209693616</v>
+        <v>2242.203784222276</v>
       </c>
       <c r="E66">
         <v>-142.7520000000002</v>
@@ -6693,37 +6824,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M66">
-        <v>110.0033048057525</v>
+        <v>105.6882200057525</v>
       </c>
       <c r="N66">
-        <v>428.5966951942474</v>
+        <v>432.9117799942474</v>
       </c>
       <c r="O66">
-        <v>115.7211077024468</v>
+        <v>116.8861805984468</v>
       </c>
       <c r="P66">
-        <v>312.8755874918006</v>
+        <v>316.0255993958006</v>
       </c>
       <c r="Q66">
-        <v>683.2755874918007</v>
+        <v>686.4255993958006</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1689952841254723</v>
+        <v>0.1689448288120821</v>
       </c>
       <c r="T66">
         <v>2.255440786370855</v>
       </c>
       <c r="U66">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V66">
         <v>0.27</v>
       </c>
       <c r="W66">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.896216535958421</v>
+        <v>5.096121402845884</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6742,13 +6873,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09168592660751194</v>
+        <v>0.09043412198212451</v>
       </c>
       <c r="C67">
-        <v>962.9189518188741</v>
+        <v>1023.447653598884</v>
       </c>
       <c r="D67">
-        <v>2188.598951818874</v>
+        <v>2249.127653598884</v>
       </c>
       <c r="E67">
         <v>-116.8200000000002</v>
@@ -6775,37 +6906,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M67">
-        <v>111.7221064433424</v>
+        <v>107.3395984433424</v>
       </c>
       <c r="N67">
-        <v>426.8778935566575</v>
+        <v>431.2604015566575</v>
       </c>
       <c r="O67">
-        <v>115.2570312602975</v>
+        <v>116.4403084202975</v>
       </c>
       <c r="P67">
-        <v>311.62086229636</v>
+        <v>314.82009313636</v>
       </c>
       <c r="Q67">
-        <v>682.0208622963601</v>
+        <v>685.22009313636</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1721015481974395</v>
+        <v>0.1720498206963325</v>
       </c>
       <c r="T67">
         <v>2.312309803159012</v>
       </c>
       <c r="U67">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V67">
         <v>0.27</v>
       </c>
       <c r="W67">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.820890127712906</v>
+        <v>5.017719535109793</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6824,13 +6955,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09156701826434431</v>
+        <v>0.09029629292638994</v>
       </c>
       <c r="C68">
-        <v>942.6732011112374</v>
+        <v>1004.482416902849</v>
       </c>
       <c r="D68">
-        <v>2194.285201111237</v>
+        <v>2256.094416902848</v>
       </c>
       <c r="E68">
         <v>-90.88800000000015</v>
@@ -6857,37 +6988,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M68">
-        <v>113.4409080809323</v>
+        <v>108.9909768809323</v>
       </c>
       <c r="N68">
-        <v>425.1590919190676</v>
+        <v>429.6090231190676</v>
       </c>
       <c r="O68">
-        <v>114.7929548181483</v>
+        <v>115.9944362421483</v>
       </c>
       <c r="P68">
-        <v>310.3661371009193</v>
+        <v>313.6145868769194</v>
       </c>
       <c r="Q68">
-        <v>680.7661371009194</v>
+        <v>684.0145868769193</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1753905336854047</v>
+        <v>0.1753374591620095</v>
       </c>
       <c r="T68">
         <v>2.372524056228825</v>
       </c>
       <c r="U68">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V68">
         <v>0.27</v>
       </c>
       <c r="W68">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.747846337899075</v>
+        <v>4.941693481547524</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6906,13 +7037,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09144810992117672</v>
+        <v>0.09015846387065538</v>
       </c>
       <c r="C69">
-        <v>922.4570745209326</v>
+        <v>985.5604739696682</v>
       </c>
       <c r="D69">
-        <v>2200.001074520932</v>
+        <v>2263.104473969668</v>
       </c>
       <c r="E69">
         <v>-64.95600000000013</v>
@@ -6939,37 +7070,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M69">
-        <v>115.1597097185222</v>
+        <v>110.6423553185222</v>
       </c>
       <c r="N69">
-        <v>423.4402902814777</v>
+        <v>427.9576446814777</v>
       </c>
       <c r="O69">
-        <v>114.328878375999</v>
+        <v>115.548564063999</v>
       </c>
       <c r="P69">
-        <v>309.1114119054787</v>
+        <v>312.4090806174788</v>
       </c>
       <c r="Q69">
-        <v>679.5114119054788</v>
+        <v>682.8090806174788</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1788788516271861</v>
+        <v>0.1788243484437881</v>
       </c>
       <c r="T69">
         <v>2.436387657969536</v>
       </c>
       <c r="U69">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V69">
         <v>0.27</v>
       </c>
       <c r="W69">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.676982959721476</v>
+        <v>4.867936862419949</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6988,13 +7119,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09132920157800911</v>
+        <v>0.09002063481492081</v>
       </c>
       <c r="C70">
-        <v>902.2708041553522</v>
+        <v>966.682229619749</v>
       </c>
       <c r="D70">
-        <v>2205.746804155352</v>
+        <v>2270.158229619749</v>
       </c>
       <c r="E70">
         <v>-39.02400000000011</v>
@@ -7021,37 +7152,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M70">
-        <v>116.8785113561121</v>
+        <v>112.293733756112</v>
       </c>
       <c r="N70">
-        <v>421.7214886438878</v>
+        <v>426.3062662438879</v>
       </c>
       <c r="O70">
-        <v>113.8648019338497</v>
+        <v>115.1026918858497</v>
       </c>
       <c r="P70">
-        <v>307.8566867100381</v>
+        <v>311.2035743580382</v>
       </c>
       <c r="Q70">
-        <v>678.2566867100381</v>
+        <v>681.6035743580383</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1825851894403288</v>
+        <v>0.1825291683056779</v>
       </c>
       <c r="T70">
         <v>2.504242734819042</v>
       </c>
       <c r="U70">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V70">
         <v>0.27</v>
       </c>
       <c r="W70">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.608203798549102</v>
+        <v>4.796349555619655</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7070,13 +7201,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09121029323484148</v>
+        <v>0.08988280575918622</v>
       </c>
       <c r="C71">
-        <v>882.1146245530099</v>
+        <v>947.8480937363361</v>
       </c>
       <c r="D71">
-        <v>2211.52262455301</v>
+        <v>2277.256093736336</v>
       </c>
       <c r="E71">
         <v>-13.0920000000001</v>
@@ -7103,37 +7234,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M71">
-        <v>118.5973129937019</v>
+        <v>113.9451121937019</v>
       </c>
       <c r="N71">
-        <v>420.0026870062979</v>
+        <v>424.654887806298</v>
       </c>
       <c r="O71">
-        <v>113.4007254917005</v>
+        <v>114.6568197077005</v>
       </c>
       <c r="P71">
-        <v>306.6019615145975</v>
+        <v>309.9980680985975</v>
       </c>
       <c r="Q71">
-        <v>677.0019615145975</v>
+        <v>680.3980680985976</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1865306458220613</v>
+        <v>0.1864730088038186</v>
       </c>
       <c r="T71">
         <v>2.576475558562064</v>
       </c>
       <c r="U71">
-        <v>0.06628110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V71">
         <v>0.27</v>
       </c>
       <c r="W71">
-        <v>0.04838520728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.541418236251289</v>
+        <v>4.726837243219371</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7152,13 +7283,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09241998489167388</v>
+        <v>0.08974497670345169</v>
       </c>
       <c r="C72">
-        <v>798.7982115371303</v>
+        <v>929.0584813449007</v>
       </c>
       <c r="D72">
-        <v>2154.13821153713</v>
+        <v>2284.398481344901</v>
       </c>
       <c r="E72">
         <v>12.83999999999992</v>
@@ -7185,45 +7316,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M72">
-        <v>125.0357386312918</v>
+        <v>115.5964906312918</v>
       </c>
       <c r="N72">
-        <v>413.5642613687081</v>
+        <v>423.0035093687081</v>
       </c>
       <c r="O72">
-        <v>111.6623505695512</v>
+        <v>114.2109475295512</v>
       </c>
       <c r="P72">
-        <v>301.9019107991569</v>
+        <v>308.7925618391569</v>
       </c>
       <c r="Q72">
-        <v>672.301910799157</v>
+        <v>679.192561839157</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1907391326292428</v>
+        <v>0.1906797720018354</v>
       </c>
       <c r="T72">
         <v>2.653523903887955</v>
       </c>
       <c r="U72">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V72">
         <v>0.27</v>
       </c>
       <c r="W72">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>4.307568427201726</v>
+        <v>4.659310996887665</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7234,13 +7365,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09232005654850628</v>
+        <v>0.08960714764771711</v>
       </c>
       <c r="C73">
-        <v>777.4934514504891</v>
+        <v>910.3138126940501</v>
       </c>
       <c r="D73">
-        <v>2158.765451450489</v>
+        <v>2291.58581269405</v>
       </c>
       <c r="E73">
         <v>38.77199999999971</v>
@@ -7267,45 +7398,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M73">
-        <v>126.8219634688817</v>
+        <v>117.2478690688817</v>
       </c>
       <c r="N73">
-        <v>411.7780365311182</v>
+        <v>421.3521309311182</v>
       </c>
       <c r="O73">
-        <v>111.1800698634019</v>
+        <v>113.7650753514019</v>
       </c>
       <c r="P73">
-        <v>300.5979666677163</v>
+        <v>307.5870555797163</v>
       </c>
       <c r="Q73">
-        <v>670.9979666677164</v>
+        <v>677.9870555797163</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1952378599058849</v>
+        <v>0.1951766567997154</v>
       </c>
       <c r="T73">
         <v>2.735885928201836</v>
       </c>
       <c r="U73">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V73">
         <v>0.27</v>
       </c>
       <c r="W73">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.246898449353815</v>
+        <v>4.593686898339952</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7316,13 +7447,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09222012820533865</v>
+        <v>0.08946931859198254</v>
       </c>
       <c r="C74">
-        <v>756.2086134293777</v>
+        <v>891.6145133379382</v>
       </c>
       <c r="D74">
-        <v>2163.412613429377</v>
+        <v>2298.818513337938</v>
       </c>
       <c r="E74">
         <v>64.70399999999972</v>
@@ -7349,45 +7480,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M74">
-        <v>128.6081883064716</v>
+        <v>118.8992475064716</v>
       </c>
       <c r="N74">
-        <v>409.9918116935283</v>
+        <v>419.7007524935283</v>
       </c>
       <c r="O74">
-        <v>110.6977891572527</v>
+        <v>113.3192031732527</v>
       </c>
       <c r="P74">
-        <v>299.2940225362757</v>
+        <v>306.3815493202757</v>
       </c>
       <c r="Q74">
-        <v>669.6940225362757</v>
+        <v>676.7815493202756</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2000579248451443</v>
+        <v>0.1999947476545868</v>
       </c>
       <c r="T74">
         <v>2.824130954252425</v>
       </c>
       <c r="U74">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V74">
         <v>0.27</v>
       </c>
       <c r="W74">
-        <v>0.05028320728985866</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.187913748668345</v>
+        <v>4.529885691418563</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7398,13 +7529,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.09212019986217104</v>
+        <v>0.09066373953624798</v>
       </c>
       <c r="C75">
-        <v>734.9438264097009</v>
+        <v>804.4803708554207</v>
       </c>
       <c r="D75">
-        <v>2168.079826409701</v>
+        <v>2237.61637085542</v>
       </c>
       <c r="E75">
         <v>90.63599999999974</v>
@@ -7431,37 +7562,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M75">
-        <v>130.3944131440615</v>
+        <v>125.2832159440615</v>
       </c>
       <c r="N75">
-        <v>408.2055868559385</v>
+        <v>413.3167840559385</v>
       </c>
       <c r="O75">
-        <v>110.2155084511034</v>
+        <v>111.5955316951034</v>
       </c>
       <c r="P75">
-        <v>297.9900784048351</v>
+        <v>301.7212523608351</v>
       </c>
       <c r="Q75">
-        <v>668.3900784048351</v>
+        <v>672.1212523608351</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2052350316317564</v>
+        <v>0.2051697341283376</v>
       </c>
       <c r="T75">
         <v>2.918912648899353</v>
       </c>
       <c r="U75">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651871</v>
       </c>
       <c r="V75">
         <v>0.27</v>
       </c>
       <c r="W75">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985865</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.130545067179739</v>
+        <v>4.29905950243553</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7480,13 +7611,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09202027151900344</v>
+        <v>0.09054416048051342</v>
       </c>
       <c r="C76">
-        <v>713.6992204424068</v>
+        <v>784.5284149516697</v>
       </c>
       <c r="D76">
-        <v>2172.767220442407</v>
+        <v>2243.596414951669</v>
       </c>
       <c r="E76">
         <v>116.5679999999998</v>
@@ -7513,37 +7644,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M76">
-        <v>132.1806379816514</v>
+        <v>126.9994243816513</v>
       </c>
       <c r="N76">
-        <v>406.4193620183486</v>
+        <v>411.6005756183486</v>
       </c>
       <c r="O76">
-        <v>109.7332277449541</v>
+        <v>111.1321554169541</v>
       </c>
       <c r="P76">
-        <v>296.6861342733945</v>
+        <v>300.4684202013945</v>
       </c>
       <c r="Q76">
-        <v>667.0861342733945</v>
+        <v>670.8684202013944</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2108103774019539</v>
+        <v>0.2107427964846847</v>
       </c>
       <c r="T76">
         <v>3.020985243134507</v>
       </c>
       <c r="U76">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651871</v>
       </c>
       <c r="V76">
         <v>0.27</v>
       </c>
       <c r="W76">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985865</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.074726890596228</v>
+        <v>4.240964103753969</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7562,13 +7693,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.09192034317583582</v>
+        <v>0.09042458142477885</v>
       </c>
       <c r="C77">
-        <v>692.4749267055611</v>
+        <v>764.6085081116155</v>
       </c>
       <c r="D77">
-        <v>2177.474926705561</v>
+        <v>2249.608508111615</v>
       </c>
       <c r="E77">
         <v>142.4999999999998</v>
@@ -7595,37 +7726,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M77">
-        <v>133.9668628192412</v>
+        <v>128.7156328192412</v>
       </c>
       <c r="N77">
-        <v>404.6331371807587</v>
+        <v>409.8843671807587</v>
       </c>
       <c r="O77">
-        <v>109.2509470388049</v>
+        <v>110.6687791388049</v>
       </c>
       <c r="P77">
-        <v>295.3821901419539</v>
+        <v>299.2155880419538</v>
       </c>
       <c r="Q77">
-        <v>665.7821901419538</v>
+        <v>669.6155880419539</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2168317508337673</v>
+        <v>0.2167617038295394</v>
       </c>
       <c r="T77">
         <v>3.131223644908473</v>
       </c>
       <c r="U77">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651871</v>
       </c>
       <c r="V77">
         <v>0.27</v>
       </c>
       <c r="W77">
-        <v>0.05028320728985866</v>
+        <v>0.04831220728985865</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.020397198721612</v>
+        <v>4.184417915703916</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7644,13 +7775,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.09331837483266821</v>
+        <v>0.09030500236904428</v>
       </c>
       <c r="C78">
-        <v>602.4797324104497</v>
+        <v>744.7209086700473</v>
       </c>
       <c r="D78">
-        <v>2113.41173241045</v>
+        <v>2255.652908670047</v>
       </c>
       <c r="E78">
         <v>168.4319999999998</v>
@@ -7677,45 +7808,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M78">
-        <v>141.0743340568311</v>
+        <v>130.4318412568311</v>
       </c>
       <c r="N78">
-        <v>397.5256659431688</v>
+        <v>408.1681587431688</v>
       </c>
       <c r="O78">
-        <v>107.3319298046556</v>
+        <v>110.2054028606556</v>
       </c>
       <c r="P78">
-        <v>290.1937361385132</v>
+        <v>297.9627558825132</v>
       </c>
       <c r="Q78">
-        <v>660.5937361385132</v>
+        <v>668.3627558825133</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2233549053848985</v>
+        <v>0.2232821867864654</v>
       </c>
       <c r="T78">
         <v>3.250648580163603</v>
       </c>
       <c r="U78">
-        <v>0.07158110587651871</v>
+        <v>0.06618110587651871</v>
       </c>
       <c r="V78">
         <v>0.27</v>
       </c>
       <c r="W78">
-        <v>0.05225420728985865</v>
+        <v>0.04831220728985865</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.817845418877027</v>
+        <v>4.129359785234128</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7726,13 +7857,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.0932381564895006</v>
+        <v>0.09018542331330971</v>
       </c>
       <c r="C79">
-        <v>580.1215303855558</v>
+        <v>724.8658777456765</v>
       </c>
       <c r="D79">
-        <v>2116.985530385556</v>
+        <v>2261.729877745676</v>
       </c>
       <c r="E79">
         <v>194.3639999999998</v>
@@ -7759,45 +7890,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M79">
-        <v>142.930575294421</v>
+        <v>132.148049694421</v>
       </c>
       <c r="N79">
-        <v>395.6694247055789</v>
+        <v>406.4519503055789</v>
       </c>
       <c r="O79">
-        <v>106.8307446705063</v>
+        <v>109.7420265825063</v>
       </c>
       <c r="P79">
-        <v>288.8386800350726</v>
+        <v>296.7099237230726</v>
       </c>
       <c r="Q79">
-        <v>659.2386800350725</v>
+        <v>667.1099237230726</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2304452907665627</v>
+        <v>0.230369668261385</v>
       </c>
       <c r="T79">
         <v>3.38045829239744</v>
       </c>
       <c r="U79">
-        <v>0.07158110587651871</v>
+        <v>0.06618110587651871</v>
       </c>
       <c r="V79">
         <v>0.27</v>
       </c>
       <c r="W79">
-        <v>0.05225420728985865</v>
+        <v>0.04831220728985865</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.768263010839662</v>
+        <v>4.075731736075243</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7808,13 +7939,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.09315793814633298</v>
+        <v>0.09006584425757513</v>
       </c>
       <c r="C80">
-        <v>557.7754354820281</v>
+        <v>705.043679278745</v>
       </c>
       <c r="D80">
-        <v>2120.571435482028</v>
+        <v>2267.839679278745</v>
       </c>
       <c r="E80">
         <v>220.2959999999998</v>
@@ -7841,45 +7972,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M80">
-        <v>144.7868165320109</v>
+        <v>133.8642581320109</v>
       </c>
       <c r="N80">
-        <v>393.813183467989</v>
+        <v>404.735741867989</v>
       </c>
       <c r="O80">
-        <v>106.329559536357</v>
+        <v>109.278650304357</v>
       </c>
       <c r="P80">
-        <v>287.483623931632</v>
+        <v>295.457091563632</v>
       </c>
       <c r="Q80">
-        <v>657.883623931632</v>
+        <v>665.857091563632</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2381802566374693</v>
+        <v>0.2381014662340245</v>
       </c>
       <c r="T80">
         <v>3.522068887561626</v>
       </c>
       <c r="U80">
-        <v>0.07158110587651871</v>
+        <v>0.06618110587651871</v>
       </c>
       <c r="V80">
         <v>0.27</v>
       </c>
       <c r="W80">
-        <v>0.05225420728985865</v>
+        <v>0.04831220728985865</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y80">
-        <v>3.719951946598128</v>
+        <v>4.023478765099918</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7890,13 +8021,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.09307771980316537</v>
+        <v>0.09196471520184059</v>
       </c>
       <c r="C81">
-        <v>535.4415093280413</v>
+        <v>585.8297245562558</v>
       </c>
       <c r="D81">
-        <v>2124.169509328041</v>
+        <v>2174.557724556256</v>
       </c>
       <c r="E81">
         <v>246.2280000000001</v>
@@ -7923,37 +8054,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M81">
-        <v>146.6430577696008</v>
+        <v>142.7506645696008</v>
       </c>
       <c r="N81">
-        <v>391.9569422303991</v>
+        <v>395.8493354303992</v>
       </c>
       <c r="O81">
-        <v>105.8283744022078</v>
+        <v>106.8793205662078</v>
       </c>
       <c r="P81">
-        <v>286.1285678281914</v>
+        <v>288.9700148641914</v>
       </c>
       <c r="Q81">
-        <v>656.5285678281914</v>
+        <v>659.3700148641915</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2466518859246526</v>
+        <v>0.2465696259183441</v>
       </c>
       <c r="T81">
         <v>3.677166206074782</v>
       </c>
       <c r="U81">
-        <v>0.07158110587651871</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V81">
         <v>0.27</v>
       </c>
       <c r="W81">
-        <v>0.05225420728985865</v>
+        <v>0.05086720728985866</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.672863947274101</v>
+        <v>3.773012207150849</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7972,13 +8103,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.09299750145999776</v>
+        <v>0.09187068614610602</v>
       </c>
       <c r="C82">
-        <v>513.119813970754</v>
+        <v>564.3359395381617</v>
       </c>
       <c r="D82">
-        <v>2127.779813970754</v>
+        <v>2178.995939538162</v>
       </c>
       <c r="E82">
         <v>272.1599999999999</v>
@@ -8005,37 +8136,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M82">
-        <v>148.4992990071906</v>
+        <v>144.5576350071907</v>
       </c>
       <c r="N82">
-        <v>390.1007009928093</v>
+        <v>394.0423649928092</v>
       </c>
       <c r="O82">
-        <v>105.3271892680585</v>
+        <v>106.3914385480585</v>
       </c>
       <c r="P82">
-        <v>284.7735117247507</v>
+        <v>287.6509264447507</v>
       </c>
       <c r="Q82">
-        <v>655.1735117247508</v>
+        <v>658.0509264447508</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2559706781405542</v>
+        <v>0.2558846015710955</v>
       </c>
       <c r="T82">
         <v>3.847773256439253</v>
       </c>
       <c r="U82">
-        <v>0.07158110587651871</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V82">
         <v>0.27</v>
       </c>
       <c r="W82">
-        <v>0.05225420728985865</v>
+        <v>0.05086720728985866</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.626953147933175</v>
+        <v>3.725849554561463</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8054,13 +8185,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09291728311683013</v>
+        <v>0.09177665709037144</v>
       </c>
       <c r="C83">
-        <v>490.8104118798697</v>
+        <v>542.8603081306305</v>
       </c>
       <c r="D83">
-        <v>2131.40241187987</v>
+        <v>2183.452308130631</v>
       </c>
       <c r="E83">
         <v>298.0920000000001</v>
@@ -8087,37 +8218,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M83">
-        <v>150.3555402447805</v>
+        <v>146.3646054447806</v>
       </c>
       <c r="N83">
-        <v>388.2444597552194</v>
+        <v>392.2353945552194</v>
       </c>
       <c r="O83">
-        <v>104.8260041339092</v>
+        <v>105.9035565299092</v>
       </c>
       <c r="P83">
-        <v>283.4184556213102</v>
+        <v>286.3318380253102</v>
       </c>
       <c r="Q83">
-        <v>653.8184556213102</v>
+        <v>656.7318380253103</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2662703958528665</v>
+        <v>0.2661801009767681</v>
       </c>
       <c r="T83">
         <v>4.036338943684195</v>
       </c>
       <c r="U83">
-        <v>0.07158110587651871</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V83">
         <v>0.27</v>
       </c>
       <c r="W83">
-        <v>0.05225420728985865</v>
+        <v>0.05086720728985866</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.582175948575975</v>
+        <v>3.679851411912556</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8136,13 +8267,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09283706477366252</v>
+        <v>0.09168262803463689</v>
       </c>
       <c r="C84">
-        <v>468.513365951243</v>
+        <v>521.4029419423637</v>
       </c>
       <c r="D84">
-        <v>2135.037365951243</v>
+        <v>2187.926941942364</v>
       </c>
       <c r="E84">
         <v>324.0239999999999</v>
@@ -8169,37 +8300,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M84">
-        <v>152.2117814823704</v>
+        <v>148.1715758823704</v>
       </c>
       <c r="N84">
-        <v>386.3882185176295</v>
+        <v>390.4284241176294</v>
       </c>
       <c r="O84">
-        <v>104.32481899976</v>
+        <v>105.41567451176</v>
       </c>
       <c r="P84">
-        <v>282.0633995178695</v>
+        <v>285.0127496058695</v>
       </c>
       <c r="Q84">
-        <v>652.4633995178696</v>
+        <v>655.4127496058695</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2777145266443247</v>
+        <v>0.2776195447608489</v>
       </c>
       <c r="T84">
         <v>4.245856373956353</v>
       </c>
       <c r="U84">
-        <v>0.07158110587651871</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V84">
         <v>0.27</v>
       </c>
       <c r="W84">
-        <v>0.05225420728985865</v>
+        <v>0.05086720728985866</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.538490876032366</v>
+        <v>3.634975175181915</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8218,13 +8349,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09560457643049494</v>
+        <v>0.09158859897890231</v>
       </c>
       <c r="C85">
-        <v>323.9428547636444</v>
+        <v>499.9639534988401</v>
       </c>
       <c r="D85">
-        <v>2016.398854763645</v>
+        <v>2192.41995349884</v>
       </c>
       <c r="E85">
         <v>349.9560000000001</v>
@@ -8251,45 +8382,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M85">
-        <v>164.1840959199603</v>
+        <v>149.9785463199603</v>
       </c>
       <c r="N85">
-        <v>374.4159040800396</v>
+        <v>388.6214536800396</v>
       </c>
       <c r="O85">
-        <v>101.0922941016107</v>
+        <v>104.9277924936107</v>
       </c>
       <c r="P85">
-        <v>273.3236099784289</v>
+        <v>283.6936611864289</v>
       </c>
       <c r="Q85">
-        <v>643.7236099784288</v>
+        <v>654.093661186429</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2905050257641898</v>
+        <v>0.2904048054607039</v>
       </c>
       <c r="T85">
         <v>4.480022913672295</v>
       </c>
       <c r="U85">
-        <v>0.07628110587651871</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V85">
         <v>0.27</v>
       </c>
       <c r="W85">
-        <v>0.05568520728985865</v>
+        <v>0.05086720728985866</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.280463902317111</v>
+        <v>3.591180293553218</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8300,13 +8431,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.09555866808732733</v>
+        <v>0.09149456992316776</v>
       </c>
       <c r="C86">
-        <v>299.8712247081303</v>
+        <v>478.5434562517439</v>
       </c>
       <c r="D86">
-        <v>2018.25922470813</v>
+        <v>2196.931456251743</v>
       </c>
       <c r="E86">
         <v>375.8879999999995</v>
@@ -8333,45 +8464,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M86">
-        <v>166.1622175575502</v>
+        <v>151.7855167575502</v>
       </c>
       <c r="N86">
-        <v>372.4377824424498</v>
+        <v>386.8144832424497</v>
       </c>
       <c r="O86">
-        <v>100.5582012594614</v>
+        <v>104.4399104754614</v>
       </c>
       <c r="P86">
-        <v>271.8795811829883</v>
+        <v>282.3745727669883</v>
       </c>
       <c r="Q86">
-        <v>642.2795811829883</v>
+        <v>652.7745727669883</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3048943372740378</v>
+        <v>0.3047882237480405</v>
       </c>
       <c r="T86">
         <v>4.743460270852726</v>
       </c>
       <c r="U86">
-        <v>0.07628110587651871</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V86">
         <v>0.27</v>
       </c>
       <c r="W86">
-        <v>0.05568520728985865</v>
+        <v>0.05086720728985866</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>3.241410760622861</v>
+        <v>3.548428147201394</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8382,13 +8513,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.09551275974415969</v>
+        <v>0.09140054086743318</v>
       </c>
       <c r="C87">
-        <v>275.8030306518353</v>
+        <v>457.1415645885172</v>
       </c>
       <c r="D87">
-        <v>2020.123030651835</v>
+        <v>2201.461564588517</v>
       </c>
       <c r="E87">
         <v>401.8199999999997</v>
@@ -8415,45 +8546,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M87">
-        <v>168.1403391951401</v>
+        <v>153.5924871951401</v>
       </c>
       <c r="N87">
-        <v>370.4596608048598</v>
+        <v>385.0075128048599</v>
       </c>
       <c r="O87">
-        <v>100.0241084173122</v>
+        <v>103.9520284573122</v>
       </c>
       <c r="P87">
-        <v>270.4355523875477</v>
+        <v>281.0554843475477</v>
       </c>
       <c r="Q87">
-        <v>640.8355523875478</v>
+        <v>651.4554843475478</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3212022236518656</v>
+        <v>0.3210894311403555</v>
       </c>
       <c r="T87">
         <v>5.04202260899055</v>
       </c>
       <c r="U87">
-        <v>0.07628110587651871</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V87">
         <v>0.27</v>
       </c>
       <c r="W87">
-        <v>0.05568520728985865</v>
+        <v>0.05086720728985866</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>3.203276516380238</v>
+        <v>3.506681933704907</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8464,13 +8595,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.09546685140099209</v>
+        <v>0.09306435181169861</v>
       </c>
       <c r="C88">
-        <v>251.7382821227043</v>
+        <v>353.7131914416955</v>
       </c>
       <c r="D88">
-        <v>2021.990282122704</v>
+        <v>2123.965191441695</v>
       </c>
       <c r="E88">
         <v>427.7519999999995</v>
@@ -8497,37 +8628,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M88">
-        <v>170.1184608327299</v>
+        <v>161.6438832327299</v>
       </c>
       <c r="N88">
-        <v>368.48153916727</v>
+        <v>376.95611676727</v>
       </c>
       <c r="O88">
-        <v>99.4900155751629</v>
+        <v>101.7781515271629</v>
       </c>
       <c r="P88">
-        <v>268.9915235921071</v>
+        <v>275.1779652401071</v>
       </c>
       <c r="Q88">
-        <v>639.3915235921072</v>
+        <v>645.5779652401071</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3398398080836689</v>
+        <v>0.3397193824458584</v>
       </c>
       <c r="T88">
         <v>5.383236709719493</v>
       </c>
       <c r="U88">
-        <v>0.07628110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V88">
         <v>0.27</v>
       </c>
       <c r="W88">
-        <v>0.05568520728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.16602911502698</v>
+        <v>3.332015967622728</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8546,13 +8677,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.09542094305782448</v>
+        <v>0.09299076275596405</v>
       </c>
       <c r="C89">
-        <v>227.6769886839456</v>
+        <v>331.0932928726374</v>
       </c>
       <c r="D89">
-        <v>2023.860988683946</v>
+        <v>2127.277292872637</v>
       </c>
       <c r="E89">
         <v>453.6839999999997</v>
@@ -8579,37 +8710,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M89">
-        <v>172.0965824703198</v>
+        <v>163.5234632703198</v>
       </c>
       <c r="N89">
-        <v>366.5034175296801</v>
+        <v>375.0765367296801</v>
       </c>
       <c r="O89">
-        <v>98.95592273301362</v>
+        <v>101.2706649170136</v>
       </c>
       <c r="P89">
-        <v>267.5474947966665</v>
+        <v>273.8058718126665</v>
       </c>
       <c r="Q89">
-        <v>637.9474947966664</v>
+        <v>644.2058718126666</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.361344713197288</v>
+        <v>0.361215480106054</v>
       </c>
       <c r="T89">
         <v>5.776945287483657</v>
       </c>
       <c r="U89">
-        <v>0.07628110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V89">
         <v>0.27</v>
       </c>
       <c r="W89">
-        <v>0.05568520728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.129637975773796</v>
+        <v>3.293716933512123</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8628,13 +8759,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.09537503471465686</v>
+        <v>0.09291717370022949</v>
       </c>
       <c r="C90">
-        <v>203.6191599341896</v>
+        <v>308.483740188005</v>
       </c>
       <c r="D90">
-        <v>2025.73515993419</v>
+        <v>2130.599740188005</v>
       </c>
       <c r="E90">
         <v>479.616</v>
@@ -8661,37 +8792,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M90">
-        <v>174.0747041079097</v>
+        <v>165.4030433079097</v>
       </c>
       <c r="N90">
-        <v>364.5252958920902</v>
+        <v>373.1969566920902</v>
       </c>
       <c r="O90">
-        <v>98.42182989086436</v>
+        <v>100.7631783068644</v>
       </c>
       <c r="P90">
-        <v>266.1034660012258</v>
+        <v>272.4337783852259</v>
       </c>
       <c r="Q90">
-        <v>636.5034660012259</v>
+        <v>642.833778385226</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3864337691631771</v>
+        <v>0.3862942607096156</v>
       </c>
       <c r="T90">
         <v>6.23627196154185</v>
       </c>
       <c r="U90">
-        <v>0.07628110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V90">
         <v>0.27</v>
       </c>
       <c r="W90">
-        <v>0.05568520728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.094073907867275</v>
+        <v>3.256288331994939</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8710,13 +8841,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.09532912637148924</v>
+        <v>0.09284358464449492</v>
       </c>
       <c r="C91">
-        <v>179.564805507654</v>
+        <v>285.884581939194</v>
       </c>
       <c r="D91">
-        <v>2027.612805507654</v>
+        <v>2133.932581939194</v>
       </c>
       <c r="E91">
         <v>505.5479999999998</v>
@@ -8743,37 +8874,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M91">
-        <v>176.0528257454996</v>
+        <v>167.2826233454996</v>
       </c>
       <c r="N91">
-        <v>362.5471742545003</v>
+        <v>371.3173766545003</v>
       </c>
       <c r="O91">
-        <v>97.8877370487151</v>
+        <v>100.2556916967151</v>
       </c>
       <c r="P91">
-        <v>264.6594372057852</v>
+        <v>271.0616849577852</v>
       </c>
       <c r="Q91">
-        <v>635.0594372057852</v>
+        <v>641.4616849577853</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4160844716683187</v>
+        <v>0.4159328196047339</v>
       </c>
       <c r="T91">
         <v>6.779112576337895</v>
       </c>
       <c r="U91">
-        <v>0.07628110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V91">
         <v>0.27</v>
       </c>
       <c r="W91">
-        <v>0.05568520728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.059309032497981</v>
+        <v>3.219700822646681</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8792,13 +8923,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.09528321802832164</v>
+        <v>0.09276999558876035</v>
       </c>
       <c r="C92">
-        <v>155.5139350743075</v>
+        <v>263.2958669818627</v>
       </c>
       <c r="D92">
-        <v>2029.493935074308</v>
+        <v>2137.275866981863</v>
       </c>
       <c r="E92">
         <v>531.48</v>
@@ -8825,37 +8956,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M92">
-        <v>178.0309473830895</v>
+        <v>169.1622033830895</v>
       </c>
       <c r="N92">
-        <v>360.5690526169104</v>
+        <v>369.4377966169104</v>
       </c>
       <c r="O92">
-        <v>97.35364420656582</v>
+        <v>99.74820508656582</v>
       </c>
       <c r="P92">
-        <v>263.2154084103446</v>
+        <v>269.6895915303446</v>
       </c>
       <c r="Q92">
-        <v>633.6154084103446</v>
+        <v>640.0895915303447</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4516653146744886</v>
+        <v>0.4514990902788757</v>
       </c>
       <c r="T92">
         <v>7.430521314093149</v>
       </c>
       <c r="U92">
-        <v>0.07628110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V92">
         <v>0.27</v>
       </c>
       <c r="W92">
-        <v>0.05568520728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.025316709914669</v>
+        <v>3.183926369061718</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8874,13 +9005,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.101415299685154</v>
+        <v>0.0926964065330258</v>
       </c>
       <c r="C93">
-        <v>-94.18782976333114</v>
+        <v>240.7176444783263</v>
       </c>
       <c r="D93">
-        <v>1805.724170236669</v>
+        <v>2140.629644478326</v>
       </c>
       <c r="E93">
         <v>557.4119999999998</v>
@@ -8907,45 +9038,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M93">
-        <v>201.9553206206794</v>
+        <v>171.0417834206794</v>
       </c>
       <c r="N93">
-        <v>336.6446793793206</v>
+        <v>367.5582165793205</v>
       </c>
       <c r="O93">
-        <v>90.89406343241656</v>
+        <v>99.24071847641655</v>
       </c>
       <c r="P93">
-        <v>245.750615946904</v>
+        <v>268.317498102904</v>
       </c>
       <c r="Q93">
-        <v>616.1506159469041</v>
+        <v>638.7174981029041</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4951530116820297</v>
+        <v>0.4949689766583826</v>
       </c>
       <c r="T93">
         <v>8.22668754912735</v>
       </c>
       <c r="U93">
-        <v>0.08558110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V93">
         <v>0.27</v>
       </c>
       <c r="W93">
-        <v>0.06247420728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.666926517928291</v>
+        <v>3.148938167203896</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8956,13 +9087,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.1014372813419864</v>
+        <v>0.09262281747729123</v>
       </c>
       <c r="C94">
-        <v>-120.8332508379544</v>
+        <v>218.1499638999626</v>
       </c>
       <c r="D94">
-        <v>1805.010749162046</v>
+        <v>2143.993963899963</v>
       </c>
       <c r="E94">
         <v>583.3440000000001</v>
@@ -8989,45 +9120,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M94">
-        <v>204.1746098582693</v>
+        <v>172.9213634582693</v>
       </c>
       <c r="N94">
-        <v>334.4253901417306</v>
+        <v>365.6786365417306</v>
       </c>
       <c r="O94">
-        <v>90.29485533826728</v>
+        <v>98.73323186626727</v>
       </c>
       <c r="P94">
-        <v>244.1305348034634</v>
+        <v>266.9454046754634</v>
       </c>
       <c r="Q94">
-        <v>614.5305348034634</v>
+        <v>637.3454046754634</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.5495126329414559</v>
+        <v>0.549306334632766</v>
       </c>
       <c r="T94">
         <v>9.221895342920101</v>
       </c>
       <c r="U94">
-        <v>0.08558110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V94">
         <v>0.27</v>
       </c>
       <c r="W94">
-        <v>0.06247420728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.637938186211678</v>
+        <v>3.11471057842994</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9038,13 +9169,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1014592629988188</v>
+        <v>0.09254922842155665</v>
       </c>
       <c r="C95">
-        <v>-147.4781084061128</v>
+        <v>195.5928750296462</v>
       </c>
       <c r="D95">
-        <v>1804.297891593887</v>
+        <v>2147.368875029646</v>
       </c>
       <c r="E95">
         <v>609.2759999999998</v>
@@ -9071,45 +9202,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M95">
-        <v>206.3938990958591</v>
+        <v>174.8009434958591</v>
       </c>
       <c r="N95">
-        <v>332.2061009041408</v>
+        <v>363.7990565041408</v>
       </c>
       <c r="O95">
-        <v>89.69564724411802</v>
+        <v>98.22574525611803</v>
       </c>
       <c r="P95">
-        <v>242.5104536600228</v>
+        <v>265.5733112480228</v>
       </c>
       <c r="Q95">
-        <v>612.9104536600228</v>
+        <v>635.9733112480228</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.6194035745607184</v>
+        <v>0.6191686520284019</v>
       </c>
       <c r="T95">
         <v>10.50144822065364</v>
       </c>
       <c r="U95">
-        <v>0.08558110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V95">
         <v>0.27</v>
       </c>
       <c r="W95">
-        <v>0.06247420728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y95">
-        <v>2.60957325947822</v>
+        <v>3.081219066833921</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9120,13 +9251,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1014812446556512</v>
+        <v>0.09247563936582209</v>
       </c>
       <c r="C96">
-        <v>-174.1224031351858</v>
+        <v>173.0464279642015</v>
       </c>
       <c r="D96">
-        <v>1803.585596864814</v>
+        <v>2150.754427964202</v>
       </c>
       <c r="E96">
         <v>635.2080000000001</v>
@@ -9153,45 +9284,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M96">
-        <v>208.613188333449</v>
+        <v>176.680523533449</v>
       </c>
       <c r="N96">
-        <v>329.9868116665509</v>
+        <v>361.9194764665509</v>
       </c>
       <c r="O96">
-        <v>89.09643914996875</v>
+        <v>97.71825864596876</v>
       </c>
       <c r="P96">
-        <v>240.8903725165821</v>
+        <v>264.2012178205821</v>
       </c>
       <c r="Q96">
-        <v>611.2903725165821</v>
+        <v>634.6012178205822</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.7125914967197349</v>
+        <v>0.7123184085559165</v>
       </c>
       <c r="T96">
         <v>12.20751872429835</v>
       </c>
       <c r="U96">
-        <v>0.08558110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V96">
         <v>0.27</v>
       </c>
       <c r="W96">
-        <v>0.06247420728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y96">
-        <v>2.581811841824196</v>
+        <v>3.048440140591006</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9202,13 +9333,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1015032263124836</v>
+        <v>0.09240205031008752</v>
       </c>
       <c r="C97">
-        <v>-200.7661356914959</v>
+        <v>150.5106731168867</v>
       </c>
       <c r="D97">
-        <v>1802.873864308504</v>
+        <v>2154.150673116887</v>
       </c>
       <c r="E97">
         <v>661.1399999999999</v>
@@ -9235,45 +9366,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M97">
-        <v>210.8324775710389</v>
+        <v>178.5601035710389</v>
       </c>
       <c r="N97">
-        <v>327.767522428961</v>
+        <v>360.039896428961</v>
       </c>
       <c r="O97">
-        <v>88.49723105581947</v>
+        <v>97.21077203581947</v>
       </c>
       <c r="P97">
-        <v>239.2702913731415</v>
+        <v>262.8291243931416</v>
       </c>
       <c r="Q97">
-        <v>609.6702913731416</v>
+        <v>633.2291243931415</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.8430545877423583</v>
+        <v>0.8427280676944371</v>
       </c>
       <c r="T97">
         <v>14.59601742940096</v>
       </c>
       <c r="U97">
-        <v>0.08558110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V97">
         <v>0.27</v>
       </c>
       <c r="W97">
-        <v>0.06247420728985865</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.554634875068152</v>
+        <v>3.016351297005838</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9284,13 +9415,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.101525207969316</v>
+        <v>0.09779470125435297</v>
       </c>
       <c r="C98">
-        <v>-227.4093067403173</v>
+        <v>-98.83991341651063</v>
       </c>
       <c r="D98">
-        <v>1802.162693259683</v>
+        <v>1930.732086583489</v>
       </c>
       <c r="E98">
         <v>687.0719999999997</v>
@@ -9317,37 +9448,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M98">
-        <v>213.0517668086288</v>
+        <v>199.8575652086288</v>
       </c>
       <c r="N98">
-        <v>325.5482331913711</v>
+        <v>338.7424347913711</v>
       </c>
       <c r="O98">
-        <v>87.89802296167021</v>
+        <v>91.46045739367021</v>
       </c>
       <c r="P98">
-        <v>237.6502102297009</v>
+        <v>247.2819773977009</v>
       </c>
       <c r="Q98">
-        <v>608.050210229701</v>
+        <v>617.681977397701</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.038749224276291</v>
+        <v>1.038342556402216</v>
       </c>
       <c r="T98">
         <v>18.17876548705482</v>
       </c>
       <c r="U98">
-        <v>0.08558110587651871</v>
+        <v>0.08028110587651871</v>
       </c>
       <c r="V98">
         <v>0.27</v>
       </c>
       <c r="W98">
-        <v>0.06247420728985865</v>
+        <v>0.05860520728985866</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.528024095119526</v>
+        <v>2.694919251306611</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9366,13 +9497,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1015471896261484</v>
+        <v>0.0977780521986184</v>
       </c>
       <c r="C99">
-        <v>-254.0519169458721</v>
+        <v>-124.1534818909272</v>
       </c>
       <c r="D99">
-        <v>1801.452083054128</v>
+        <v>1931.350518109072</v>
       </c>
       <c r="E99">
         <v>713.0039999999995</v>
@@ -9399,37 +9530,37 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M99">
-        <v>215.2710560462186</v>
+        <v>201.9394148462186</v>
       </c>
       <c r="N99">
-        <v>323.3289439537813</v>
+        <v>336.6605851537813</v>
       </c>
       <c r="O99">
-        <v>87.29881486752095</v>
+        <v>90.89835799152097</v>
       </c>
       <c r="P99">
-        <v>236.0301290862603</v>
+        <v>245.7622271622603</v>
       </c>
       <c r="Q99">
-        <v>606.4301290862604</v>
+        <v>616.1622271622604</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.364906951832848</v>
+        <v>1.364366704248516</v>
       </c>
       <c r="T99">
         <v>24.15001224981131</v>
       </c>
       <c r="U99">
-        <v>0.08558110587651871</v>
+        <v>0.08028110587651871</v>
       </c>
       <c r="V99">
         <v>0.27</v>
       </c>
       <c r="W99">
-        <v>0.06247420728985865</v>
+        <v>0.05860520728985866</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.501961991046128</v>
+        <v>2.667136578612729</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9448,13 +9579,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1049315512829807</v>
+        <v>0.09776140314288384</v>
       </c>
       <c r="C100">
-        <v>-383.0890312922293</v>
+        <v>-149.4666540596127</v>
       </c>
       <c r="D100">
-        <v>1698.34696870777</v>
+        <v>1931.969345940387</v>
       </c>
       <c r="E100">
         <v>738.9359999999997</v>
@@ -9481,45 +9612,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M100">
-        <v>229.4346244838086</v>
+        <v>204.0212644838085</v>
       </c>
       <c r="N100">
-        <v>309.1653755161914</v>
+        <v>334.5787355161914</v>
       </c>
       <c r="O100">
-        <v>83.47465138937167</v>
+        <v>90.33625858937168</v>
       </c>
       <c r="P100">
-        <v>225.6907241268197</v>
+        <v>244.2424769268197</v>
       </c>
       <c r="Q100">
-        <v>596.0907241268197</v>
+        <v>614.6424769268198</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.017222406945962</v>
+        <v>2.016414999941116</v>
       </c>
       <c r="T100">
         <v>36.09250577532428</v>
       </c>
       <c r="U100">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651871</v>
       </c>
       <c r="V100">
         <v>0.27</v>
       </c>
       <c r="W100">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985866</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y100">
-        <v>2.347509671706109</v>
+        <v>2.639920899239129</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9530,13 +9661,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1049878429398131</v>
+        <v>0.09774475408714928</v>
       </c>
       <c r="C101">
-        <v>-410.6362745583515</v>
+        <v>-174.779429541501</v>
       </c>
       <c r="D101">
-        <v>1696.731725441648</v>
+        <v>1932.588570458498</v>
       </c>
       <c r="E101">
         <v>764.8679999999995</v>
@@ -9563,45 +9694,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M101">
-        <v>231.7757941213984</v>
+        <v>206.1031141213984</v>
       </c>
       <c r="N101">
-        <v>306.8242058786014</v>
+        <v>332.4968858786015</v>
       </c>
       <c r="O101">
-        <v>82.8425355872224</v>
+        <v>89.77415918722241</v>
       </c>
       <c r="P101">
-        <v>223.981670291379</v>
+        <v>242.7227266913791</v>
       </c>
       <c r="Q101">
-        <v>594.3816702913791</v>
+        <v>613.1227266913792</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.974168772285304</v>
+        <v>3.972559887018916</v>
       </c>
       <c r="T101">
         <v>71.91998635186322</v>
       </c>
       <c r="U101">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651871</v>
       </c>
       <c r="V101">
         <v>0.27</v>
       </c>
       <c r="W101">
-        <v>0.06590520728985866</v>
+        <v>0.05860520728985866</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y101">
-        <v>2.323797452799987</v>
+        <v>2.613255031570047</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/chile/chile_steel.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_steel.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0993930106048713</v>
+        <v>0.09921868154913673</v>
       </c>
       <c r="C2">
-        <v>2333.051683607365</v>
+        <v>2313.232615540187</v>
       </c>
       <c r="D2">
-        <v>1873.151683607365</v>
+        <v>1879.264615540186</v>
       </c>
       <c r="E2">
-        <v>-1802.4</v>
+        <v>-1776.468</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25.932</v>
       </c>
       <c r="G2">
         <v>459.9</v>
@@ -1576,28 +1576,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.521718437589883</v>
       </c>
       <c r="N2">
-        <v>538.5999999999999</v>
+        <v>537.07828156241</v>
       </c>
       <c r="O2">
-        <v>145.422</v>
+        <v>145.0111360218507</v>
       </c>
       <c r="P2">
-        <v>393.1779999999999</v>
+        <v>392.0671455405593</v>
       </c>
       <c r="Q2">
-        <v>763.578</v>
+        <v>762.4671455405594</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0993930106048713</v>
+        <v>0.09978819139013953</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.9888126851800831</v>
       </c>
       <c r="U2">
         <v>0.05868110587651872</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>353.9419558147966</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09921868154913673</v>
+        <v>0.09904435249340217</v>
       </c>
       <c r="C3">
-        <v>2313.232615540187</v>
+        <v>2293.453576569115</v>
       </c>
       <c r="D3">
-        <v>1879.264615540186</v>
+        <v>1885.417576569115</v>
       </c>
       <c r="E3">
-        <v>-1776.468</v>
+        <v>-1750.536</v>
       </c>
       <c r="F3">
-        <v>25.932</v>
+        <v>51.864</v>
       </c>
       <c r="G3">
         <v>459.9</v>
@@ -1658,28 +1658,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M3">
-        <v>1.521718437589883</v>
+        <v>3.043436875179767</v>
       </c>
       <c r="N3">
-        <v>537.07828156241</v>
+        <v>535.5565631248202</v>
       </c>
       <c r="O3">
-        <v>145.0111360218507</v>
+        <v>144.6002720437015</v>
       </c>
       <c r="P3">
-        <v>392.0671455405593</v>
+        <v>390.9562910811187</v>
       </c>
       <c r="Q3">
-        <v>762.4671455405594</v>
+        <v>761.3562910811188</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09978819139013953</v>
+        <v>0.1001914370893928</v>
       </c>
       <c r="T3">
-        <v>0.9888126851800831</v>
+        <v>0.9961982717759477</v>
       </c>
       <c r="U3">
         <v>0.05868110587651872</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>353.9419558147966</v>
+        <v>176.9709779073983</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09904435249340217</v>
+        <v>0.0988700234376676</v>
       </c>
       <c r="C4">
-        <v>2293.453576569115</v>
+        <v>2273.714961167385</v>
       </c>
       <c r="D4">
-        <v>1885.417576569115</v>
+        <v>1891.610961167385</v>
       </c>
       <c r="E4">
-        <v>-1750.536</v>
+        <v>-1724.604</v>
       </c>
       <c r="F4">
-        <v>51.864</v>
+        <v>77.79599999999999</v>
       </c>
       <c r="G4">
         <v>459.9</v>
@@ -1740,28 +1740,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M4">
-        <v>3.043436875179767</v>
+        <v>4.565155312769649</v>
       </c>
       <c r="N4">
-        <v>535.5565631248202</v>
+        <v>534.0348446872302</v>
       </c>
       <c r="O4">
-        <v>144.6002720437015</v>
+        <v>144.1894080655522</v>
       </c>
       <c r="P4">
-        <v>390.9562910811187</v>
+        <v>389.8454366216781</v>
       </c>
       <c r="Q4">
-        <v>761.3562910811188</v>
+        <v>760.2454366216781</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1001914370893928</v>
+        <v>0.1006029971329607</v>
       </c>
       <c r="T4">
-        <v>0.9961982717759477</v>
+        <v>1.003736138507809</v>
       </c>
       <c r="U4">
         <v>0.05868110587651872</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>176.9709779073983</v>
+        <v>117.9806519382656</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0988700234376676</v>
+        <v>0.09869569438193301</v>
       </c>
       <c r="C5">
-        <v>2273.714961167385</v>
+        <v>2254.017169008508</v>
       </c>
       <c r="D5">
-        <v>1891.610961167385</v>
+        <v>1897.845169008508</v>
       </c>
       <c r="E5">
-        <v>-1724.604</v>
+        <v>-1698.672</v>
       </c>
       <c r="F5">
-        <v>77.79599999999999</v>
+        <v>103.728</v>
       </c>
       <c r="G5">
         <v>459.9</v>
@@ -1822,28 +1822,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M5">
-        <v>4.565155312769649</v>
+        <v>6.086873750359533</v>
       </c>
       <c r="N5">
-        <v>534.0348446872302</v>
+        <v>532.5131262496403</v>
       </c>
       <c r="O5">
-        <v>144.1894080655522</v>
+        <v>143.7785440874029</v>
       </c>
       <c r="P5">
-        <v>389.8454366216781</v>
+        <v>388.7345821622374</v>
       </c>
       <c r="Q5">
-        <v>760.2454366216781</v>
+        <v>759.1345821622374</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1006029971329607</v>
+        <v>0.1010231313441028</v>
       </c>
       <c r="T5">
-        <v>1.003736138507809</v>
+        <v>1.011431044129918</v>
       </c>
       <c r="U5">
         <v>0.05868110587651872</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>117.9806519382656</v>
+        <v>88.48548895369916</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09869569438193301</v>
+        <v>0.09852136532619847</v>
       </c>
       <c r="C6">
-        <v>2254.017169008508</v>
+        <v>2234.360605052256</v>
       </c>
       <c r="D6">
-        <v>1897.845169008508</v>
+        <v>1904.120605052256</v>
       </c>
       <c r="E6">
-        <v>-1698.672</v>
+        <v>-1672.74</v>
       </c>
       <c r="F6">
-        <v>103.728</v>
+        <v>129.66</v>
       </c>
       <c r="G6">
         <v>459.9</v>
@@ -1904,28 +1904,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M6">
-        <v>6.086873750359533</v>
+        <v>7.608592187949417</v>
       </c>
       <c r="N6">
-        <v>532.5131262496403</v>
+        <v>530.9914078120505</v>
       </c>
       <c r="O6">
-        <v>143.7785440874029</v>
+        <v>143.3676801092537</v>
       </c>
       <c r="P6">
-        <v>388.7345821622374</v>
+        <v>387.6237277027968</v>
       </c>
       <c r="Q6">
-        <v>759.1345821622374</v>
+        <v>758.0237277027968</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1010231313441028</v>
+        <v>0.1014521104860058</v>
       </c>
       <c r="T6">
-        <v>1.011431044129918</v>
+        <v>1.019287947765124</v>
       </c>
       <c r="U6">
         <v>0.05868110587651872</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>88.48548895369916</v>
+        <v>70.78839116295934</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09852136532619847</v>
+        <v>0.0983470362704639</v>
       </c>
       <c r="C7">
-        <v>2234.360605052256</v>
+        <v>2214.745679632351</v>
       </c>
       <c r="D7">
-        <v>1904.120605052256</v>
+        <v>1910.437679632352</v>
       </c>
       <c r="E7">
-        <v>-1672.74</v>
+        <v>-1646.808</v>
       </c>
       <c r="F7">
-        <v>129.66</v>
+        <v>155.592</v>
       </c>
       <c r="G7">
         <v>459.9</v>
@@ -1986,28 +1986,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M7">
-        <v>7.608592187949417</v>
+        <v>9.1303106255393</v>
       </c>
       <c r="N7">
-        <v>530.9914078120505</v>
+        <v>529.4696893744606</v>
       </c>
       <c r="O7">
-        <v>143.3676801092537</v>
+        <v>142.9568161311044</v>
       </c>
       <c r="P7">
-        <v>387.6237277027968</v>
+        <v>386.5128732433562</v>
       </c>
       <c r="Q7">
-        <v>758.0237277027968</v>
+        <v>756.9128732433562</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1014521104860058</v>
+        <v>0.101890216843694</v>
       </c>
       <c r="T7">
-        <v>1.019287947765124</v>
+        <v>1.027312019562781</v>
       </c>
       <c r="U7">
         <v>0.05868110587651872</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>70.78839116295934</v>
+        <v>58.99032596913278</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0983470362704639</v>
+        <v>0.09817270721472934</v>
       </c>
       <c r="C8">
-        <v>2214.745679632351</v>
+        <v>2195.1728085459</v>
       </c>
       <c r="D8">
-        <v>1910.437679632352</v>
+        <v>1916.7968085459</v>
       </c>
       <c r="E8">
-        <v>-1646.808</v>
+        <v>-1620.876</v>
       </c>
       <c r="F8">
-        <v>155.592</v>
+        <v>181.524</v>
       </c>
       <c r="G8">
         <v>459.9</v>
@@ -2068,28 +2068,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M8">
-        <v>9.130310625539298</v>
+        <v>10.65202906312918</v>
       </c>
       <c r="N8">
-        <v>529.4696893744606</v>
+        <v>527.9479709368708</v>
       </c>
       <c r="O8">
-        <v>142.9568161311044</v>
+        <v>142.5459521529551</v>
       </c>
       <c r="P8">
-        <v>386.5128732433562</v>
+        <v>385.4020187839157</v>
       </c>
       <c r="Q8">
-        <v>756.9128732433562</v>
+        <v>755.8020187839156</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.101890216843694</v>
+        <v>0.102337744843483</v>
       </c>
       <c r="T8">
-        <v>1.027312019562781</v>
+        <v>1.035508652044259</v>
       </c>
       <c r="U8">
         <v>0.05868110587651872</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>58.99032596913278</v>
+        <v>50.56313654497096</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09817270721472933</v>
+        <v>0.09799837815899476</v>
       </c>
       <c r="C9">
-        <v>2195.172808545901</v>
+        <v>2175.64241314463</v>
       </c>
       <c r="D9">
-        <v>1916.796808545901</v>
+        <v>1923.19841314463</v>
       </c>
       <c r="E9">
-        <v>-1620.876</v>
+        <v>-1594.944</v>
       </c>
       <c r="F9">
-        <v>181.524</v>
+        <v>207.456</v>
       </c>
       <c r="G9">
         <v>459.9</v>
@@ -2150,28 +2150,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M9">
-        <v>10.65202906312918</v>
+        <v>12.17374750071907</v>
       </c>
       <c r="N9">
-        <v>527.9479709368708</v>
+        <v>526.4262524992808</v>
       </c>
       <c r="O9">
-        <v>142.5459521529551</v>
+        <v>142.1350881748058</v>
       </c>
       <c r="P9">
-        <v>385.4020187839157</v>
+        <v>384.291164324475</v>
       </c>
       <c r="Q9">
-        <v>755.8020187839156</v>
+        <v>754.691164324475</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.102337744843483</v>
+        <v>0.1027950017128327</v>
       </c>
       <c r="T9">
-        <v>1.035508652044259</v>
+        <v>1.043883472188377</v>
       </c>
       <c r="U9">
         <v>0.05868110587651872</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>50.56313654497095</v>
+        <v>44.24274447684958</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09799837815899476</v>
+        <v>0.0978240491032602</v>
       </c>
       <c r="C10">
-        <v>2175.64241314463</v>
+        <v>2156.154920427949</v>
       </c>
       <c r="D10">
-        <v>1923.19841314463</v>
+        <v>1929.642920427949</v>
       </c>
       <c r="E10">
-        <v>-1594.944</v>
+        <v>-1569.012</v>
       </c>
       <c r="F10">
-        <v>207.456</v>
+        <v>233.388</v>
       </c>
       <c r="G10">
         <v>459.9</v>
@@ -2232,28 +2232,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M10">
-        <v>12.17374750071907</v>
+        <v>13.69546593830895</v>
       </c>
       <c r="N10">
-        <v>526.4262524992808</v>
+        <v>524.9045340616909</v>
       </c>
       <c r="O10">
-        <v>142.1350881748058</v>
+        <v>141.7242241966566</v>
       </c>
       <c r="P10">
-        <v>384.291164324475</v>
+        <v>383.1803098650344</v>
       </c>
       <c r="Q10">
-        <v>754.691164324475</v>
+        <v>753.5803098650345</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1027950017128327</v>
+        <v>0.1032623081837065</v>
       </c>
       <c r="T10">
-        <v>1.043883472188377</v>
+        <v>1.052442354313685</v>
       </c>
       <c r="U10">
         <v>0.05868110587651872</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>44.24274447684958</v>
+        <v>39.32688397942185</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0978240491032602</v>
+        <v>0.09764972004752563</v>
       </c>
       <c r="C11">
-        <v>2156.154920427949</v>
+        <v>2136.710763137896</v>
       </c>
       <c r="D11">
-        <v>1929.642920427949</v>
+        <v>1936.130763137896</v>
       </c>
       <c r="E11">
-        <v>-1569.012</v>
+        <v>-1543.08</v>
       </c>
       <c r="F11">
-        <v>233.388</v>
+        <v>259.3199999999999</v>
       </c>
       <c r="G11">
         <v>459.9</v>
@@ -2314,28 +2314,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M11">
-        <v>13.69546593830895</v>
+        <v>15.21718437589883</v>
       </c>
       <c r="N11">
-        <v>524.9045340616909</v>
+        <v>523.3828156241011</v>
       </c>
       <c r="O11">
-        <v>141.7242241966566</v>
+        <v>141.3133602185073</v>
       </c>
       <c r="P11">
-        <v>383.1803098650344</v>
+        <v>382.0694554055938</v>
       </c>
       <c r="Q11">
-        <v>753.5803098650345</v>
+        <v>752.4694554055939</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1032623081837065</v>
+        <v>0.103739999242822</v>
       </c>
       <c r="T11">
-        <v>1.052442354313685</v>
+        <v>1.061191433819556</v>
       </c>
       <c r="U11">
         <v>0.05868110587651872</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>39.32688397942185</v>
+        <v>35.39419558147968</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09764972004752563</v>
+        <v>0.09747539099179107</v>
       </c>
       <c r="C12">
-        <v>2136.710763137896</v>
+        <v>2117.310379855998</v>
       </c>
       <c r="D12">
-        <v>1936.130763137896</v>
+        <v>1942.662379855998</v>
       </c>
       <c r="E12">
-        <v>-1543.08</v>
+        <v>-1517.148</v>
       </c>
       <c r="F12">
-        <v>259.32</v>
+        <v>285.252</v>
       </c>
       <c r="G12">
         <v>459.9</v>
@@ -2396,28 +2396,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M12">
-        <v>15.21718437589883</v>
+        <v>16.73890281348872</v>
       </c>
       <c r="N12">
-        <v>523.3828156241011</v>
+        <v>521.8610971865112</v>
       </c>
       <c r="O12">
-        <v>141.3133602185073</v>
+        <v>140.902496240358</v>
       </c>
       <c r="P12">
-        <v>382.0694554055938</v>
+        <v>380.9586009461532</v>
       </c>
       <c r="Q12">
-        <v>752.4694554055939</v>
+        <v>751.3586009461533</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.103739999242822</v>
+        <v>0.1042284249324794</v>
       </c>
       <c r="T12">
-        <v>1.061191433819556</v>
+        <v>1.070137121853648</v>
       </c>
       <c r="U12">
         <v>0.05868110587651872</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>35.39419558147967</v>
+        <v>32.17654143770879</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09747539099179107</v>
+        <v>0.09730106193605649</v>
       </c>
       <c r="C13">
-        <v>2117.310379855998</v>
+        <v>2097.954215102111</v>
       </c>
       <c r="D13">
-        <v>1942.662379855998</v>
+        <v>1949.238215102112</v>
       </c>
       <c r="E13">
-        <v>-1517.148</v>
+        <v>-1491.216</v>
       </c>
       <c r="F13">
-        <v>285.252</v>
+        <v>311.184</v>
       </c>
       <c r="G13">
         <v>459.9</v>
@@ -2478,28 +2478,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M13">
-        <v>16.73890281348872</v>
+        <v>18.2606212510786</v>
       </c>
       <c r="N13">
-        <v>521.8610971865112</v>
+        <v>520.3393787489213</v>
       </c>
       <c r="O13">
-        <v>140.902496240358</v>
+        <v>140.4916322622088</v>
       </c>
       <c r="P13">
-        <v>380.9586009461532</v>
+        <v>379.8477464867125</v>
       </c>
       <c r="Q13">
-        <v>751.3586009461533</v>
+        <v>750.2477464867125</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1042284249324794</v>
+        <v>0.1047279512059926</v>
       </c>
       <c r="T13">
-        <v>1.070137121853648</v>
+        <v>1.079286120979424</v>
       </c>
       <c r="U13">
         <v>0.05868110587651872</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.17654143770879</v>
+        <v>29.49516298456639</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09730106193605649</v>
+        <v>0.09712673288032193</v>
       </c>
       <c r="C14">
-        <v>2097.954215102111</v>
+        <v>2078.642719435259</v>
       </c>
       <c r="D14">
-        <v>1949.238215102112</v>
+        <v>1955.858719435259</v>
       </c>
       <c r="E14">
-        <v>-1491.216</v>
+        <v>-1465.284</v>
       </c>
       <c r="F14">
-        <v>311.184</v>
+        <v>337.116</v>
       </c>
       <c r="G14">
         <v>459.9</v>
@@ -2560,28 +2560,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M14">
-        <v>18.2606212510786</v>
+        <v>19.78233968866848</v>
       </c>
       <c r="N14">
-        <v>520.3393787489213</v>
+        <v>518.8176603113315</v>
       </c>
       <c r="O14">
-        <v>140.4916322622088</v>
+        <v>140.0807682840595</v>
       </c>
       <c r="P14">
-        <v>379.8477464867125</v>
+        <v>378.7368920272719</v>
       </c>
       <c r="Q14">
-        <v>750.2477464867125</v>
+        <v>749.136892027272</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1047279512059926</v>
+        <v>0.1052389608421153</v>
       </c>
       <c r="T14">
-        <v>1.079286120979424</v>
+        <v>1.088645441924183</v>
       </c>
       <c r="U14">
         <v>0.05868110587651872</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.49516298456639</v>
+        <v>27.2263042934459</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09712673288032193</v>
+        <v>0.09695240382458736</v>
       </c>
       <c r="C15">
-        <v>2078.642719435259</v>
+        <v>2059.376349556545</v>
       </c>
       <c r="D15">
-        <v>1955.858719435259</v>
+        <v>1962.524349556545</v>
       </c>
       <c r="E15">
-        <v>-1465.284</v>
+        <v>-1439.352</v>
       </c>
       <c r="F15">
-        <v>337.116</v>
+        <v>363.048</v>
       </c>
       <c r="G15">
         <v>459.9</v>
@@ -2642,28 +2642,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M15">
-        <v>19.78233968866848</v>
+        <v>21.30405812625837</v>
       </c>
       <c r="N15">
-        <v>518.8176603113315</v>
+        <v>517.2959418737415</v>
       </c>
       <c r="O15">
-        <v>140.0807682840595</v>
+        <v>139.6699043059102</v>
       </c>
       <c r="P15">
-        <v>378.7368920272719</v>
+        <v>377.6260375678313</v>
       </c>
       <c r="Q15">
-        <v>749.136892027272</v>
+        <v>748.0260375678313</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1052389608421153</v>
+        <v>0.1057618544232641</v>
       </c>
       <c r="T15">
-        <v>1.088645441924183</v>
+        <v>1.098222421495565</v>
       </c>
       <c r="U15">
         <v>0.05868110587651872</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.2263042934459</v>
+        <v>25.28156827248547</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09695240382458736</v>
+        <v>0.09677807476885281</v>
       </c>
       <c r="C16">
-        <v>2059.376349556545</v>
+        <v>2040.155568414173</v>
       </c>
       <c r="D16">
-        <v>1962.524349556545</v>
+        <v>1969.235568414173</v>
       </c>
       <c r="E16">
-        <v>-1439.352</v>
+        <v>-1413.42</v>
       </c>
       <c r="F16">
-        <v>363.048</v>
+        <v>388.98</v>
       </c>
       <c r="G16">
         <v>459.9</v>
@@ -2724,28 +2724,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M16">
-        <v>21.30405812625837</v>
+        <v>22.82577656384825</v>
       </c>
       <c r="N16">
-        <v>517.2959418737415</v>
+        <v>515.7742234361517</v>
       </c>
       <c r="O16">
-        <v>139.6699043059102</v>
+        <v>139.259040327761</v>
       </c>
       <c r="P16">
-        <v>377.6260375678313</v>
+        <v>376.5151831083907</v>
       </c>
       <c r="Q16">
-        <v>748.0260375678313</v>
+        <v>746.9151831083907</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1057618544232641</v>
+        <v>0.106297051382793</v>
       </c>
       <c r="T16">
-        <v>1.098222421495565</v>
+        <v>1.108024741762744</v>
       </c>
       <c r="U16">
         <v>0.05868110587651872</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.28156827248547</v>
+        <v>23.59613038765311</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09677807476885281</v>
+        <v>0.09660374571311822</v>
       </c>
       <c r="C17">
-        <v>2040.155568414173</v>
+        <v>2020.980845310627</v>
       </c>
       <c r="D17">
-        <v>1969.235568414173</v>
+        <v>1975.992845310627</v>
       </c>
       <c r="E17">
-        <v>-1413.42</v>
+        <v>-1387.488</v>
       </c>
       <c r="F17">
-        <v>388.98</v>
+        <v>414.912</v>
       </c>
       <c r="G17">
         <v>459.9</v>
@@ -2806,28 +2806,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M17">
-        <v>22.82577656384825</v>
+        <v>24.34749500143813</v>
       </c>
       <c r="N17">
-        <v>515.7742234361517</v>
+        <v>514.2525049985618</v>
       </c>
       <c r="O17">
-        <v>139.259040327761</v>
+        <v>138.8481763496117</v>
       </c>
       <c r="P17">
-        <v>376.5151831083907</v>
+        <v>375.4043286489501</v>
       </c>
       <c r="Q17">
-        <v>746.9151831083907</v>
+        <v>745.8043286489501</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.106297051382793</v>
+        <v>0.1068449911270724</v>
       </c>
       <c r="T17">
-        <v>1.108024741762744</v>
+        <v>1.118060450607713</v>
       </c>
       <c r="U17">
         <v>0.05868110587651872</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.59613038765312</v>
+        <v>22.12137223842479</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09660374571311822</v>
+        <v>0.09642941665738367</v>
       </c>
       <c r="C18">
-        <v>2020.980845310627</v>
+        <v>2001.852656012069</v>
       </c>
       <c r="D18">
-        <v>1975.992845310627</v>
+        <v>1982.796656012069</v>
       </c>
       <c r="E18">
-        <v>-1387.488</v>
+        <v>-1361.556</v>
       </c>
       <c r="F18">
-        <v>414.912</v>
+        <v>440.844</v>
       </c>
       <c r="G18">
         <v>459.9</v>
@@ -2888,28 +2888,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M18">
-        <v>24.34749500143813</v>
+        <v>25.86921343902802</v>
       </c>
       <c r="N18">
-        <v>514.2525049985618</v>
+        <v>512.7307865609719</v>
       </c>
       <c r="O18">
-        <v>138.8481763496117</v>
+        <v>138.4373123714624</v>
       </c>
       <c r="P18">
-        <v>375.4043286489501</v>
+        <v>374.2934741895094</v>
       </c>
       <c r="Q18">
-        <v>745.8043286489501</v>
+        <v>744.6934741895095</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1068449911270724</v>
+        <v>0.107406134238684</v>
       </c>
       <c r="T18">
-        <v>1.118060450607713</v>
+        <v>1.128337983762199</v>
       </c>
       <c r="U18">
         <v>0.05868110587651872</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.12137223842479</v>
+        <v>20.82011504792921</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09642941665738367</v>
+        <v>0.09625508760164908</v>
       </c>
       <c r="C19">
-        <v>2001.852656012069</v>
+        <v>1982.771482860004</v>
       </c>
       <c r="D19">
-        <v>1982.796656012069</v>
+        <v>1989.647482860003</v>
       </c>
       <c r="E19">
-        <v>-1361.556</v>
+        <v>-1335.624</v>
       </c>
       <c r="F19">
-        <v>440.844</v>
+        <v>466.776</v>
       </c>
       <c r="G19">
         <v>459.9</v>
@@ -2970,28 +2970,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M19">
-        <v>25.86921343902802</v>
+        <v>27.3909318766179</v>
       </c>
       <c r="N19">
-        <v>512.7307865609719</v>
+        <v>511.209068123382</v>
       </c>
       <c r="O19">
-        <v>138.4373123714624</v>
+        <v>138.0264483933132</v>
       </c>
       <c r="P19">
-        <v>374.2934741895094</v>
+        <v>373.1826197300688</v>
       </c>
       <c r="Q19">
-        <v>744.6934741895095</v>
+        <v>743.5826197300689</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.107406134238684</v>
+        <v>0.1079809637676519</v>
       </c>
       <c r="T19">
-        <v>1.128337983762199</v>
+        <v>1.138866188457038</v>
       </c>
       <c r="U19">
         <v>0.05868110587651872</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.82011504792921</v>
+        <v>19.66344198971093</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09625508760164909</v>
+        <v>0.09608075854591455</v>
       </c>
       <c r="C20">
-        <v>1982.771482860003</v>
+        <v>1963.737814885262</v>
       </c>
       <c r="D20">
-        <v>1989.647482860003</v>
+        <v>1996.545814885262</v>
       </c>
       <c r="E20">
-        <v>-1335.624</v>
+        <v>-1309.692</v>
       </c>
       <c r="F20">
-        <v>466.776</v>
+        <v>492.708</v>
       </c>
       <c r="G20">
         <v>459.9</v>
@@ -3052,28 +3052,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M20">
-        <v>27.3909318766179</v>
+        <v>28.91265031420778</v>
       </c>
       <c r="N20">
-        <v>511.209068123382</v>
+        <v>509.6873496857921</v>
       </c>
       <c r="O20">
-        <v>138.0264483933132</v>
+        <v>137.6155844151639</v>
       </c>
       <c r="P20">
-        <v>373.1826197300688</v>
+        <v>372.0717652706282</v>
       </c>
       <c r="Q20">
-        <v>743.5826197300689</v>
+        <v>742.4717652706283</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1079809637676519</v>
+        <v>0.1085699866183227</v>
       </c>
       <c r="T20">
-        <v>1.138866188457038</v>
+        <v>1.149654348823356</v>
       </c>
       <c r="U20">
         <v>0.05868110587651872</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.66344198971093</v>
+        <v>18.62852399025246</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09608075854591455</v>
+        <v>0.09590642949018</v>
       </c>
       <c r="C21">
-        <v>1963.737814885262</v>
+        <v>1944.752147924377</v>
       </c>
       <c r="D21">
-        <v>1996.545814885262</v>
+        <v>2003.492147924377</v>
       </c>
       <c r="E21">
-        <v>-1309.692</v>
+        <v>-1283.76</v>
       </c>
       <c r="F21">
-        <v>492.708</v>
+        <v>518.64</v>
       </c>
       <c r="G21">
         <v>459.9</v>
@@ -3134,28 +3134,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M21">
-        <v>28.91265031420778</v>
+        <v>30.43436875179767</v>
       </c>
       <c r="N21">
-        <v>509.6873496857921</v>
+        <v>508.1656312482023</v>
       </c>
       <c r="O21">
-        <v>137.6155844151639</v>
+        <v>137.2047204370146</v>
       </c>
       <c r="P21">
-        <v>372.0717652706282</v>
+        <v>370.9609108111877</v>
       </c>
       <c r="Q21">
-        <v>742.4717652706283</v>
+        <v>741.3609108111878</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1085699866183227</v>
+        <v>0.1091737350402603</v>
       </c>
       <c r="T21">
-        <v>1.149654348823356</v>
+        <v>1.160712213198831</v>
       </c>
       <c r="U21">
         <v>0.05868110587651872</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.62852399025246</v>
+        <v>17.69709779073983</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09590642949018</v>
+        <v>0.09573210043444541</v>
       </c>
       <c r="C22">
-        <v>1944.752147924377</v>
+        <v>1925.814984738379</v>
       </c>
       <c r="D22">
-        <v>2003.492147924377</v>
+        <v>2010.486984738379</v>
       </c>
       <c r="E22">
-        <v>-1283.76</v>
+        <v>-1257.828</v>
       </c>
       <c r="F22">
-        <v>518.64</v>
+        <v>544.572</v>
       </c>
       <c r="G22">
         <v>459.9</v>
@@ -3216,28 +3216,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M22">
-        <v>30.43436875179767</v>
+        <v>31.95608718938755</v>
       </c>
       <c r="N22">
-        <v>508.1656312482023</v>
+        <v>506.6439128106123</v>
       </c>
       <c r="O22">
-        <v>137.2047204370146</v>
+        <v>136.7938564588653</v>
       </c>
       <c r="P22">
-        <v>370.9609108111877</v>
+        <v>369.850056351747</v>
       </c>
       <c r="Q22">
-        <v>741.3609108111878</v>
+        <v>740.2500563517469</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1091737350402603</v>
+        <v>0.1097927682323735</v>
       </c>
       <c r="T22">
-        <v>1.160712213198831</v>
+        <v>1.172050023507862</v>
       </c>
       <c r="U22">
         <v>0.05868110587651872</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.69709779073983</v>
+        <v>16.85437884832365</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09573210043444541</v>
+        <v>0.09555777137871085</v>
       </c>
       <c r="C23">
-        <v>1925.814984738379</v>
+        <v>1906.926835134099</v>
       </c>
       <c r="D23">
-        <v>2010.486984738379</v>
+        <v>2017.530835134099</v>
       </c>
       <c r="E23">
-        <v>-1257.828</v>
+        <v>-1231.896</v>
       </c>
       <c r="F23">
-        <v>544.5719999999999</v>
+        <v>570.504</v>
       </c>
       <c r="G23">
         <v>459.9</v>
@@ -3298,28 +3298,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M23">
-        <v>31.95608718938754</v>
+        <v>33.47780562697744</v>
       </c>
       <c r="N23">
-        <v>506.6439128106124</v>
+        <v>505.1221943730225</v>
       </c>
       <c r="O23">
-        <v>136.7938564588653</v>
+        <v>136.3829924807161</v>
       </c>
       <c r="P23">
-        <v>369.8500563517471</v>
+        <v>368.7392018923064</v>
       </c>
       <c r="Q23">
-        <v>740.2500563517472</v>
+        <v>739.1392018923063</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1097927682323735</v>
+        <v>0.1104276740704384</v>
       </c>
       <c r="T23">
-        <v>1.172050023507862</v>
+        <v>1.18367854690174</v>
       </c>
       <c r="U23">
         <v>0.05868110587651872</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.85437884832366</v>
+        <v>16.08827071885439</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09555777137871085</v>
+        <v>0.0953834423229763</v>
       </c>
       <c r="C24">
-        <v>1906.926835134099</v>
+        <v>1888.088216088032</v>
       </c>
       <c r="D24">
-        <v>2017.530835134099</v>
+        <v>2024.624216088032</v>
       </c>
       <c r="E24">
-        <v>-1231.896</v>
+        <v>-1205.964</v>
       </c>
       <c r="F24">
-        <v>570.504</v>
+        <v>596.436</v>
       </c>
       <c r="G24">
         <v>459.9</v>
@@ -3380,28 +3380,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M24">
-        <v>33.47780562697744</v>
+        <v>34.99952406456732</v>
       </c>
       <c r="N24">
-        <v>505.1221943730225</v>
+        <v>503.6004759354326</v>
       </c>
       <c r="O24">
-        <v>136.3829924807161</v>
+        <v>135.9721285025668</v>
       </c>
       <c r="P24">
-        <v>368.7392018923064</v>
+        <v>367.6283474328658</v>
       </c>
       <c r="Q24">
-        <v>739.1392018923063</v>
+        <v>738.0283474328658</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1104276740704384</v>
+        <v>0.1110790709692322</v>
       </c>
       <c r="T24">
-        <v>1.18367854690174</v>
+        <v>1.195609109864291</v>
       </c>
       <c r="U24">
         <v>0.05868110587651872</v>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.08827071885439</v>
+        <v>15.38878068759985</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0953834423229763</v>
+        <v>0.09520911326724173</v>
       </c>
       <c r="C25">
-        <v>1888.088216088032</v>
+        <v>1869.299651872823</v>
       </c>
       <c r="D25">
-        <v>2024.624216088032</v>
+        <v>2031.767651872823</v>
       </c>
       <c r="E25">
-        <v>-1205.964</v>
+        <v>-1180.032</v>
       </c>
       <c r="F25">
-        <v>596.436</v>
+        <v>622.3680000000001</v>
       </c>
       <c r="G25">
         <v>459.9</v>
@@ -3462,28 +3462,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M25">
-        <v>34.99952406456732</v>
+        <v>36.5212425021572</v>
       </c>
       <c r="N25">
-        <v>503.6004759354326</v>
+        <v>502.0787574978427</v>
       </c>
       <c r="O25">
-        <v>135.9721285025668</v>
+        <v>135.5612645244175</v>
       </c>
       <c r="P25">
-        <v>367.6283474328658</v>
+        <v>366.5174929734252</v>
       </c>
       <c r="Q25">
-        <v>738.0283474328658</v>
+        <v>736.9174929734252</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1110790709692322</v>
+        <v>0.1117476098916785</v>
       </c>
       <c r="T25">
-        <v>1.195609109864291</v>
+        <v>1.207853635010066</v>
       </c>
       <c r="U25">
         <v>0.05868110587651872</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.38878068759985</v>
+        <v>14.7475814922832</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09520911326724173</v>
+        <v>0.09503478421150714</v>
       </c>
       <c r="C26">
-        <v>1869.299651872823</v>
+        <v>1850.561674186427</v>
       </c>
       <c r="D26">
-        <v>2031.767651872823</v>
+        <v>2038.961674186427</v>
       </c>
       <c r="E26">
-        <v>-1180.032</v>
+        <v>-1154.1</v>
       </c>
       <c r="F26">
-        <v>622.3679999999999</v>
+        <v>648.3</v>
       </c>
       <c r="G26">
         <v>459.9</v>
@@ -3544,28 +3544,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M26">
-        <v>36.52124250215719</v>
+        <v>38.04296093974708</v>
       </c>
       <c r="N26">
-        <v>502.0787574978427</v>
+        <v>500.5570390602528</v>
       </c>
       <c r="O26">
-        <v>135.5612645244175</v>
+        <v>135.1504005462683</v>
       </c>
       <c r="P26">
-        <v>366.5174929734252</v>
+        <v>365.4066385139845</v>
       </c>
       <c r="Q26">
-        <v>736.9174929734252</v>
+        <v>735.8066385139846</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1117476098916785</v>
+        <v>0.1124339765187233</v>
       </c>
       <c r="T26">
-        <v>1.207853635010066</v>
+        <v>1.220424680826396</v>
       </c>
       <c r="U26">
         <v>0.05868110587651872</v>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.7475814922832</v>
+        <v>14.15767823259187</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09503478421150714</v>
+        <v>0.09486045515577257</v>
       </c>
       <c r="C27">
-        <v>1850.561674186427</v>
+        <v>1831.87482228404</v>
       </c>
       <c r="D27">
-        <v>2038.961674186427</v>
+        <v>2046.206822284041</v>
       </c>
       <c r="E27">
-        <v>-1154.1</v>
+        <v>-1128.168</v>
       </c>
       <c r="F27">
-        <v>648.3</v>
+        <v>674.232</v>
       </c>
       <c r="G27">
         <v>459.9</v>
@@ -3626,28 +3626,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M27">
-        <v>38.04296093974708</v>
+        <v>39.56467937733697</v>
       </c>
       <c r="N27">
-        <v>500.5570390602528</v>
+        <v>499.0353206226629</v>
       </c>
       <c r="O27">
-        <v>135.1504005462683</v>
+        <v>134.739536568119</v>
       </c>
       <c r="P27">
-        <v>365.4066385139845</v>
+        <v>364.2957840545439</v>
       </c>
       <c r="Q27">
-        <v>735.8066385139846</v>
+        <v>734.695784054544</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1124339765187233</v>
+        <v>0.1131388935951477</v>
       </c>
       <c r="T27">
-        <v>1.220424680826396</v>
+        <v>1.233335484637761</v>
       </c>
       <c r="U27">
         <v>0.05868110587651872</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.15767823259187</v>
+        <v>13.61315214672295</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09486045515577257</v>
+        <v>0.094686126100038</v>
       </c>
       <c r="C28">
-        <v>1831.87482228404</v>
+        <v>1813.239643112847</v>
       </c>
       <c r="D28">
-        <v>2046.206822284041</v>
+        <v>2053.503643112847</v>
       </c>
       <c r="E28">
-        <v>-1128.168</v>
+        <v>-1102.236</v>
       </c>
       <c r="F28">
-        <v>674.232</v>
+        <v>700.164</v>
       </c>
       <c r="G28">
         <v>459.9</v>
@@ -3708,28 +3708,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M28">
-        <v>39.56467937733697</v>
+        <v>41.08639781492685</v>
       </c>
       <c r="N28">
-        <v>499.0353206226629</v>
+        <v>497.5136021850731</v>
       </c>
       <c r="O28">
-        <v>134.739536568119</v>
+        <v>134.3286725899697</v>
       </c>
       <c r="P28">
-        <v>364.2957840545439</v>
+        <v>363.1849295951033</v>
       </c>
       <c r="Q28">
-        <v>734.695784054544</v>
+        <v>733.5849295951034</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1131388935951477</v>
+        <v>0.1138631234681865</v>
       </c>
       <c r="T28">
-        <v>1.233335484637761</v>
+        <v>1.246600009101492</v>
       </c>
       <c r="U28">
         <v>0.05868110587651872</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.61315214672295</v>
+        <v>13.10896132647395</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.094686126100038</v>
+        <v>0.09481839704430345</v>
       </c>
       <c r="C29">
-        <v>1813.239643112847</v>
+        <v>1781.766481379598</v>
       </c>
       <c r="D29">
-        <v>2053.503643112847</v>
+        <v>2047.962481379598</v>
       </c>
       <c r="E29">
-        <v>-1102.236</v>
+        <v>-1076.304</v>
       </c>
       <c r="F29">
-        <v>700.164</v>
+        <v>726.096</v>
       </c>
       <c r="G29">
         <v>459.9</v>
@@ -3790,45 +3790,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M29">
-        <v>41.08639781492685</v>
+        <v>43.69726025251673</v>
       </c>
       <c r="N29">
-        <v>497.5136021850731</v>
+        <v>494.9027397474832</v>
       </c>
       <c r="O29">
-        <v>134.3286725899697</v>
+        <v>133.6237397318205</v>
       </c>
       <c r="P29">
-        <v>363.1849295951033</v>
+        <v>361.2790000156627</v>
       </c>
       <c r="Q29">
-        <v>733.5849295951034</v>
+        <v>731.6790000156627</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1138631234681865</v>
+        <v>0.1146074708376986</v>
       </c>
       <c r="T29">
-        <v>1.246600009101492</v>
+        <v>1.260232992578106</v>
       </c>
       <c r="U29">
-        <v>0.05868110587651872</v>
+        <v>0.06018110587651871</v>
       </c>
       <c r="V29">
         <v>0.27</v>
       </c>
       <c r="W29">
-        <v>0.04283720728985866</v>
+        <v>0.04393220728985866</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>13.10896132647395</v>
+        <v>12.32571554572416</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09481839704430345</v>
+        <v>0.09465501798856887</v>
       </c>
       <c r="C30">
-        <v>1781.766481379598</v>
+        <v>1762.683198055251</v>
       </c>
       <c r="D30">
-        <v>2047.962481379598</v>
+        <v>2054.811198055251</v>
       </c>
       <c r="E30">
-        <v>-1076.304</v>
+        <v>-1050.372</v>
       </c>
       <c r="F30">
-        <v>726.096</v>
+        <v>752.028</v>
       </c>
       <c r="G30">
         <v>459.9</v>
@@ -3872,28 +3872,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M30">
-        <v>43.69726025251673</v>
+        <v>45.25787669010661</v>
       </c>
       <c r="N30">
-        <v>494.9027397474832</v>
+        <v>493.3421233098933</v>
       </c>
       <c r="O30">
-        <v>133.6237397318205</v>
+        <v>133.2023732936712</v>
       </c>
       <c r="P30">
-        <v>361.2790000156627</v>
+        <v>360.1397500162221</v>
       </c>
       <c r="Q30">
-        <v>731.6790000156627</v>
+        <v>730.5397500162221</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1146074708376986</v>
+        <v>0.1153727857387463</v>
       </c>
       <c r="T30">
-        <v>1.260232992578106</v>
+        <v>1.274250003758285</v>
       </c>
       <c r="U30">
         <v>0.06018110587651871</v>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.32571554572416</v>
+        <v>11.90069087173367</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09465501798856887</v>
+        <v>0.09449163893283433</v>
       </c>
       <c r="C31">
-        <v>1762.683198055252</v>
+        <v>1743.64587485416</v>
       </c>
       <c r="D31">
-        <v>2054.811198055251</v>
+        <v>2061.70587485416</v>
       </c>
       <c r="E31">
-        <v>-1050.372</v>
+        <v>-1024.44</v>
       </c>
       <c r="F31">
-        <v>752.0279999999999</v>
+        <v>777.9599999999999</v>
       </c>
       <c r="G31">
         <v>459.9</v>
@@ -3954,28 +3954,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M31">
-        <v>45.25787669010661</v>
+        <v>46.81849312769649</v>
       </c>
       <c r="N31">
-        <v>493.3421233098933</v>
+        <v>491.7815068723034</v>
       </c>
       <c r="O31">
-        <v>133.2023732936712</v>
+        <v>132.7810068555219</v>
       </c>
       <c r="P31">
-        <v>360.1397500162221</v>
+        <v>359.0005000167815</v>
       </c>
       <c r="Q31">
-        <v>730.5397500162221</v>
+        <v>729.4005000167815</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1153727857387463</v>
+        <v>0.1161599667798239</v>
       </c>
       <c r="T31">
-        <v>1.274250003758285</v>
+        <v>1.288667500972184</v>
       </c>
       <c r="U31">
         <v>0.06018110587651871</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.90069087173367</v>
+        <v>11.50400117600922</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09449163893283433</v>
+        <v>0.09432825987709975</v>
       </c>
       <c r="C32">
-        <v>1743.64587485416</v>
+        <v>1724.654975975222</v>
       </c>
       <c r="D32">
-        <v>2061.70587485416</v>
+        <v>2068.646975975221</v>
       </c>
       <c r="E32">
-        <v>-1024.44</v>
+        <v>-998.5080000000002</v>
       </c>
       <c r="F32">
-        <v>777.9599999999999</v>
+        <v>803.8919999999999</v>
       </c>
       <c r="G32">
         <v>459.9</v>
@@ -4036,28 +4036,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M32">
-        <v>46.81849312769649</v>
+        <v>48.37910956528638</v>
       </c>
       <c r="N32">
-        <v>491.7815068723034</v>
+        <v>490.2208904347135</v>
       </c>
       <c r="O32">
-        <v>132.7810068555219</v>
+        <v>132.3596404173726</v>
       </c>
       <c r="P32">
-        <v>359.0005000167815</v>
+        <v>357.8612500173409</v>
       </c>
       <c r="Q32">
-        <v>729.4005000167815</v>
+        <v>728.2612500173409</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1161599667798239</v>
+        <v>0.1169699646626718</v>
       </c>
       <c r="T32">
-        <v>1.288667500972184</v>
+        <v>1.303502896656051</v>
       </c>
       <c r="U32">
         <v>0.06018110587651871</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.50400117600922</v>
+        <v>11.13290436387989</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09432825987709975</v>
+        <v>0.09416488082136518</v>
       </c>
       <c r="C33">
-        <v>1724.654975975222</v>
+        <v>1705.71097188968</v>
       </c>
       <c r="D33">
-        <v>2068.646975975221</v>
+        <v>2075.63497188968</v>
       </c>
       <c r="E33">
-        <v>-998.5080000000002</v>
+        <v>-972.5760000000001</v>
       </c>
       <c r="F33">
-        <v>803.8919999999999</v>
+        <v>829.824</v>
       </c>
       <c r="G33">
         <v>459.9</v>
@@ -4118,28 +4118,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M33">
-        <v>48.37910956528638</v>
+        <v>49.93972600287626</v>
       </c>
       <c r="N33">
-        <v>490.2208904347135</v>
+        <v>488.6602739971236</v>
       </c>
       <c r="O33">
-        <v>132.3596404173726</v>
+        <v>131.9382739792234</v>
       </c>
       <c r="P33">
-        <v>357.8612500173409</v>
+        <v>356.7220000179002</v>
       </c>
       <c r="Q33">
-        <v>728.2612500173409</v>
+        <v>727.1220000179003</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1169699646626718</v>
+        <v>0.1178037860126624</v>
       </c>
       <c r="T33">
-        <v>1.303502896656051</v>
+        <v>1.318774627507091</v>
       </c>
       <c r="U33">
         <v>0.06018110587651871</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.13290436387989</v>
+        <v>10.78500110250864</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09416488082136518</v>
+        <v>0.09400150176563062</v>
       </c>
       <c r="C34">
-        <v>1705.71097188968</v>
+        <v>1686.814339447435</v>
       </c>
       <c r="D34">
-        <v>2075.63497188968</v>
+        <v>2082.670339447435</v>
       </c>
       <c r="E34">
-        <v>-972.5760000000001</v>
+        <v>-946.6440000000001</v>
       </c>
       <c r="F34">
-        <v>829.824</v>
+        <v>855.756</v>
       </c>
       <c r="G34">
         <v>459.9</v>
@@ -4200,28 +4200,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M34">
-        <v>49.93972600287626</v>
+        <v>51.50034244046614</v>
       </c>
       <c r="N34">
-        <v>488.6602739971236</v>
+        <v>487.0996575595337</v>
       </c>
       <c r="O34">
-        <v>131.9382739792234</v>
+        <v>131.5169075410741</v>
       </c>
       <c r="P34">
-        <v>356.7220000179002</v>
+        <v>355.5827500184596</v>
       </c>
       <c r="Q34">
-        <v>727.1220000179003</v>
+        <v>725.9827500184597</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1178037860126624</v>
+        <v>0.1186624975522049</v>
       </c>
       <c r="T34">
-        <v>1.318774627507091</v>
+        <v>1.334502230920848</v>
       </c>
       <c r="U34">
         <v>0.06018110587651871</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.78500110250864</v>
+        <v>10.45818288728111</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09400150176563062</v>
+        <v>0.09383812270989603</v>
       </c>
       <c r="C35">
-        <v>1686.814339447435</v>
+        <v>1667.965561985506</v>
       </c>
       <c r="D35">
-        <v>2082.670339447435</v>
+        <v>2089.753561985506</v>
       </c>
       <c r="E35">
-        <v>-946.6440000000001</v>
+        <v>-920.7120000000001</v>
       </c>
       <c r="F35">
-        <v>855.756</v>
+        <v>881.688</v>
       </c>
       <c r="G35">
         <v>459.9</v>
@@ -4282,28 +4282,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M35">
-        <v>51.50034244046614</v>
+        <v>53.06095887805603</v>
       </c>
       <c r="N35">
-        <v>487.0996575595337</v>
+        <v>485.5390411219439</v>
       </c>
       <c r="O35">
-        <v>131.5169075410741</v>
+        <v>131.0955411029249</v>
       </c>
       <c r="P35">
-        <v>355.5827500184596</v>
+        <v>354.443500019019</v>
       </c>
       <c r="Q35">
-        <v>725.9827500184597</v>
+        <v>724.8435000190191</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1186624975522049</v>
+        <v>0.1195472306535517</v>
       </c>
       <c r="T35">
-        <v>1.334502230920848</v>
+        <v>1.350706428377446</v>
       </c>
       <c r="U35">
         <v>0.06018110587651871</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.45818288728111</v>
+        <v>10.15058927294931</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09383812270989603</v>
+        <v>0.09367474365416148</v>
       </c>
       <c r="C36">
-        <v>1667.965561985506</v>
+        <v>1649.165129438723</v>
       </c>
       <c r="D36">
-        <v>2089.753561985506</v>
+        <v>2096.885129438723</v>
       </c>
       <c r="E36">
-        <v>-920.7120000000001</v>
+        <v>-894.7800000000001</v>
       </c>
       <c r="F36">
-        <v>881.688</v>
+        <v>907.62</v>
       </c>
       <c r="G36">
         <v>459.9</v>
@@ -4364,28 +4364,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M36">
-        <v>53.06095887805603</v>
+        <v>54.62157531564591</v>
       </c>
       <c r="N36">
-        <v>485.5390411219439</v>
+        <v>483.978424684354</v>
       </c>
       <c r="O36">
-        <v>131.0955411029249</v>
+        <v>130.6741746647756</v>
       </c>
       <c r="P36">
-        <v>354.443500019019</v>
+        <v>353.3042500195784</v>
       </c>
       <c r="Q36">
-        <v>724.8435000190191</v>
+        <v>723.7042500195785</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1195472306535517</v>
+        <v>0.120459186311863</v>
       </c>
       <c r="T36">
-        <v>1.350706428377446</v>
+        <v>1.367409216525017</v>
       </c>
       <c r="U36">
         <v>0.06018110587651871</v>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.15058927294931</v>
+        <v>9.860572436579329</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09367474365416148</v>
+        <v>0.09395812459842691</v>
       </c>
       <c r="C37">
-        <v>1649.165129438723</v>
+        <v>1610.894250112515</v>
       </c>
       <c r="D37">
-        <v>2096.885129438723</v>
+        <v>2084.546250112515</v>
       </c>
       <c r="E37">
-        <v>-894.7800000000001</v>
+        <v>-868.8480000000001</v>
       </c>
       <c r="F37">
-        <v>907.62</v>
+        <v>933.552</v>
       </c>
       <c r="G37">
         <v>459.9</v>
@@ -4446,45 +4446,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M37">
-        <v>54.62157531564591</v>
+        <v>57.7692301532358</v>
       </c>
       <c r="N37">
-        <v>483.978424684354</v>
+        <v>480.8307698467641</v>
       </c>
       <c r="O37">
-        <v>130.6741746647756</v>
+        <v>129.8243078586263</v>
       </c>
       <c r="P37">
-        <v>353.3042500195784</v>
+        <v>351.0064619881377</v>
       </c>
       <c r="Q37">
-        <v>723.7042500195785</v>
+        <v>721.4064619881378</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.120459186311863</v>
+        <v>0.1213996405844966</v>
       </c>
       <c r="T37">
-        <v>1.367409216525017</v>
+        <v>1.384633966802199</v>
       </c>
       <c r="U37">
-        <v>0.06018110587651871</v>
+        <v>0.06188110587651871</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.04393220728985866</v>
+        <v>0.04517320728985866</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>9.860572436579329</v>
+        <v>9.323302363063108</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09395812459842692</v>
+        <v>0.09380715554269235</v>
       </c>
       <c r="C38">
-        <v>1610.894250112514</v>
+        <v>1591.517564116375</v>
       </c>
       <c r="D38">
-        <v>2084.546250112514</v>
+        <v>2091.101564116375</v>
       </c>
       <c r="E38">
-        <v>-868.8480000000002</v>
+        <v>-842.9160000000002</v>
       </c>
       <c r="F38">
-        <v>933.5519999999999</v>
+        <v>959.4839999999999</v>
       </c>
       <c r="G38">
         <v>459.9</v>
@@ -4528,28 +4528,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M38">
-        <v>57.76923015323579</v>
+        <v>59.37393099082568</v>
       </c>
       <c r="N38">
-        <v>480.8307698467641</v>
+        <v>479.2260690091742</v>
       </c>
       <c r="O38">
-        <v>129.8243078586263</v>
+        <v>129.3910386324771</v>
       </c>
       <c r="P38">
-        <v>351.0064619881377</v>
+        <v>349.8350303766972</v>
       </c>
       <c r="Q38">
-        <v>721.4064619881378</v>
+        <v>720.2350303766973</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1213996405844966</v>
+        <v>0.1223699505483248</v>
       </c>
       <c r="T38">
-        <v>1.384633966802199</v>
+        <v>1.402405534548498</v>
       </c>
       <c r="U38">
         <v>0.06188110587651871</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.32330236306311</v>
+        <v>9.071321218115457</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09380715554269235</v>
+        <v>0.09365618648695778</v>
       </c>
       <c r="C39">
-        <v>1591.517564116375</v>
+        <v>1572.182237436046</v>
       </c>
       <c r="D39">
-        <v>2091.101564116375</v>
+        <v>2097.698237436046</v>
       </c>
       <c r="E39">
-        <v>-842.9160000000002</v>
+        <v>-816.9840000000002</v>
       </c>
       <c r="F39">
-        <v>959.4839999999999</v>
+        <v>985.4159999999999</v>
       </c>
       <c r="G39">
         <v>459.9</v>
@@ -4610,28 +4610,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M39">
-        <v>59.37393099082568</v>
+        <v>60.97863182841556</v>
       </c>
       <c r="N39">
-        <v>479.2260690091742</v>
+        <v>477.6213681715843</v>
       </c>
       <c r="O39">
-        <v>129.3910386324771</v>
+        <v>128.9577694063278</v>
       </c>
       <c r="P39">
-        <v>349.8350303766972</v>
+        <v>348.6635987652566</v>
       </c>
       <c r="Q39">
-        <v>720.2350303766973</v>
+        <v>719.0635987652565</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1223699505483248</v>
+        <v>0.1233715608335669</v>
       </c>
       <c r="T39">
-        <v>1.402405534548498</v>
+        <v>1.42075037867371</v>
       </c>
       <c r="U39">
         <v>0.06188110587651871</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.071321218115457</v>
+        <v>8.832602238691367</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09365618648695778</v>
+        <v>0.09350521743122323</v>
       </c>
       <c r="C40">
-        <v>1572.182237436046</v>
+        <v>1552.888662731526</v>
       </c>
       <c r="D40">
-        <v>2097.698237436046</v>
+        <v>2104.336662731525</v>
       </c>
       <c r="E40">
-        <v>-816.9840000000002</v>
+        <v>-791.0520000000001</v>
       </c>
       <c r="F40">
-        <v>985.4159999999999</v>
+        <v>1011.348</v>
       </c>
       <c r="G40">
         <v>459.9</v>
@@ -4692,28 +4692,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M40">
-        <v>60.97863182841556</v>
+        <v>62.58333266600544</v>
       </c>
       <c r="N40">
-        <v>477.6213681715843</v>
+        <v>476.0166673339945</v>
       </c>
       <c r="O40">
-        <v>128.9577694063278</v>
+        <v>128.5245001801785</v>
       </c>
       <c r="P40">
-        <v>348.6635987652566</v>
+        <v>347.492167153816</v>
       </c>
       <c r="Q40">
-        <v>719.0635987652565</v>
+        <v>717.892167153816</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1233715608335669</v>
+        <v>0.1244060108002924</v>
       </c>
       <c r="T40">
-        <v>1.42075037867371</v>
+        <v>1.439696693098109</v>
       </c>
       <c r="U40">
         <v>0.06188110587651871</v>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.832602238691367</v>
+        <v>8.606125258212101</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09350521743122323</v>
+        <v>0.09335424837548867</v>
       </c>
       <c r="C41">
-        <v>1552.888662731526</v>
+        <v>1533.637237649074</v>
       </c>
       <c r="D41">
-        <v>2104.336662731525</v>
+        <v>2111.017237649074</v>
       </c>
       <c r="E41">
-        <v>-791.0520000000001</v>
+        <v>-765.1200000000001</v>
       </c>
       <c r="F41">
-        <v>1011.348</v>
+        <v>1037.28</v>
       </c>
       <c r="G41">
         <v>459.9</v>
@@ -4774,28 +4774,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M41">
-        <v>62.58333266600544</v>
+        <v>64.18803350359532</v>
       </c>
       <c r="N41">
-        <v>476.0166673339945</v>
+        <v>474.4119664964046</v>
       </c>
       <c r="O41">
-        <v>128.5245001801785</v>
+        <v>128.0912309540292</v>
       </c>
       <c r="P41">
-        <v>347.492167153816</v>
+        <v>346.3207355423754</v>
       </c>
       <c r="Q41">
-        <v>717.892167153816</v>
+        <v>716.7207355423755</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1244060108002924</v>
+        <v>0.1254749424325753</v>
       </c>
       <c r="T41">
-        <v>1.439696693098109</v>
+        <v>1.459274551336655</v>
       </c>
       <c r="U41">
         <v>0.06188110587651871</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.606125258212101</v>
+        <v>8.3909721267568</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09335424837548867</v>
+        <v>0.0932032793197541</v>
       </c>
       <c r="C42">
-        <v>1533.637237649074</v>
+        <v>1514.42836490062</v>
       </c>
       <c r="D42">
-        <v>2111.017237649074</v>
+        <v>2117.74036490062</v>
       </c>
       <c r="E42">
-        <v>-765.1200000000001</v>
+        <v>-739.1880000000001</v>
       </c>
       <c r="F42">
-        <v>1037.28</v>
+        <v>1063.212</v>
       </c>
       <c r="G42">
         <v>459.9</v>
@@ -4856,28 +4856,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M42">
-        <v>64.18803350359532</v>
+        <v>65.79273434118521</v>
       </c>
       <c r="N42">
-        <v>474.4119664964046</v>
+        <v>472.8072656588147</v>
       </c>
       <c r="O42">
-        <v>128.0912309540292</v>
+        <v>127.65796172788</v>
       </c>
       <c r="P42">
-        <v>346.3207355423754</v>
+        <v>345.1493039309347</v>
       </c>
       <c r="Q42">
-        <v>716.7207355423755</v>
+        <v>715.5493039309347</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1254749424325753</v>
+        <v>0.1265801090354441</v>
       </c>
       <c r="T42">
-        <v>1.459274551336655</v>
+        <v>1.479516065786677</v>
       </c>
       <c r="U42">
         <v>0.06188110587651871</v>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.3909721267568</v>
+        <v>8.186314270006633</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0932032793197541</v>
+        <v>0.09305231026401953</v>
       </c>
       <c r="C43">
-        <v>1514.42836490062</v>
+        <v>1495.262452344676</v>
       </c>
       <c r="D43">
-        <v>2117.74036490062</v>
+        <v>2124.506452344676</v>
       </c>
       <c r="E43">
-        <v>-739.1880000000001</v>
+        <v>-713.2560000000001</v>
       </c>
       <c r="F43">
-        <v>1063.212</v>
+        <v>1089.144</v>
       </c>
       <c r="G43">
         <v>459.9</v>
@@ -4938,28 +4938,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M43">
-        <v>65.79273434118521</v>
+        <v>67.3974351787751</v>
       </c>
       <c r="N43">
-        <v>472.8072656588147</v>
+        <v>471.2025648212248</v>
       </c>
       <c r="O43">
-        <v>127.65796172788</v>
+        <v>127.2246925017307</v>
       </c>
       <c r="P43">
-        <v>345.1493039309347</v>
+        <v>343.9778723194941</v>
       </c>
       <c r="Q43">
-        <v>715.5493039309347</v>
+        <v>714.3778723194941</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1265801090354441</v>
+        <v>0.1277233848315153</v>
       </c>
       <c r="T43">
-        <v>1.479516065786677</v>
+        <v>1.500455563493597</v>
       </c>
       <c r="U43">
         <v>0.06188110587651871</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.186314270006633</v>
+        <v>7.991402025482665</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09305231026401954</v>
+        <v>0.09290134120828497</v>
       </c>
       <c r="C44">
-        <v>1495.262452344676</v>
+        <v>1476.139913068823</v>
       </c>
       <c r="D44">
-        <v>2124.506452344676</v>
+        <v>2131.315913068823</v>
       </c>
       <c r="E44">
-        <v>-713.2560000000003</v>
+        <v>-687.3240000000003</v>
       </c>
       <c r="F44">
-        <v>1089.144</v>
+        <v>1115.076</v>
       </c>
       <c r="G44">
         <v>459.9</v>
@@ -5020,28 +5020,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M44">
-        <v>67.39743517877508</v>
+        <v>69.00213601636497</v>
       </c>
       <c r="N44">
-        <v>471.2025648212248</v>
+        <v>469.597863983635</v>
       </c>
       <c r="O44">
-        <v>127.2246925017307</v>
+        <v>126.7914232755815</v>
       </c>
       <c r="P44">
-        <v>343.9778723194941</v>
+        <v>342.8064407080535</v>
       </c>
       <c r="Q44">
-        <v>714.3778723194941</v>
+        <v>713.2064407080536</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1277233848315153</v>
+        <v>0.1289067755677995</v>
       </c>
       <c r="T44">
-        <v>1.500455563493596</v>
+        <v>1.522129780418302</v>
       </c>
       <c r="U44">
         <v>0.06188110587651871</v>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.991402025482667</v>
+        <v>7.805555466750511</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09290134120828497</v>
+        <v>0.09275037215255039</v>
       </c>
       <c r="C45">
-        <v>1476.139913068823</v>
+        <v>1457.06116547378</v>
       </c>
       <c r="D45">
-        <v>2131.315913068823</v>
+        <v>2138.16916547378</v>
       </c>
       <c r="E45">
-        <v>-687.3240000000003</v>
+        <v>-661.3920000000001</v>
       </c>
       <c r="F45">
-        <v>1115.076</v>
+        <v>1141.008</v>
       </c>
       <c r="G45">
         <v>459.9</v>
@@ -5102,28 +5102,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M45">
-        <v>69.00213601636497</v>
+        <v>70.60683685395486</v>
       </c>
       <c r="N45">
-        <v>469.597863983635</v>
+        <v>467.993163146045</v>
       </c>
       <c r="O45">
-        <v>126.7914232755815</v>
+        <v>126.3581540494322</v>
       </c>
       <c r="P45">
-        <v>342.8064407080535</v>
+        <v>341.6350090966129</v>
       </c>
       <c r="Q45">
-        <v>713.2064407080536</v>
+        <v>712.0350090966128</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1289067755677995</v>
+        <v>0.130132430258951</v>
       </c>
       <c r="T45">
-        <v>1.522129780418302</v>
+        <v>1.544578076518891</v>
       </c>
       <c r="U45">
         <v>0.06188110587651871</v>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.805555466750511</v>
+        <v>7.628156478869816</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09275037215255039</v>
+        <v>0.09286220309681581</v>
       </c>
       <c r="C46">
-        <v>1457.06116547378</v>
+        <v>1426.048368973832</v>
       </c>
       <c r="D46">
-        <v>2138.16916547378</v>
+        <v>2133.088368973832</v>
       </c>
       <c r="E46">
-        <v>-661.3920000000001</v>
+        <v>-635.46</v>
       </c>
       <c r="F46">
-        <v>1141.008</v>
+        <v>1166.94</v>
       </c>
       <c r="G46">
         <v>459.9</v>
@@ -5184,45 +5184,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M46">
-        <v>70.60683685395486</v>
+        <v>73.14508969154474</v>
       </c>
       <c r="N46">
-        <v>467.993163146045</v>
+        <v>465.4549103084552</v>
       </c>
       <c r="O46">
-        <v>126.3581540494322</v>
+        <v>125.6728257832829</v>
       </c>
       <c r="P46">
-        <v>341.6350090966129</v>
+        <v>339.7820845251723</v>
       </c>
       <c r="Q46">
-        <v>712.0350090966128</v>
+        <v>710.1820845251723</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.130132430258951</v>
+        <v>0.1314026542115989</v>
       </c>
       <c r="T46">
-        <v>1.544578076518891</v>
+        <v>1.567842674295864</v>
       </c>
       <c r="U46">
-        <v>0.06188110587651871</v>
+        <v>0.06268110587651871</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.04517320728985866</v>
+        <v>0.04575720728985865</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.628156478869816</v>
+        <v>7.363447119571442</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09286220309681581</v>
+        <v>0.09271707404108127</v>
       </c>
       <c r="C47">
-        <v>1426.048368973832</v>
+        <v>1406.714672621592</v>
       </c>
       <c r="D47">
-        <v>2133.088368973832</v>
+        <v>2139.686672621592</v>
       </c>
       <c r="E47">
-        <v>-635.46</v>
+        <v>-609.528</v>
       </c>
       <c r="F47">
-        <v>1166.94</v>
+        <v>1192.872</v>
       </c>
       <c r="G47">
         <v>459.9</v>
@@ -5266,28 +5266,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M47">
-        <v>73.14508969154474</v>
+        <v>74.77053612913463</v>
       </c>
       <c r="N47">
-        <v>465.4549103084552</v>
+        <v>463.8294638708653</v>
       </c>
       <c r="O47">
-        <v>125.6728257832829</v>
+        <v>125.2339552451336</v>
       </c>
       <c r="P47">
-        <v>339.7820845251723</v>
+        <v>338.5955086257317</v>
       </c>
       <c r="Q47">
-        <v>710.1820845251723</v>
+        <v>708.9955086257316</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1314026542115989</v>
+        <v>0.1327199234958265</v>
       </c>
       <c r="T47">
-        <v>1.567842674295864</v>
+        <v>1.591968923842355</v>
       </c>
       <c r="U47">
         <v>0.06268110587651871</v>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.363447119571442</v>
+        <v>7.203372182189455</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09271707404108127</v>
+        <v>0.0925719449853467</v>
       </c>
       <c r="C48">
-        <v>1406.714672621592</v>
+        <v>1387.421924131503</v>
       </c>
       <c r="D48">
-        <v>2139.686672621592</v>
+        <v>2146.325924131503</v>
       </c>
       <c r="E48">
-        <v>-609.528</v>
+        <v>-583.596</v>
       </c>
       <c r="F48">
-        <v>1192.872</v>
+        <v>1218.804</v>
       </c>
       <c r="G48">
         <v>459.9</v>
@@ -5348,28 +5348,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M48">
-        <v>74.77053612913463</v>
+        <v>76.39598256672451</v>
       </c>
       <c r="N48">
-        <v>463.8294638708653</v>
+        <v>462.2040174332754</v>
       </c>
       <c r="O48">
-        <v>125.2339552451336</v>
+        <v>124.7950847069844</v>
       </c>
       <c r="P48">
-        <v>338.5955086257317</v>
+        <v>337.408932726291</v>
       </c>
       <c r="Q48">
-        <v>708.9955086257316</v>
+        <v>707.808932726291</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1327199234958265</v>
+        <v>0.1340869010549304</v>
       </c>
       <c r="T48">
-        <v>1.591968923842355</v>
+        <v>1.617005597900034</v>
       </c>
       <c r="U48">
         <v>0.06268110587651871</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.203372182189455</v>
+        <v>7.050108944270529</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0925719449853467</v>
+        <v>0.09242681592961213</v>
       </c>
       <c r="C49">
-        <v>1387.421924131503</v>
+        <v>1368.170505862369</v>
       </c>
       <c r="D49">
-        <v>2146.325924131503</v>
+        <v>2153.006505862369</v>
       </c>
       <c r="E49">
-        <v>-583.596</v>
+        <v>-557.664</v>
       </c>
       <c r="F49">
-        <v>1218.804</v>
+        <v>1244.736</v>
       </c>
       <c r="G49">
         <v>459.9</v>
@@ -5430,28 +5430,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M49">
-        <v>76.39598256672451</v>
+        <v>78.0214290043144</v>
       </c>
       <c r="N49">
-        <v>462.2040174332754</v>
+        <v>460.5785709956855</v>
       </c>
       <c r="O49">
-        <v>124.7950847069844</v>
+        <v>124.3562141688351</v>
       </c>
       <c r="P49">
-        <v>337.408932726291</v>
+        <v>336.2223568268504</v>
       </c>
       <c r="Q49">
-        <v>707.808932726291</v>
+        <v>706.6223568268504</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1340869010549304</v>
+        <v>0.1355064546739999</v>
       </c>
       <c r="T49">
-        <v>1.617005597900034</v>
+        <v>1.643005220959932</v>
       </c>
       <c r="U49">
         <v>0.06268110587651871</v>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.050108944270529</v>
+        <v>6.903231674598226</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09242681592961213</v>
+        <v>0.09228168687387756</v>
       </c>
       <c r="C50">
-        <v>1368.170505862369</v>
+        <v>1348.960804948331</v>
       </c>
       <c r="D50">
-        <v>2153.006505862369</v>
+        <v>2159.72880494833</v>
       </c>
       <c r="E50">
-        <v>-557.6640000000002</v>
+        <v>-531.7320000000002</v>
       </c>
       <c r="F50">
-        <v>1244.736</v>
+        <v>1270.668</v>
       </c>
       <c r="G50">
         <v>459.9</v>
@@ -5512,28 +5512,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M50">
-        <v>78.02142900431438</v>
+        <v>79.64687544190427</v>
       </c>
       <c r="N50">
-        <v>460.5785709956855</v>
+        <v>458.9531245580956</v>
       </c>
       <c r="O50">
-        <v>124.3562141688351</v>
+        <v>123.9173436306858</v>
       </c>
       <c r="P50">
-        <v>336.2223568268504</v>
+        <v>335.0357809274098</v>
       </c>
       <c r="Q50">
-        <v>706.6223568268505</v>
+        <v>705.4357809274098</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1355064546739999</v>
+        <v>0.1369816770624447</v>
       </c>
       <c r="T50">
-        <v>1.643005220959932</v>
+        <v>1.670024437081002</v>
       </c>
       <c r="U50">
         <v>0.06268110587651871</v>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.903231674598228</v>
+        <v>6.762349395524794</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09228168687387756</v>
+        <v>0.09213655781814299</v>
       </c>
       <c r="C51">
-        <v>1348.960804948331</v>
+        <v>1329.79321337364</v>
       </c>
       <c r="D51">
-        <v>2159.72880494833</v>
+        <v>2166.49321337364</v>
       </c>
       <c r="E51">
-        <v>-531.7320000000002</v>
+        <v>-505.8000000000002</v>
       </c>
       <c r="F51">
-        <v>1270.668</v>
+        <v>1296.6</v>
       </c>
       <c r="G51">
         <v>459.9</v>
@@ -5594,28 +5594,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M51">
-        <v>79.64687544190427</v>
+        <v>81.27232187949414</v>
       </c>
       <c r="N51">
-        <v>458.9531245580956</v>
+        <v>457.3276781205058</v>
       </c>
       <c r="O51">
-        <v>123.9173436306858</v>
+        <v>123.4784730925366</v>
       </c>
       <c r="P51">
-        <v>335.0357809274098</v>
+        <v>333.8492050279692</v>
       </c>
       <c r="Q51">
-        <v>705.4357809274098</v>
+        <v>704.2492050279693</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1369816770624447</v>
+        <v>0.1385159083464273</v>
       </c>
       <c r="T51">
-        <v>1.670024437081002</v>
+        <v>1.698124421846915</v>
       </c>
       <c r="U51">
         <v>0.06268110587651871</v>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.762349395524794</v>
+        <v>6.627102407614299</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09213655781814299</v>
+        <v>0.09199142876240841</v>
       </c>
       <c r="C52">
-        <v>1329.79321337364</v>
+        <v>1310.668128048862</v>
       </c>
       <c r="D52">
-        <v>2166.49321337364</v>
+        <v>2173.300128048862</v>
       </c>
       <c r="E52">
-        <v>-505.8000000000002</v>
+        <v>-479.8680000000002</v>
       </c>
       <c r="F52">
-        <v>1296.6</v>
+        <v>1322.532</v>
       </c>
       <c r="G52">
         <v>459.9</v>
@@ -5676,28 +5676,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M52">
-        <v>81.27232187949414</v>
+        <v>82.89776831708403</v>
       </c>
       <c r="N52">
-        <v>457.3276781205058</v>
+        <v>455.7022316829159</v>
       </c>
       <c r="O52">
-        <v>123.4784730925366</v>
+        <v>123.0396025543873</v>
       </c>
       <c r="P52">
-        <v>333.8492050279692</v>
+        <v>332.6626291285286</v>
       </c>
       <c r="Q52">
-        <v>704.2492050279693</v>
+        <v>703.0626291285287</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1385159083464273</v>
+        <v>0.1401127613154704</v>
       </c>
       <c r="T52">
-        <v>1.698124421846915</v>
+        <v>1.727371344766539</v>
       </c>
       <c r="U52">
         <v>0.06268110587651871</v>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.627102407614299</v>
+        <v>6.497159223151273</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09199142876240841</v>
+        <v>0.09184629970667386</v>
       </c>
       <c r="C53">
-        <v>1310.668128048862</v>
+        <v>1291.585950888497</v>
       </c>
       <c r="D53">
-        <v>2173.300128048862</v>
+        <v>2180.149950888497</v>
       </c>
       <c r="E53">
-        <v>-479.8680000000002</v>
+        <v>-453.9360000000001</v>
       </c>
       <c r="F53">
-        <v>1322.532</v>
+        <v>1348.464</v>
       </c>
       <c r="G53">
         <v>459.9</v>
@@ -5758,28 +5758,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M53">
-        <v>82.89776831708403</v>
+        <v>84.52321475467392</v>
       </c>
       <c r="N53">
-        <v>455.7022316829159</v>
+        <v>454.076785245326</v>
       </c>
       <c r="O53">
-        <v>123.0396025543873</v>
+        <v>122.600732016238</v>
       </c>
       <c r="P53">
-        <v>332.6626291285286</v>
+        <v>331.4760532290879</v>
       </c>
       <c r="Q53">
-        <v>703.0626291285287</v>
+        <v>701.876053229088</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1401127613154704</v>
+        <v>0.1417761498248903</v>
       </c>
       <c r="T53">
-        <v>1.727371344766539</v>
+        <v>1.75783688947448</v>
       </c>
       <c r="U53">
         <v>0.06268110587651871</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.497159223151273</v>
+        <v>6.372213853475287</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09184629970667386</v>
+        <v>0.0917011706509393</v>
       </c>
       <c r="C54">
-        <v>1291.585950888497</v>
+        <v>1272.547088890104</v>
       </c>
       <c r="D54">
-        <v>2180.149950888497</v>
+        <v>2187.043088890104</v>
       </c>
       <c r="E54">
-        <v>-453.9360000000001</v>
+        <v>-428.0040000000001</v>
       </c>
       <c r="F54">
-        <v>1348.464</v>
+        <v>1374.396</v>
       </c>
       <c r="G54">
         <v>459.9</v>
@@ -5840,28 +5840,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M54">
-        <v>84.52321475467392</v>
+        <v>86.1486611922638</v>
       </c>
       <c r="N54">
-        <v>454.076785245326</v>
+        <v>452.4513388077361</v>
       </c>
       <c r="O54">
-        <v>122.600732016238</v>
+        <v>122.1618614780888</v>
       </c>
       <c r="P54">
-        <v>331.4760532290879</v>
+        <v>330.2894773296473</v>
       </c>
       <c r="Q54">
-        <v>701.876053229088</v>
+        <v>700.6894773296474</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1417761498248903</v>
+        <v>0.1435103208240728</v>
       </c>
       <c r="T54">
-        <v>1.75783688947448</v>
+        <v>1.789598840340206</v>
       </c>
       <c r="U54">
         <v>0.06268110587651871</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.372213853475287</v>
+        <v>6.251983403409715</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0917011706509393</v>
+        <v>0.09155604159520472</v>
       </c>
       <c r="C55">
-        <v>1272.547088890104</v>
+        <v>1253.551954214895</v>
       </c>
       <c r="D55">
-        <v>2187.043088890104</v>
+        <v>2193.979954214894</v>
       </c>
       <c r="E55">
-        <v>-428.0040000000001</v>
+        <v>-402.0720000000001</v>
       </c>
       <c r="F55">
-        <v>1374.396</v>
+        <v>1400.328</v>
       </c>
       <c r="G55">
         <v>459.9</v>
@@ -5922,28 +5922,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M55">
-        <v>86.1486611922638</v>
+        <v>87.77410762985369</v>
       </c>
       <c r="N55">
-        <v>452.4513388077361</v>
+        <v>450.8258923701462</v>
       </c>
       <c r="O55">
-        <v>122.1618614780888</v>
+        <v>121.7229909399395</v>
       </c>
       <c r="P55">
-        <v>330.2894773296473</v>
+        <v>329.1029014302067</v>
       </c>
       <c r="Q55">
-        <v>700.6894773296474</v>
+        <v>699.5029014302067</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1435103208240728</v>
+        <v>0.1453198905623501</v>
       </c>
       <c r="T55">
-        <v>1.789598840340206</v>
+        <v>1.822741745591398</v>
       </c>
       <c r="U55">
         <v>0.06268110587651871</v>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.251983403409715</v>
+        <v>6.136205932976202</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09155604159520472</v>
+        <v>0.09181241253947017</v>
       </c>
       <c r="C56">
-        <v>1253.551954214895</v>
+        <v>1215.395585147547</v>
       </c>
       <c r="D56">
-        <v>2193.979954214894</v>
+        <v>2181.755585147547</v>
       </c>
       <c r="E56">
-        <v>-402.0720000000001</v>
+        <v>-376.1400000000001</v>
       </c>
       <c r="F56">
-        <v>1400.328</v>
+        <v>1426.26</v>
       </c>
       <c r="G56">
         <v>459.9</v>
@@ -6004,45 +6004,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M56">
-        <v>87.77410762985369</v>
+        <v>90.82581406744357</v>
       </c>
       <c r="N56">
-        <v>450.8258923701462</v>
+        <v>447.7741859325563</v>
       </c>
       <c r="O56">
-        <v>121.7229909399395</v>
+        <v>120.8990302017902</v>
       </c>
       <c r="P56">
-        <v>329.1029014302067</v>
+        <v>326.8751557307661</v>
       </c>
       <c r="Q56">
-        <v>699.5029014302067</v>
+        <v>697.2751557307661</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1453198905623501</v>
+        <v>0.1472098856223287</v>
       </c>
       <c r="T56">
-        <v>1.822741745591398</v>
+        <v>1.857357668853755</v>
       </c>
       <c r="U56">
-        <v>0.06268110587651871</v>
+        <v>0.06368110587651871</v>
       </c>
       <c r="V56">
         <v>0.27</v>
       </c>
       <c r="W56">
-        <v>0.04575720728985865</v>
+        <v>0.04648720728985865</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>6.136205932976202</v>
+        <v>5.930032177857028</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09181241253947017</v>
+        <v>0.0916745834837356</v>
       </c>
       <c r="C57">
-        <v>1215.395585147547</v>
+        <v>1196.018616045018</v>
       </c>
       <c r="D57">
-        <v>2181.755585147547</v>
+        <v>2188.310616045018</v>
       </c>
       <c r="E57">
-        <v>-376.1400000000001</v>
+        <v>-350.2080000000001</v>
       </c>
       <c r="F57">
-        <v>1426.26</v>
+        <v>1452.192</v>
       </c>
       <c r="G57">
         <v>459.9</v>
@@ -6086,28 +6086,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M57">
-        <v>90.82581406744357</v>
+        <v>92.47719250503346</v>
       </c>
       <c r="N57">
-        <v>447.7741859325563</v>
+        <v>446.1228074949664</v>
       </c>
       <c r="O57">
-        <v>120.8990302017902</v>
+        <v>120.4531580236409</v>
       </c>
       <c r="P57">
-        <v>326.8751557307661</v>
+        <v>325.6696494713255</v>
       </c>
       <c r="Q57">
-        <v>697.2751557307661</v>
+        <v>696.0696494713255</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1472098856223287</v>
+        <v>0.1491857895486699</v>
       </c>
       <c r="T57">
-        <v>1.857357668853755</v>
+        <v>1.893547043173491</v>
       </c>
       <c r="U57">
         <v>0.06368110587651871</v>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.930032177857028</v>
+        <v>5.824138746109581</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0916745834837356</v>
+        <v>0.09153675442800102</v>
       </c>
       <c r="C58">
-        <v>1196.018616045018</v>
+        <v>1176.681154499605</v>
       </c>
       <c r="D58">
-        <v>2188.310616045018</v>
+        <v>2194.905154499605</v>
       </c>
       <c r="E58">
-        <v>-350.2080000000001</v>
+        <v>-324.2760000000001</v>
       </c>
       <c r="F58">
-        <v>1452.192</v>
+        <v>1478.124</v>
       </c>
       <c r="G58">
         <v>459.9</v>
@@ -6168,28 +6168,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M58">
-        <v>92.47719250503346</v>
+        <v>94.12857094262334</v>
       </c>
       <c r="N58">
-        <v>446.1228074949664</v>
+        <v>444.4714290573766</v>
       </c>
       <c r="O58">
-        <v>120.4531580236409</v>
+        <v>120.0072858454917</v>
       </c>
       <c r="P58">
-        <v>325.6696494713255</v>
+        <v>324.4641432118849</v>
       </c>
       <c r="Q58">
-        <v>696.0696494713255</v>
+        <v>694.864143211885</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1491857895486699</v>
+        <v>0.151253595983213</v>
       </c>
       <c r="T58">
-        <v>1.893547043173491</v>
+        <v>1.931419644205774</v>
       </c>
       <c r="U58">
         <v>0.06368110587651871</v>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.824138746109581</v>
+        <v>5.721960873370817</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09153675442800102</v>
+        <v>0.09139892537226647</v>
       </c>
       <c r="C59">
-        <v>1176.681154499605</v>
+        <v>1157.383558762464</v>
       </c>
       <c r="D59">
-        <v>2194.905154499605</v>
+        <v>2201.539558762464</v>
       </c>
       <c r="E59">
-        <v>-324.2760000000001</v>
+        <v>-298.3440000000001</v>
       </c>
       <c r="F59">
-        <v>1478.124</v>
+        <v>1504.056</v>
       </c>
       <c r="G59">
         <v>459.9</v>
@@ -6250,28 +6250,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M59">
-        <v>94.12857094262334</v>
+        <v>95.77994938021322</v>
       </c>
       <c r="N59">
-        <v>444.4714290573766</v>
+        <v>442.8200506197867</v>
       </c>
       <c r="O59">
-        <v>120.0072858454917</v>
+        <v>119.5614136673424</v>
       </c>
       <c r="P59">
-        <v>324.4641432118849</v>
+        <v>323.2586369524442</v>
       </c>
       <c r="Q59">
-        <v>694.864143211885</v>
+        <v>693.6586369524443</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.151253595983213</v>
+        <v>0.1534198693908297</v>
       </c>
       <c r="T59">
-        <v>1.931419644205774</v>
+        <v>1.971095702430069</v>
       </c>
       <c r="U59">
         <v>0.06368110587651871</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.721960873370817</v>
+        <v>5.623306375554078</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09139892537226646</v>
+        <v>0.0912610963165319</v>
       </c>
       <c r="C60">
-        <v>1157.383558762465</v>
+        <v>1138.126191429345</v>
       </c>
       <c r="D60">
-        <v>2201.539558762465</v>
+        <v>2208.214191429345</v>
       </c>
       <c r="E60">
-        <v>-298.3440000000003</v>
+        <v>-272.4120000000003</v>
       </c>
       <c r="F60">
-        <v>1504.056</v>
+        <v>1529.988</v>
       </c>
       <c r="G60">
         <v>459.9</v>
@@ -6332,28 +6332,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M60">
-        <v>95.77994938021321</v>
+        <v>97.43132781780309</v>
       </c>
       <c r="N60">
-        <v>442.8200506197867</v>
+        <v>441.1686721821968</v>
       </c>
       <c r="O60">
-        <v>119.5614136673424</v>
+        <v>119.1155414891931</v>
       </c>
       <c r="P60">
-        <v>323.2586369524442</v>
+        <v>322.0531306930037</v>
       </c>
       <c r="Q60">
-        <v>693.6586369524443</v>
+        <v>692.4531306930037</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1534198693908296</v>
+        <v>0.1556918146719885</v>
       </c>
       <c r="T60">
-        <v>1.971095702430069</v>
+        <v>2.01270717812872</v>
       </c>
       <c r="U60">
         <v>0.06368110587651871</v>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.623306375554079</v>
+        <v>5.527996098002315</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0912610963165319</v>
+        <v>0.09112326726079732</v>
       </c>
       <c r="C61">
-        <v>1138.126191429345</v>
+        <v>1118.909419506639</v>
       </c>
       <c r="D61">
-        <v>2208.214191429345</v>
+        <v>2214.929419506639</v>
       </c>
       <c r="E61">
-        <v>-272.4120000000003</v>
+        <v>-246.4800000000002</v>
       </c>
       <c r="F61">
-        <v>1529.988</v>
+        <v>1555.92</v>
       </c>
       <c r="G61">
         <v>459.9</v>
@@ -6414,28 +6414,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M61">
-        <v>97.43132781780309</v>
+        <v>99.08270625539298</v>
       </c>
       <c r="N61">
-        <v>441.1686721821968</v>
+        <v>439.5172937446069</v>
       </c>
       <c r="O61">
-        <v>119.1155414891931</v>
+        <v>118.6696693110439</v>
       </c>
       <c r="P61">
-        <v>322.0531306930037</v>
+        <v>320.8476244335631</v>
       </c>
       <c r="Q61">
-        <v>692.4531306930037</v>
+        <v>691.247624433563</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1556918146719885</v>
+        <v>0.1580773572172053</v>
       </c>
       <c r="T61">
-        <v>2.01270717812872</v>
+        <v>2.056399227612304</v>
       </c>
       <c r="U61">
         <v>0.06368110587651871</v>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.527996098002315</v>
+        <v>5.435862829702277</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09112326726079732</v>
+        <v>0.09098543820506276</v>
       </c>
       <c r="C62">
-        <v>1118.909419506639</v>
+        <v>1099.733614478653</v>
       </c>
       <c r="D62">
-        <v>2214.929419506639</v>
+        <v>2221.685614478653</v>
       </c>
       <c r="E62">
-        <v>-246.4800000000002</v>
+        <v>-220.5480000000002</v>
       </c>
       <c r="F62">
-        <v>1555.92</v>
+        <v>1581.852</v>
       </c>
       <c r="G62">
         <v>459.9</v>
@@ -6496,28 +6496,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M62">
-        <v>99.08270625539298</v>
+        <v>100.7340846929829</v>
       </c>
       <c r="N62">
-        <v>439.5172937446069</v>
+        <v>437.8659153070171</v>
       </c>
       <c r="O62">
-        <v>118.6696693110439</v>
+        <v>118.2237971328946</v>
       </c>
       <c r="P62">
-        <v>320.8476244335631</v>
+        <v>319.6421181741225</v>
       </c>
       <c r="Q62">
-        <v>691.247624433563</v>
+        <v>690.0421181741225</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1580773572172053</v>
+        <v>0.1605852352775615</v>
       </c>
       <c r="T62">
-        <v>2.056399227612304</v>
+        <v>2.102331895018124</v>
       </c>
       <c r="U62">
         <v>0.06368110587651871</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.435862829702277</v>
+        <v>5.346750324297322</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09098543820506276</v>
+        <v>0.09084760914932821</v>
       </c>
       <c r="C63">
-        <v>1099.733614478653</v>
+        <v>1080.599152376115</v>
       </c>
       <c r="D63">
-        <v>2221.685614478653</v>
+        <v>2228.483152376115</v>
       </c>
       <c r="E63">
-        <v>-220.5480000000002</v>
+        <v>-194.6160000000002</v>
       </c>
       <c r="F63">
-        <v>1581.852</v>
+        <v>1607.784</v>
       </c>
       <c r="G63">
         <v>459.9</v>
@@ -6578,28 +6578,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M63">
-        <v>100.7340846929829</v>
+        <v>102.3854631305727</v>
       </c>
       <c r="N63">
-        <v>437.8659153070171</v>
+        <v>436.2145368694271</v>
       </c>
       <c r="O63">
-        <v>118.2237971328946</v>
+        <v>117.7779249547453</v>
       </c>
       <c r="P63">
-        <v>319.6421181741225</v>
+        <v>318.4366119146818</v>
       </c>
       <c r="Q63">
-        <v>690.0421181741225</v>
+        <v>688.8366119146818</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1605852352775615</v>
+        <v>0.1632251069200417</v>
       </c>
       <c r="T63">
-        <v>2.102331895018124</v>
+        <v>2.150682071234776</v>
       </c>
       <c r="U63">
         <v>0.06368110587651871</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.346750324297322</v>
+        <v>5.260512415840912</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09084760914932821</v>
+        <v>0.09070978009359362</v>
       </c>
       <c r="C64">
-        <v>1080.599152376115</v>
+        <v>1061.506413845941</v>
       </c>
       <c r="D64">
-        <v>2228.483152376115</v>
+        <v>2235.32241384594</v>
       </c>
       <c r="E64">
-        <v>-194.6160000000002</v>
+        <v>-168.6840000000002</v>
       </c>
       <c r="F64">
-        <v>1607.784</v>
+        <v>1633.716</v>
       </c>
       <c r="G64">
         <v>459.9</v>
@@ -6660,28 +6660,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M64">
-        <v>102.3854631305727</v>
+        <v>104.0368415681626</v>
       </c>
       <c r="N64">
-        <v>436.2145368694271</v>
+        <v>434.5631584318373</v>
       </c>
       <c r="O64">
-        <v>117.7779249547453</v>
+        <v>117.3320527765961</v>
       </c>
       <c r="P64">
-        <v>318.4366119146818</v>
+        <v>317.2311056552412</v>
       </c>
       <c r="Q64">
-        <v>688.8366119146818</v>
+        <v>687.6311056552413</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1632251069200417</v>
+        <v>0.1660076743269802</v>
       </c>
       <c r="T64">
-        <v>2.150682071234776</v>
+        <v>2.201645770490165</v>
       </c>
       <c r="U64">
         <v>0.06368110587651871</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.260512415840912</v>
+        <v>5.177012218764073</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09070978009359362</v>
+        <v>0.09057195103785907</v>
       </c>
       <c r="C65">
-        <v>1061.506413845941</v>
+        <v>1042.455784222276</v>
       </c>
       <c r="D65">
-        <v>2235.32241384594</v>
+        <v>2242.203784222276</v>
       </c>
       <c r="E65">
-        <v>-168.6840000000002</v>
+        <v>-142.7520000000002</v>
       </c>
       <c r="F65">
-        <v>1633.716</v>
+        <v>1659.648</v>
       </c>
       <c r="G65">
         <v>459.9</v>
@@ -6742,28 +6742,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M65">
-        <v>104.0368415681626</v>
+        <v>105.6882200057525</v>
       </c>
       <c r="N65">
-        <v>434.5631584318373</v>
+        <v>432.9117799942474</v>
       </c>
       <c r="O65">
-        <v>117.3320527765961</v>
+        <v>116.8861805984468</v>
       </c>
       <c r="P65">
-        <v>317.2311056552412</v>
+        <v>316.0255993958006</v>
       </c>
       <c r="Q65">
-        <v>687.6311056552413</v>
+        <v>686.4255993958006</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1660076743269802</v>
+        <v>0.1689448288120821</v>
       </c>
       <c r="T65">
-        <v>2.201645770490165</v>
+        <v>2.255440786370855</v>
       </c>
       <c r="U65">
         <v>0.06368110587651871</v>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.177012218764073</v>
+        <v>5.096121402845884</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09057195103785907</v>
+        <v>0.09043412198212451</v>
       </c>
       <c r="C66">
-        <v>1042.455784222276</v>
+        <v>1023.447653598884</v>
       </c>
       <c r="D66">
-        <v>2242.203784222276</v>
+        <v>2249.127653598884</v>
       </c>
       <c r="E66">
-        <v>-142.7520000000002</v>
+        <v>-116.8200000000002</v>
       </c>
       <c r="F66">
-        <v>1659.648</v>
+        <v>1685.58</v>
       </c>
       <c r="G66">
         <v>459.9</v>
@@ -6824,28 +6824,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M66">
-        <v>105.6882200057525</v>
+        <v>107.3395984433424</v>
       </c>
       <c r="N66">
-        <v>432.9117799942474</v>
+        <v>431.2604015566575</v>
       </c>
       <c r="O66">
-        <v>116.8861805984468</v>
+        <v>116.4403084202975</v>
       </c>
       <c r="P66">
-        <v>316.0255993958006</v>
+        <v>314.82009313636</v>
       </c>
       <c r="Q66">
-        <v>686.4255993958006</v>
+        <v>685.22009313636</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1689448288120821</v>
+        <v>0.1720498206963325</v>
       </c>
       <c r="T66">
-        <v>2.255440786370855</v>
+        <v>2.312309803159012</v>
       </c>
       <c r="U66">
         <v>0.06368110587651871</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.096121402845884</v>
+        <v>5.017719535109793</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09043412198212451</v>
+        <v>0.09029629292638994</v>
       </c>
       <c r="C67">
-        <v>1023.447653598884</v>
+        <v>1004.482416902849</v>
       </c>
       <c r="D67">
-        <v>2249.127653598884</v>
+        <v>2256.094416902848</v>
       </c>
       <c r="E67">
-        <v>-116.8200000000002</v>
+        <v>-90.88800000000015</v>
       </c>
       <c r="F67">
-        <v>1685.58</v>
+        <v>1711.512</v>
       </c>
       <c r="G67">
         <v>459.9</v>
@@ -6906,28 +6906,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M67">
-        <v>107.3395984433424</v>
+        <v>108.9909768809323</v>
       </c>
       <c r="N67">
-        <v>431.2604015566575</v>
+        <v>429.6090231190676</v>
       </c>
       <c r="O67">
-        <v>116.4403084202975</v>
+        <v>115.9944362421483</v>
       </c>
       <c r="P67">
-        <v>314.82009313636</v>
+        <v>313.6145868769194</v>
       </c>
       <c r="Q67">
-        <v>685.22009313636</v>
+        <v>684.0145868769193</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1720498206963325</v>
+        <v>0.1753374591620095</v>
       </c>
       <c r="T67">
-        <v>2.312309803159012</v>
+        <v>2.372524056228825</v>
       </c>
       <c r="U67">
         <v>0.06368110587651871</v>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.017719535109793</v>
+        <v>4.941693481547524</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09029629292638994</v>
+        <v>0.09015846387065538</v>
       </c>
       <c r="C68">
-        <v>1004.482416902849</v>
+        <v>985.5604739696682</v>
       </c>
       <c r="D68">
-        <v>2256.094416902848</v>
+        <v>2263.104473969668</v>
       </c>
       <c r="E68">
-        <v>-90.88800000000015</v>
+        <v>-64.95600000000013</v>
       </c>
       <c r="F68">
-        <v>1711.512</v>
+        <v>1737.444</v>
       </c>
       <c r="G68">
         <v>459.9</v>
@@ -6988,28 +6988,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M68">
-        <v>108.9909768809323</v>
+        <v>110.6423553185222</v>
       </c>
       <c r="N68">
-        <v>429.6090231190676</v>
+        <v>427.9576446814777</v>
       </c>
       <c r="O68">
-        <v>115.9944362421483</v>
+        <v>115.548564063999</v>
       </c>
       <c r="P68">
-        <v>313.6145868769194</v>
+        <v>312.4090806174788</v>
       </c>
       <c r="Q68">
-        <v>684.0145868769193</v>
+        <v>682.8090806174788</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1753374591620095</v>
+        <v>0.1788243484437881</v>
       </c>
       <c r="T68">
-        <v>2.372524056228825</v>
+        <v>2.436387657969536</v>
       </c>
       <c r="U68">
         <v>0.06368110587651871</v>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.941693481547524</v>
+        <v>4.867936862419949</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09015846387065538</v>
+        <v>0.09002063481492081</v>
       </c>
       <c r="C69">
-        <v>985.5604739696682</v>
+        <v>966.682229619749</v>
       </c>
       <c r="D69">
-        <v>2263.104473969668</v>
+        <v>2270.158229619749</v>
       </c>
       <c r="E69">
-        <v>-64.95600000000013</v>
+        <v>-39.02400000000011</v>
       </c>
       <c r="F69">
-        <v>1737.444</v>
+        <v>1763.376</v>
       </c>
       <c r="G69">
         <v>459.9</v>
@@ -7070,28 +7070,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M69">
-        <v>110.6423553185222</v>
+        <v>112.293733756112</v>
       </c>
       <c r="N69">
-        <v>427.9576446814777</v>
+        <v>426.3062662438879</v>
       </c>
       <c r="O69">
-        <v>115.548564063999</v>
+        <v>115.1026918858497</v>
       </c>
       <c r="P69">
-        <v>312.4090806174788</v>
+        <v>311.2035743580382</v>
       </c>
       <c r="Q69">
-        <v>682.8090806174788</v>
+        <v>681.6035743580383</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1788243484437881</v>
+        <v>0.1825291683056779</v>
       </c>
       <c r="T69">
-        <v>2.436387657969536</v>
+        <v>2.504242734819042</v>
       </c>
       <c r="U69">
         <v>0.06368110587651871</v>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.867936862419949</v>
+        <v>4.796349555619655</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09002063481492081</v>
+        <v>0.08988280575918622</v>
       </c>
       <c r="C70">
-        <v>966.682229619749</v>
+        <v>947.8480937363361</v>
       </c>
       <c r="D70">
-        <v>2270.158229619749</v>
+        <v>2277.256093736336</v>
       </c>
       <c r="E70">
-        <v>-39.02400000000011</v>
+        <v>-13.0920000000001</v>
       </c>
       <c r="F70">
-        <v>1763.376</v>
+        <v>1789.308</v>
       </c>
       <c r="G70">
         <v>459.9</v>
@@ -7152,28 +7152,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M70">
-        <v>112.293733756112</v>
+        <v>113.9451121937019</v>
       </c>
       <c r="N70">
-        <v>426.3062662438879</v>
+        <v>424.654887806298</v>
       </c>
       <c r="O70">
-        <v>115.1026918858497</v>
+        <v>114.6568197077005</v>
       </c>
       <c r="P70">
-        <v>311.2035743580382</v>
+        <v>309.9980680985975</v>
       </c>
       <c r="Q70">
-        <v>681.6035743580383</v>
+        <v>680.3980680985976</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1825291683056779</v>
+        <v>0.1864730088038186</v>
       </c>
       <c r="T70">
-        <v>2.504242734819042</v>
+        <v>2.576475558562064</v>
       </c>
       <c r="U70">
         <v>0.06368110587651871</v>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.796349555619655</v>
+        <v>4.726837243219371</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08988280575918622</v>
+        <v>0.08974497670345169</v>
       </c>
       <c r="C71">
-        <v>947.8480937363361</v>
+        <v>929.0584813449007</v>
       </c>
       <c r="D71">
-        <v>2277.256093736336</v>
+        <v>2284.398481344901</v>
       </c>
       <c r="E71">
-        <v>-13.0920000000001</v>
+        <v>12.83999999999992</v>
       </c>
       <c r="F71">
-        <v>1789.308</v>
+        <v>1815.24</v>
       </c>
       <c r="G71">
         <v>459.9</v>
@@ -7234,28 +7234,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M71">
-        <v>113.9451121937019</v>
+        <v>115.5964906312918</v>
       </c>
       <c r="N71">
-        <v>424.654887806298</v>
+        <v>423.0035093687081</v>
       </c>
       <c r="O71">
-        <v>114.6568197077005</v>
+        <v>114.2109475295512</v>
       </c>
       <c r="P71">
-        <v>309.9980680985975</v>
+        <v>308.7925618391569</v>
       </c>
       <c r="Q71">
-        <v>680.3980680985976</v>
+        <v>679.192561839157</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1864730088038186</v>
+        <v>0.1906797720018354</v>
       </c>
       <c r="T71">
-        <v>2.576475558562064</v>
+        <v>2.653523903887955</v>
       </c>
       <c r="U71">
         <v>0.06368110587651871</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.726837243219371</v>
+        <v>4.659310996887665</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08974497670345169</v>
+        <v>0.0896071476477171</v>
       </c>
       <c r="C72">
-        <v>929.0584813449007</v>
+        <v>910.3138126940507</v>
       </c>
       <c r="D72">
-        <v>2284.398481344901</v>
+        <v>2291.585812694051</v>
       </c>
       <c r="E72">
-        <v>12.83999999999992</v>
+        <v>38.77199999999993</v>
       </c>
       <c r="F72">
-        <v>1815.24</v>
+        <v>1841.172</v>
       </c>
       <c r="G72">
         <v>459.9</v>
@@ -7316,28 +7316,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M72">
-        <v>115.5964906312918</v>
+        <v>117.2478690688817</v>
       </c>
       <c r="N72">
-        <v>423.0035093687081</v>
+        <v>421.3521309311182</v>
       </c>
       <c r="O72">
-        <v>114.2109475295512</v>
+        <v>113.7650753514019</v>
       </c>
       <c r="P72">
-        <v>308.7925618391569</v>
+        <v>307.5870555797163</v>
       </c>
       <c r="Q72">
-        <v>679.192561839157</v>
+        <v>677.9870555797163</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1906797720018354</v>
+        <v>0.1951766567997154</v>
       </c>
       <c r="T72">
-        <v>2.653523903887955</v>
+        <v>2.735885928201837</v>
       </c>
       <c r="U72">
         <v>0.06368110587651871</v>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.659310996887665</v>
+        <v>4.593686898339952</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08960714764771711</v>
+        <v>0.08946931859198254</v>
       </c>
       <c r="C73">
-        <v>910.3138126940501</v>
+        <v>891.6145133379382</v>
       </c>
       <c r="D73">
-        <v>2291.58581269405</v>
+        <v>2298.818513337938</v>
       </c>
       <c r="E73">
-        <v>38.77199999999971</v>
+        <v>64.70399999999972</v>
       </c>
       <c r="F73">
-        <v>1841.172</v>
+        <v>1867.104</v>
       </c>
       <c r="G73">
         <v>459.9</v>
@@ -7398,28 +7398,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M73">
-        <v>117.2478690688817</v>
+        <v>118.8992475064716</v>
       </c>
       <c r="N73">
-        <v>421.3521309311182</v>
+        <v>419.7007524935283</v>
       </c>
       <c r="O73">
-        <v>113.7650753514019</v>
+        <v>113.3192031732527</v>
       </c>
       <c r="P73">
-        <v>307.5870555797163</v>
+        <v>306.3815493202757</v>
       </c>
       <c r="Q73">
-        <v>677.9870555797163</v>
+        <v>676.7815493202756</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1951766567997154</v>
+        <v>0.1999947476545868</v>
       </c>
       <c r="T73">
-        <v>2.735885928201836</v>
+        <v>2.824130954252425</v>
       </c>
       <c r="U73">
         <v>0.06368110587651871</v>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.593686898339952</v>
+        <v>4.529885691418563</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08946931859198254</v>
+        <v>0.09066373953624798</v>
       </c>
       <c r="C74">
-        <v>891.6145133379382</v>
+        <v>804.4803708554207</v>
       </c>
       <c r="D74">
-        <v>2298.818513337938</v>
+        <v>2237.61637085542</v>
       </c>
       <c r="E74">
-        <v>64.70399999999972</v>
+        <v>90.63599999999974</v>
       </c>
       <c r="F74">
-        <v>1867.104</v>
+        <v>1893.036</v>
       </c>
       <c r="G74">
         <v>459.9</v>
@@ -7480,45 +7480,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M74">
-        <v>118.8992475064716</v>
+        <v>125.2832159440615</v>
       </c>
       <c r="N74">
-        <v>419.7007524935283</v>
+        <v>413.3167840559385</v>
       </c>
       <c r="O74">
-        <v>113.3192031732527</v>
+        <v>111.5955316951034</v>
       </c>
       <c r="P74">
-        <v>306.3815493202757</v>
+        <v>301.7212523608351</v>
       </c>
       <c r="Q74">
-        <v>676.7815493202756</v>
+        <v>672.1212523608351</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1999947476545868</v>
+        <v>0.2051697341283376</v>
       </c>
       <c r="T74">
-        <v>2.824130954252425</v>
+        <v>2.918912648899353</v>
       </c>
       <c r="U74">
-        <v>0.06368110587651871</v>
+        <v>0.06618110587651871</v>
       </c>
       <c r="V74">
         <v>0.27</v>
       </c>
       <c r="W74">
-        <v>0.04648720728985865</v>
+        <v>0.04831220728985865</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y74">
-        <v>4.529885691418563</v>
+        <v>4.29905950243553</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09066373953624798</v>
+        <v>0.09054416048051342</v>
       </c>
       <c r="C75">
-        <v>804.4803708554207</v>
+        <v>784.5284149516697</v>
       </c>
       <c r="D75">
-        <v>2237.61637085542</v>
+        <v>2243.596414951669</v>
       </c>
       <c r="E75">
-        <v>90.63599999999974</v>
+        <v>116.5679999999998</v>
       </c>
       <c r="F75">
-        <v>1893.036</v>
+        <v>1918.968</v>
       </c>
       <c r="G75">
         <v>459.9</v>
@@ -7562,28 +7562,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M75">
-        <v>125.2832159440615</v>
+        <v>126.9994243816513</v>
       </c>
       <c r="N75">
-        <v>413.3167840559385</v>
+        <v>411.6005756183486</v>
       </c>
       <c r="O75">
-        <v>111.5955316951034</v>
+        <v>111.1321554169541</v>
       </c>
       <c r="P75">
-        <v>301.7212523608351</v>
+        <v>300.4684202013945</v>
       </c>
       <c r="Q75">
-        <v>672.1212523608351</v>
+        <v>670.8684202013944</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2051697341283376</v>
+        <v>0.2107427964846847</v>
       </c>
       <c r="T75">
-        <v>2.918912648899353</v>
+        <v>3.020985243134507</v>
       </c>
       <c r="U75">
         <v>0.06618110587651871</v>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.29905950243553</v>
+        <v>4.240964103753969</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09054416048051342</v>
+        <v>0.09042458142477885</v>
       </c>
       <c r="C76">
-        <v>784.5284149516697</v>
+        <v>764.6085081116155</v>
       </c>
       <c r="D76">
-        <v>2243.596414951669</v>
+        <v>2249.608508111615</v>
       </c>
       <c r="E76">
-        <v>116.5679999999998</v>
+        <v>142.4999999999998</v>
       </c>
       <c r="F76">
-        <v>1918.968</v>
+        <v>1944.9</v>
       </c>
       <c r="G76">
         <v>459.9</v>
@@ -7644,28 +7644,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M76">
-        <v>126.9994243816513</v>
+        <v>128.7156328192412</v>
       </c>
       <c r="N76">
-        <v>411.6005756183486</v>
+        <v>409.8843671807587</v>
       </c>
       <c r="O76">
-        <v>111.1321554169541</v>
+        <v>110.6687791388049</v>
       </c>
       <c r="P76">
-        <v>300.4684202013945</v>
+        <v>299.2155880419538</v>
       </c>
       <c r="Q76">
-        <v>670.8684202013944</v>
+        <v>669.6155880419539</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2107427964846847</v>
+        <v>0.2167617038295394</v>
       </c>
       <c r="T76">
-        <v>3.020985243134507</v>
+        <v>3.131223644908473</v>
       </c>
       <c r="U76">
         <v>0.06618110587651871</v>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.240964103753969</v>
+        <v>4.184417915703916</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09042458142477885</v>
+        <v>0.09030500236904428</v>
       </c>
       <c r="C77">
-        <v>764.6085081116155</v>
+        <v>744.7209086700473</v>
       </c>
       <c r="D77">
-        <v>2249.608508111615</v>
+        <v>2255.652908670047</v>
       </c>
       <c r="E77">
-        <v>142.4999999999998</v>
+        <v>168.4319999999998</v>
       </c>
       <c r="F77">
-        <v>1944.9</v>
+        <v>1970.832</v>
       </c>
       <c r="G77">
         <v>459.9</v>
@@ -7726,28 +7726,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M77">
-        <v>128.7156328192412</v>
+        <v>130.4318412568311</v>
       </c>
       <c r="N77">
-        <v>409.8843671807587</v>
+        <v>408.1681587431688</v>
       </c>
       <c r="O77">
-        <v>110.6687791388049</v>
+        <v>110.2054028606556</v>
       </c>
       <c r="P77">
-        <v>299.2155880419538</v>
+        <v>297.9627558825132</v>
       </c>
       <c r="Q77">
-        <v>669.6155880419539</v>
+        <v>668.3627558825133</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2167617038295394</v>
+        <v>0.2232821867864654</v>
       </c>
       <c r="T77">
-        <v>3.131223644908473</v>
+        <v>3.250648580163603</v>
       </c>
       <c r="U77">
         <v>0.06618110587651871</v>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.184417915703916</v>
+        <v>4.129359785234128</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09030500236904428</v>
+        <v>0.09018542331330971</v>
       </c>
       <c r="C78">
-        <v>744.7209086700473</v>
+        <v>724.8658777456765</v>
       </c>
       <c r="D78">
-        <v>2255.652908670047</v>
+        <v>2261.729877745676</v>
       </c>
       <c r="E78">
-        <v>168.4319999999998</v>
+        <v>194.3639999999998</v>
       </c>
       <c r="F78">
-        <v>1970.832</v>
+        <v>1996.764</v>
       </c>
       <c r="G78">
         <v>459.9</v>
@@ -7808,28 +7808,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M78">
-        <v>130.4318412568311</v>
+        <v>132.148049694421</v>
       </c>
       <c r="N78">
-        <v>408.1681587431688</v>
+        <v>406.4519503055789</v>
       </c>
       <c r="O78">
-        <v>110.2054028606556</v>
+        <v>109.7420265825063</v>
       </c>
       <c r="P78">
-        <v>297.9627558825132</v>
+        <v>296.7099237230726</v>
       </c>
       <c r="Q78">
-        <v>668.3627558825133</v>
+        <v>667.1099237230726</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2232821867864654</v>
+        <v>0.230369668261385</v>
       </c>
       <c r="T78">
-        <v>3.250648580163603</v>
+        <v>3.38045829239744</v>
       </c>
       <c r="U78">
         <v>0.06618110587651871</v>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.129359785234128</v>
+        <v>4.075731736075243</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09018542331330971</v>
+        <v>0.09006584425757513</v>
       </c>
       <c r="C79">
-        <v>724.8658777456765</v>
+        <v>705.043679278745</v>
       </c>
       <c r="D79">
-        <v>2261.729877745676</v>
+        <v>2267.839679278745</v>
       </c>
       <c r="E79">
-        <v>194.3639999999998</v>
+        <v>220.2959999999998</v>
       </c>
       <c r="F79">
-        <v>1996.764</v>
+        <v>2022.696</v>
       </c>
       <c r="G79">
         <v>459.9</v>
@@ -7890,28 +7890,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M79">
-        <v>132.148049694421</v>
+        <v>133.8642581320109</v>
       </c>
       <c r="N79">
-        <v>406.4519503055789</v>
+        <v>404.735741867989</v>
       </c>
       <c r="O79">
-        <v>109.7420265825063</v>
+        <v>109.278650304357</v>
       </c>
       <c r="P79">
-        <v>296.7099237230726</v>
+        <v>295.457091563632</v>
       </c>
       <c r="Q79">
-        <v>667.1099237230726</v>
+        <v>665.857091563632</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.230369668261385</v>
+        <v>0.2381014662340245</v>
       </c>
       <c r="T79">
-        <v>3.38045829239744</v>
+        <v>3.522068887561626</v>
       </c>
       <c r="U79">
         <v>0.06618110587651871</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.075731736075243</v>
+        <v>4.023478765099918</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09006584425757513</v>
+        <v>0.09196471520184059</v>
       </c>
       <c r="C80">
-        <v>705.043679278745</v>
+        <v>585.8297245562558</v>
       </c>
       <c r="D80">
-        <v>2267.839679278745</v>
+        <v>2174.557724556256</v>
       </c>
       <c r="E80">
-        <v>220.2959999999998</v>
+        <v>246.2280000000001</v>
       </c>
       <c r="F80">
-        <v>2022.696</v>
+        <v>2048.628</v>
       </c>
       <c r="G80">
         <v>459.9</v>
@@ -7972,45 +7972,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M80">
-        <v>133.8642581320109</v>
+        <v>142.7506645696008</v>
       </c>
       <c r="N80">
-        <v>404.735741867989</v>
+        <v>395.8493354303992</v>
       </c>
       <c r="O80">
-        <v>109.278650304357</v>
+        <v>106.8793205662078</v>
       </c>
       <c r="P80">
-        <v>295.457091563632</v>
+        <v>288.9700148641914</v>
       </c>
       <c r="Q80">
-        <v>665.857091563632</v>
+        <v>659.3700148641915</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2381014662340245</v>
+        <v>0.2465696259183441</v>
       </c>
       <c r="T80">
-        <v>3.522068887561626</v>
+        <v>3.677166206074782</v>
       </c>
       <c r="U80">
-        <v>0.06618110587651871</v>
+        <v>0.06968110587651871</v>
       </c>
       <c r="V80">
         <v>0.27</v>
       </c>
       <c r="W80">
-        <v>0.04831220728985865</v>
+        <v>0.05086720728985866</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.023478765099918</v>
+        <v>3.773012207150849</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09196471520184059</v>
+        <v>0.09187068614610602</v>
       </c>
       <c r="C81">
-        <v>585.8297245562558</v>
+        <v>564.3359395381617</v>
       </c>
       <c r="D81">
-        <v>2174.557724556256</v>
+        <v>2178.995939538162</v>
       </c>
       <c r="E81">
-        <v>246.2280000000001</v>
+        <v>272.1599999999999</v>
       </c>
       <c r="F81">
-        <v>2048.628</v>
+        <v>2074.56</v>
       </c>
       <c r="G81">
         <v>459.9</v>
@@ -8054,28 +8054,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M81">
-        <v>142.7506645696008</v>
+        <v>144.5576350071907</v>
       </c>
       <c r="N81">
-        <v>395.8493354303992</v>
+        <v>394.0423649928092</v>
       </c>
       <c r="O81">
-        <v>106.8793205662078</v>
+        <v>106.3914385480585</v>
       </c>
       <c r="P81">
-        <v>288.9700148641914</v>
+        <v>287.6509264447507</v>
       </c>
       <c r="Q81">
-        <v>659.3700148641915</v>
+        <v>658.0509264447508</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2465696259183441</v>
+        <v>0.2558846015710955</v>
       </c>
       <c r="T81">
-        <v>3.677166206074782</v>
+        <v>3.847773256439253</v>
       </c>
       <c r="U81">
         <v>0.06968110587651871</v>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.773012207150849</v>
+        <v>3.725849554561463</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09187068614610602</v>
+        <v>0.09177665709037144</v>
       </c>
       <c r="C82">
-        <v>564.3359395381617</v>
+        <v>542.8603081306305</v>
       </c>
       <c r="D82">
-        <v>2178.995939538162</v>
+        <v>2183.452308130631</v>
       </c>
       <c r="E82">
-        <v>272.1599999999999</v>
+        <v>298.0920000000001</v>
       </c>
       <c r="F82">
-        <v>2074.56</v>
+        <v>2100.492</v>
       </c>
       <c r="G82">
         <v>459.9</v>
@@ -8136,28 +8136,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M82">
-        <v>144.5576350071907</v>
+        <v>146.3646054447806</v>
       </c>
       <c r="N82">
-        <v>394.0423649928092</v>
+        <v>392.2353945552194</v>
       </c>
       <c r="O82">
-        <v>106.3914385480585</v>
+        <v>105.9035565299092</v>
       </c>
       <c r="P82">
-        <v>287.6509264447507</v>
+        <v>286.3318380253102</v>
       </c>
       <c r="Q82">
-        <v>658.0509264447508</v>
+        <v>656.7318380253103</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2558846015710955</v>
+        <v>0.2661801009767681</v>
       </c>
       <c r="T82">
-        <v>3.847773256439253</v>
+        <v>4.036338943684195</v>
       </c>
       <c r="U82">
         <v>0.06968110587651871</v>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.725849554561463</v>
+        <v>3.679851411912556</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09177665709037144</v>
+        <v>0.09168262803463689</v>
       </c>
       <c r="C83">
-        <v>542.8603081306305</v>
+        <v>521.4029419423637</v>
       </c>
       <c r="D83">
-        <v>2183.452308130631</v>
+        <v>2187.926941942364</v>
       </c>
       <c r="E83">
-        <v>298.0920000000001</v>
+        <v>324.0239999999999</v>
       </c>
       <c r="F83">
-        <v>2100.492</v>
+        <v>2126.424</v>
       </c>
       <c r="G83">
         <v>459.9</v>
@@ -8218,28 +8218,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M83">
-        <v>146.3646054447806</v>
+        <v>148.1715758823704</v>
       </c>
       <c r="N83">
-        <v>392.2353945552194</v>
+        <v>390.4284241176294</v>
       </c>
       <c r="O83">
-        <v>105.9035565299092</v>
+        <v>105.41567451176</v>
       </c>
       <c r="P83">
-        <v>286.3318380253102</v>
+        <v>285.0127496058695</v>
       </c>
       <c r="Q83">
-        <v>656.7318380253103</v>
+        <v>655.4127496058695</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2661801009767681</v>
+        <v>0.2776195447608489</v>
       </c>
       <c r="T83">
-        <v>4.036338943684195</v>
+        <v>4.245856373956353</v>
       </c>
       <c r="U83">
         <v>0.06968110587651871</v>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.679851411912556</v>
+        <v>3.634975175181915</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09168262803463689</v>
+        <v>0.09158859897890231</v>
       </c>
       <c r="C84">
-        <v>521.4029419423637</v>
+        <v>499.9639534988401</v>
       </c>
       <c r="D84">
-        <v>2187.926941942364</v>
+        <v>2192.41995349884</v>
       </c>
       <c r="E84">
-        <v>324.0239999999999</v>
+        <v>349.9560000000001</v>
       </c>
       <c r="F84">
-        <v>2126.424</v>
+        <v>2152.356</v>
       </c>
       <c r="G84">
         <v>459.9</v>
@@ -8300,28 +8300,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M84">
-        <v>148.1715758823704</v>
+        <v>149.9785463199603</v>
       </c>
       <c r="N84">
-        <v>390.4284241176294</v>
+        <v>388.6214536800396</v>
       </c>
       <c r="O84">
-        <v>105.41567451176</v>
+        <v>104.9277924936107</v>
       </c>
       <c r="P84">
-        <v>285.0127496058695</v>
+        <v>283.6936611864289</v>
       </c>
       <c r="Q84">
-        <v>655.4127496058695</v>
+        <v>654.093661186429</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2776195447608489</v>
+        <v>0.2904048054607039</v>
       </c>
       <c r="T84">
-        <v>4.245856373956353</v>
+        <v>4.480022913672295</v>
       </c>
       <c r="U84">
         <v>0.06968110587651871</v>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.634975175181915</v>
+        <v>3.591180293553218</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09158859897890231</v>
+        <v>0.09149456992316776</v>
       </c>
       <c r="C85">
-        <v>499.9639534988401</v>
+        <v>478.5434562517435</v>
       </c>
       <c r="D85">
-        <v>2192.41995349884</v>
+        <v>2196.931456251743</v>
       </c>
       <c r="E85">
-        <v>349.9560000000001</v>
+        <v>375.8879999999999</v>
       </c>
       <c r="F85">
-        <v>2152.356</v>
+        <v>2178.288</v>
       </c>
       <c r="G85">
         <v>459.9</v>
@@ -8382,28 +8382,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M85">
-        <v>149.9785463199603</v>
+        <v>151.7855167575502</v>
       </c>
       <c r="N85">
-        <v>388.6214536800396</v>
+        <v>386.8144832424497</v>
       </c>
       <c r="O85">
-        <v>104.9277924936107</v>
+        <v>104.4399104754614</v>
       </c>
       <c r="P85">
-        <v>283.6936611864289</v>
+        <v>282.3745727669883</v>
       </c>
       <c r="Q85">
-        <v>654.093661186429</v>
+        <v>652.7745727669883</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2904048054607039</v>
+        <v>0.3047882237480407</v>
       </c>
       <c r="T85">
-        <v>4.480022913672295</v>
+        <v>4.743460270852729</v>
       </c>
       <c r="U85">
         <v>0.06968110587651871</v>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.591180293553218</v>
+        <v>3.548428147201393</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09149456992316776</v>
+        <v>0.09140054086743318</v>
       </c>
       <c r="C86">
-        <v>478.5434562517439</v>
+        <v>457.1415645885172</v>
       </c>
       <c r="D86">
-        <v>2196.931456251743</v>
+        <v>2201.461564588517</v>
       </c>
       <c r="E86">
-        <v>375.8879999999995</v>
+        <v>401.8199999999997</v>
       </c>
       <c r="F86">
-        <v>2178.288</v>
+        <v>2204.22</v>
       </c>
       <c r="G86">
         <v>459.9</v>
@@ -8464,28 +8464,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M86">
-        <v>151.7855167575502</v>
+        <v>153.5924871951401</v>
       </c>
       <c r="N86">
-        <v>386.8144832424497</v>
+        <v>385.0075128048599</v>
       </c>
       <c r="O86">
-        <v>104.4399104754614</v>
+        <v>103.9520284573122</v>
       </c>
       <c r="P86">
-        <v>282.3745727669883</v>
+        <v>281.0554843475477</v>
       </c>
       <c r="Q86">
-        <v>652.7745727669883</v>
+        <v>651.4554843475478</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3047882237480405</v>
+        <v>0.3210894311403555</v>
       </c>
       <c r="T86">
-        <v>4.743460270852726</v>
+        <v>5.04202260899055</v>
       </c>
       <c r="U86">
         <v>0.06968110587651871</v>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.548428147201394</v>
+        <v>3.506681933704907</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09140054086743318</v>
+        <v>0.09306435181169861</v>
       </c>
       <c r="C87">
-        <v>457.1415645885172</v>
+        <v>353.7131914416955</v>
       </c>
       <c r="D87">
-        <v>2201.461564588517</v>
+        <v>2123.965191441695</v>
       </c>
       <c r="E87">
-        <v>401.8199999999997</v>
+        <v>427.7519999999995</v>
       </c>
       <c r="F87">
-        <v>2204.22</v>
+        <v>2230.152</v>
       </c>
       <c r="G87">
         <v>459.9</v>
@@ -8546,45 +8546,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M87">
-        <v>153.5924871951401</v>
+        <v>161.6438832327299</v>
       </c>
       <c r="N87">
-        <v>385.0075128048599</v>
+        <v>376.95611676727</v>
       </c>
       <c r="O87">
-        <v>103.9520284573122</v>
+        <v>101.7781515271629</v>
       </c>
       <c r="P87">
-        <v>281.0554843475477</v>
+        <v>275.1779652401071</v>
       </c>
       <c r="Q87">
-        <v>651.4554843475478</v>
+        <v>645.5779652401071</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3210894311403555</v>
+        <v>0.3397193824458584</v>
       </c>
       <c r="T87">
-        <v>5.04202260899055</v>
+        <v>5.383236709719493</v>
       </c>
       <c r="U87">
-        <v>0.06968110587651871</v>
+        <v>0.07248110587651871</v>
       </c>
       <c r="V87">
         <v>0.27</v>
       </c>
       <c r="W87">
-        <v>0.05086720728985866</v>
+        <v>0.05291120728985865</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y87">
-        <v>3.506681933704907</v>
+        <v>3.332015967622728</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09306435181169861</v>
+        <v>0.09299076275596405</v>
       </c>
       <c r="C88">
-        <v>353.7131914416955</v>
+        <v>331.0932928726374</v>
       </c>
       <c r="D88">
-        <v>2123.965191441695</v>
+        <v>2127.277292872637</v>
       </c>
       <c r="E88">
-        <v>427.7519999999995</v>
+        <v>453.6839999999997</v>
       </c>
       <c r="F88">
-        <v>2230.152</v>
+        <v>2256.084</v>
       </c>
       <c r="G88">
         <v>459.9</v>
@@ -8628,28 +8628,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M88">
-        <v>161.6438832327299</v>
+        <v>163.5234632703198</v>
       </c>
       <c r="N88">
-        <v>376.95611676727</v>
+        <v>375.0765367296801</v>
       </c>
       <c r="O88">
-        <v>101.7781515271629</v>
+        <v>101.2706649170136</v>
       </c>
       <c r="P88">
-        <v>275.1779652401071</v>
+        <v>273.8058718126665</v>
       </c>
       <c r="Q88">
-        <v>645.5779652401071</v>
+        <v>644.2058718126666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3397193824458584</v>
+        <v>0.361215480106054</v>
       </c>
       <c r="T88">
-        <v>5.383236709719493</v>
+        <v>5.776945287483657</v>
       </c>
       <c r="U88">
         <v>0.07248110587651871</v>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.332015967622728</v>
+        <v>3.293716933512123</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09299076275596405</v>
+        <v>0.09291717370022949</v>
       </c>
       <c r="C89">
-        <v>331.0932928726374</v>
+        <v>308.483740188005</v>
       </c>
       <c r="D89">
-        <v>2127.277292872637</v>
+        <v>2130.599740188005</v>
       </c>
       <c r="E89">
-        <v>453.6839999999997</v>
+        <v>479.616</v>
       </c>
       <c r="F89">
-        <v>2256.084</v>
+        <v>2282.016</v>
       </c>
       <c r="G89">
         <v>459.9</v>
@@ -8710,28 +8710,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M89">
-        <v>163.5234632703198</v>
+        <v>165.4030433079097</v>
       </c>
       <c r="N89">
-        <v>375.0765367296801</v>
+        <v>373.1969566920902</v>
       </c>
       <c r="O89">
-        <v>101.2706649170136</v>
+        <v>100.7631783068644</v>
       </c>
       <c r="P89">
-        <v>273.8058718126665</v>
+        <v>272.4337783852259</v>
       </c>
       <c r="Q89">
-        <v>644.2058718126666</v>
+        <v>642.833778385226</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.361215480106054</v>
+        <v>0.3862942607096156</v>
       </c>
       <c r="T89">
-        <v>5.776945287483657</v>
+        <v>6.23627196154185</v>
       </c>
       <c r="U89">
         <v>0.07248110587651871</v>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.293716933512123</v>
+        <v>3.256288331994939</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09291717370022949</v>
+        <v>0.09284358464449492</v>
       </c>
       <c r="C90">
-        <v>308.483740188005</v>
+        <v>285.884581939194</v>
       </c>
       <c r="D90">
-        <v>2130.599740188005</v>
+        <v>2133.932581939194</v>
       </c>
       <c r="E90">
-        <v>479.616</v>
+        <v>505.5479999999998</v>
       </c>
       <c r="F90">
-        <v>2282.016</v>
+        <v>2307.948</v>
       </c>
       <c r="G90">
         <v>459.9</v>
@@ -8792,28 +8792,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M90">
-        <v>165.4030433079097</v>
+        <v>167.2826233454996</v>
       </c>
       <c r="N90">
-        <v>373.1969566920902</v>
+        <v>371.3173766545003</v>
       </c>
       <c r="O90">
-        <v>100.7631783068644</v>
+        <v>100.2556916967151</v>
       </c>
       <c r="P90">
-        <v>272.4337783852259</v>
+        <v>271.0616849577852</v>
       </c>
       <c r="Q90">
-        <v>642.833778385226</v>
+        <v>641.4616849577853</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3862942607096156</v>
+        <v>0.4159328196047339</v>
       </c>
       <c r="T90">
-        <v>6.23627196154185</v>
+        <v>6.779112576337895</v>
       </c>
       <c r="U90">
         <v>0.07248110587651871</v>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.256288331994939</v>
+        <v>3.219700822646681</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09284358464449492</v>
+        <v>0.09276999558876035</v>
       </c>
       <c r="C91">
-        <v>285.884581939194</v>
+        <v>263.2958669818627</v>
       </c>
       <c r="D91">
-        <v>2133.932581939194</v>
+        <v>2137.275866981863</v>
       </c>
       <c r="E91">
-        <v>505.5479999999998</v>
+        <v>531.48</v>
       </c>
       <c r="F91">
-        <v>2307.948</v>
+        <v>2333.88</v>
       </c>
       <c r="G91">
         <v>459.9</v>
@@ -8874,28 +8874,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M91">
-        <v>167.2826233454996</v>
+        <v>169.1622033830895</v>
       </c>
       <c r="N91">
-        <v>371.3173766545003</v>
+        <v>369.4377966169104</v>
       </c>
       <c r="O91">
-        <v>100.2556916967151</v>
+        <v>99.74820508656582</v>
       </c>
       <c r="P91">
-        <v>271.0616849577852</v>
+        <v>269.6895915303446</v>
       </c>
       <c r="Q91">
-        <v>641.4616849577853</v>
+        <v>640.0895915303447</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4159328196047339</v>
+        <v>0.4514990902788757</v>
       </c>
       <c r="T91">
-        <v>6.779112576337895</v>
+        <v>7.430521314093149</v>
       </c>
       <c r="U91">
         <v>0.07248110587651871</v>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.219700822646681</v>
+        <v>3.183926369061718</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09276999558876035</v>
+        <v>0.0926964065330258</v>
       </c>
       <c r="C92">
-        <v>263.2958669818627</v>
+        <v>240.7176444783263</v>
       </c>
       <c r="D92">
-        <v>2137.275866981863</v>
+        <v>2140.629644478326</v>
       </c>
       <c r="E92">
-        <v>531.48</v>
+        <v>557.4119999999998</v>
       </c>
       <c r="F92">
-        <v>2333.88</v>
+        <v>2359.812</v>
       </c>
       <c r="G92">
         <v>459.9</v>
@@ -8956,28 +8956,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M92">
-        <v>169.1622033830895</v>
+        <v>171.0417834206794</v>
       </c>
       <c r="N92">
-        <v>369.4377966169104</v>
+        <v>367.5582165793205</v>
       </c>
       <c r="O92">
-        <v>99.74820508656582</v>
+        <v>99.24071847641655</v>
       </c>
       <c r="P92">
-        <v>269.6895915303446</v>
+        <v>268.317498102904</v>
       </c>
       <c r="Q92">
-        <v>640.0895915303447</v>
+        <v>638.7174981029041</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4514990902788757</v>
+        <v>0.4949689766583826</v>
       </c>
       <c r="T92">
-        <v>7.430521314093149</v>
+        <v>8.22668754912735</v>
       </c>
       <c r="U92">
         <v>0.07248110587651871</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.183926369061718</v>
+        <v>3.148938167203896</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0926964065330258</v>
+        <v>0.09262281747729123</v>
       </c>
       <c r="C93">
-        <v>240.7176444783263</v>
+        <v>218.1499638999626</v>
       </c>
       <c r="D93">
-        <v>2140.629644478326</v>
+        <v>2143.993963899963</v>
       </c>
       <c r="E93">
-        <v>557.4119999999998</v>
+        <v>583.3440000000001</v>
       </c>
       <c r="F93">
-        <v>2359.812</v>
+        <v>2385.744</v>
       </c>
       <c r="G93">
         <v>459.9</v>
@@ -9038,28 +9038,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M93">
-        <v>171.0417834206794</v>
+        <v>172.9213634582693</v>
       </c>
       <c r="N93">
-        <v>367.5582165793205</v>
+        <v>365.6786365417306</v>
       </c>
       <c r="O93">
-        <v>99.24071847641655</v>
+        <v>98.73323186626727</v>
       </c>
       <c r="P93">
-        <v>268.317498102904</v>
+        <v>266.9454046754634</v>
       </c>
       <c r="Q93">
-        <v>638.7174981029041</v>
+        <v>637.3454046754634</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4949689766583826</v>
+        <v>0.549306334632766</v>
       </c>
       <c r="T93">
-        <v>8.22668754912735</v>
+        <v>9.221895342920101</v>
       </c>
       <c r="U93">
         <v>0.07248110587651871</v>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.148938167203896</v>
+        <v>3.11471057842994</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09262281747729123</v>
+        <v>0.09254922842155665</v>
       </c>
       <c r="C94">
-        <v>218.1499638999626</v>
+        <v>195.5928750296462</v>
       </c>
       <c r="D94">
-        <v>2143.993963899963</v>
+        <v>2147.368875029646</v>
       </c>
       <c r="E94">
-        <v>583.3440000000001</v>
+        <v>609.2759999999998</v>
       </c>
       <c r="F94">
-        <v>2385.744</v>
+        <v>2411.676</v>
       </c>
       <c r="G94">
         <v>459.9</v>
@@ -9120,28 +9120,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M94">
-        <v>172.9213634582693</v>
+        <v>174.8009434958591</v>
       </c>
       <c r="N94">
-        <v>365.6786365417306</v>
+        <v>363.7990565041408</v>
       </c>
       <c r="O94">
-        <v>98.73323186626727</v>
+        <v>98.22574525611803</v>
       </c>
       <c r="P94">
-        <v>266.9454046754634</v>
+        <v>265.5733112480228</v>
       </c>
       <c r="Q94">
-        <v>637.3454046754634</v>
+        <v>635.9733112480228</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.549306334632766</v>
+        <v>0.6191686520284019</v>
       </c>
       <c r="T94">
-        <v>9.221895342920101</v>
+        <v>10.50144822065364</v>
       </c>
       <c r="U94">
         <v>0.07248110587651871</v>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.11471057842994</v>
+        <v>3.081219066833921</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09254922842155665</v>
+        <v>0.09247563936582209</v>
       </c>
       <c r="C95">
-        <v>195.5928750296462</v>
+        <v>173.0464279642015</v>
       </c>
       <c r="D95">
-        <v>2147.368875029646</v>
+        <v>2150.754427964202</v>
       </c>
       <c r="E95">
-        <v>609.2759999999998</v>
+        <v>635.2080000000001</v>
       </c>
       <c r="F95">
-        <v>2411.676</v>
+        <v>2437.608</v>
       </c>
       <c r="G95">
         <v>459.9</v>
@@ -9202,28 +9202,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M95">
-        <v>174.8009434958591</v>
+        <v>176.680523533449</v>
       </c>
       <c r="N95">
-        <v>363.7990565041408</v>
+        <v>361.9194764665509</v>
       </c>
       <c r="O95">
-        <v>98.22574525611803</v>
+        <v>97.71825864596876</v>
       </c>
       <c r="P95">
-        <v>265.5733112480228</v>
+        <v>264.2012178205821</v>
       </c>
       <c r="Q95">
-        <v>635.9733112480228</v>
+        <v>634.6012178205822</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6191686520284019</v>
+        <v>0.7123184085559165</v>
       </c>
       <c r="T95">
-        <v>10.50144822065364</v>
+        <v>12.20751872429835</v>
       </c>
       <c r="U95">
         <v>0.07248110587651871</v>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.081219066833921</v>
+        <v>3.048440140591006</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09247563936582209</v>
+        <v>0.09240205031008752</v>
       </c>
       <c r="C96">
-        <v>173.0464279642015</v>
+        <v>150.5106731168867</v>
       </c>
       <c r="D96">
-        <v>2150.754427964202</v>
+        <v>2154.150673116887</v>
       </c>
       <c r="E96">
-        <v>635.2080000000001</v>
+        <v>661.1399999999999</v>
       </c>
       <c r="F96">
-        <v>2437.608</v>
+        <v>2463.54</v>
       </c>
       <c r="G96">
         <v>459.9</v>
@@ -9284,28 +9284,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M96">
-        <v>176.680523533449</v>
+        <v>178.5601035710389</v>
       </c>
       <c r="N96">
-        <v>361.9194764665509</v>
+        <v>360.039896428961</v>
       </c>
       <c r="O96">
-        <v>97.71825864596876</v>
+        <v>97.21077203581947</v>
       </c>
       <c r="P96">
-        <v>264.2012178205821</v>
+        <v>262.8291243931416</v>
       </c>
       <c r="Q96">
-        <v>634.6012178205822</v>
+        <v>633.2291243931415</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7123184085559165</v>
+        <v>0.8427280676944371</v>
       </c>
       <c r="T96">
-        <v>12.20751872429835</v>
+        <v>14.59601742940096</v>
       </c>
       <c r="U96">
         <v>0.07248110587651871</v>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.048440140591006</v>
+        <v>3.016351297005838</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09240205031008752</v>
+        <v>0.09779470125435297</v>
       </c>
       <c r="C97">
-        <v>150.5106731168867</v>
+        <v>-98.83991341651108</v>
       </c>
       <c r="D97">
-        <v>2154.150673116887</v>
+        <v>1930.732086583489</v>
       </c>
       <c r="E97">
-        <v>661.1399999999999</v>
+        <v>687.0720000000001</v>
       </c>
       <c r="F97">
-        <v>2463.54</v>
+        <v>2489.472</v>
       </c>
       <c r="G97">
         <v>459.9</v>
@@ -9366,45 +9366,45 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M97">
-        <v>178.5601035710389</v>
+        <v>199.8575652086288</v>
       </c>
       <c r="N97">
-        <v>360.039896428961</v>
+        <v>338.7424347913711</v>
       </c>
       <c r="O97">
-        <v>97.21077203581947</v>
+        <v>91.46045739367021</v>
       </c>
       <c r="P97">
-        <v>262.8291243931416</v>
+        <v>247.2819773977009</v>
       </c>
       <c r="Q97">
-        <v>633.2291243931415</v>
+        <v>617.681977397701</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8427280676944371</v>
+        <v>1.038342556402218</v>
       </c>
       <c r="T97">
-        <v>14.59601742940096</v>
+        <v>18.17876548705487</v>
       </c>
       <c r="U97">
-        <v>0.07248110587651871</v>
+        <v>0.08028110587651871</v>
       </c>
       <c r="V97">
         <v>0.27</v>
       </c>
       <c r="W97">
-        <v>0.05291120728985865</v>
+        <v>0.05860520728985866</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y97">
-        <v>3.016351297005838</v>
+        <v>2.69491925130661</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09779470125435297</v>
+        <v>0.0977780521986184</v>
       </c>
       <c r="C98">
-        <v>-98.83991341651063</v>
+        <v>-124.1534818909272</v>
       </c>
       <c r="D98">
-        <v>1930.732086583489</v>
+        <v>1931.350518109072</v>
       </c>
       <c r="E98">
-        <v>687.0719999999997</v>
+        <v>713.0039999999995</v>
       </c>
       <c r="F98">
-        <v>2489.472</v>
+        <v>2515.404</v>
       </c>
       <c r="G98">
         <v>459.9</v>
@@ -9448,28 +9448,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M98">
-        <v>199.8575652086288</v>
+        <v>201.9394148462186</v>
       </c>
       <c r="N98">
-        <v>338.7424347913711</v>
+        <v>336.6605851537813</v>
       </c>
       <c r="O98">
-        <v>91.46045739367021</v>
+        <v>90.89835799152097</v>
       </c>
       <c r="P98">
-        <v>247.2819773977009</v>
+        <v>245.7622271622603</v>
       </c>
       <c r="Q98">
-        <v>617.681977397701</v>
+        <v>616.1622271622604</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.038342556402216</v>
+        <v>1.364366704248516</v>
       </c>
       <c r="T98">
-        <v>18.17876548705482</v>
+        <v>24.15001224981131</v>
       </c>
       <c r="U98">
         <v>0.08028110587651871</v>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.694919251306611</v>
+        <v>2.667136578612729</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0977780521986184</v>
+        <v>0.09776140314288384</v>
       </c>
       <c r="C99">
-        <v>-124.1534818909272</v>
+        <v>-149.4666540596127</v>
       </c>
       <c r="D99">
-        <v>1931.350518109072</v>
+        <v>1931.969345940387</v>
       </c>
       <c r="E99">
-        <v>713.0039999999995</v>
+        <v>738.9359999999997</v>
       </c>
       <c r="F99">
-        <v>2515.404</v>
+        <v>2541.336</v>
       </c>
       <c r="G99">
         <v>459.9</v>
@@ -9530,28 +9530,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M99">
-        <v>201.9394148462186</v>
+        <v>204.0212644838085</v>
       </c>
       <c r="N99">
-        <v>336.6605851537813</v>
+        <v>334.5787355161914</v>
       </c>
       <c r="O99">
-        <v>90.89835799152097</v>
+        <v>90.33625858937168</v>
       </c>
       <c r="P99">
-        <v>245.7622271622603</v>
+        <v>244.2424769268197</v>
       </c>
       <c r="Q99">
-        <v>616.1622271622604</v>
+        <v>614.6424769268198</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.364366704248516</v>
+        <v>2.016414999941116</v>
       </c>
       <c r="T99">
-        <v>24.15001224981131</v>
+        <v>36.09250577532428</v>
       </c>
       <c r="U99">
         <v>0.08028110587651871</v>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.667136578612729</v>
+        <v>2.639920899239129</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09776140314288384</v>
+        <v>0.09774475408714928</v>
       </c>
       <c r="C100">
-        <v>-149.4666540596127</v>
+        <v>-174.779429541501</v>
       </c>
       <c r="D100">
-        <v>1931.969345940387</v>
+        <v>1932.588570458498</v>
       </c>
       <c r="E100">
-        <v>738.9359999999997</v>
+        <v>764.8679999999995</v>
       </c>
       <c r="F100">
-        <v>2541.336</v>
+        <v>2567.268</v>
       </c>
       <c r="G100">
         <v>459.9</v>
@@ -9612,28 +9612,28 @@
         <v>538.5999999999999</v>
       </c>
       <c r="M100">
-        <v>204.0212644838085</v>
+        <v>206.1031141213984</v>
       </c>
       <c r="N100">
-        <v>334.5787355161914</v>
+        <v>332.4968858786015</v>
       </c>
       <c r="O100">
-        <v>90.33625858937168</v>
+        <v>89.77415918722241</v>
       </c>
       <c r="P100">
-        <v>244.2424769268197</v>
+        <v>242.7227266913791</v>
       </c>
       <c r="Q100">
-        <v>614.6424769268198</v>
+        <v>613.1227266913792</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.016414999941116</v>
+        <v>3.972559887018916</v>
       </c>
       <c r="T100">
-        <v>36.09250577532428</v>
+        <v>71.91998635186322</v>
       </c>
       <c r="U100">
         <v>0.08028110587651871</v>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.639920899239129</v>
+        <v>2.613255031570047</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09774475408714928</v>
-      </c>
-      <c r="C101">
-        <v>-174.779429541501</v>
-      </c>
-      <c r="D101">
-        <v>1932.588570458498</v>
-      </c>
-      <c r="E101">
-        <v>764.8679999999995</v>
-      </c>
-      <c r="F101">
-        <v>2567.268</v>
-      </c>
-      <c r="G101">
-        <v>459.9</v>
-      </c>
-      <c r="H101">
-        <v>790.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>909</v>
-      </c>
-      <c r="K101">
-        <v>370.4</v>
-      </c>
-      <c r="L101">
-        <v>538.5999999999999</v>
-      </c>
-      <c r="M101">
-        <v>206.1031141213984</v>
-      </c>
-      <c r="N101">
-        <v>332.4968858786015</v>
-      </c>
-      <c r="O101">
-        <v>89.77415918722241</v>
-      </c>
-      <c r="P101">
-        <v>242.7227266913791</v>
-      </c>
-      <c r="Q101">
-        <v>613.1227266913792</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.972559887018916</v>
-      </c>
-      <c r="T101">
-        <v>71.91998635186322</v>
-      </c>
-      <c r="U101">
-        <v>0.08028110587651871</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.05860520728985866</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.613255031570047</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
